--- a/data/50001592 - VITA EXPRESS INC (Venezuela).xlsx
+++ b/data/50001592 - VITA EXPRESS INC (Venezuela).xlsx
@@ -2625,7 +2625,7 @@
       </c>
       <c r="C17" s="10"/>
       <c r="D17" s="9">
-        <v>46240.58590744213</v>
+        <v>46246.17197285879</v>
       </c>
       <c r="E17" s="10" t="s">
         <v>64</v>
@@ -3160,7 +3160,7 @@
       </c>
       <c r="C26" s="6"/>
       <c r="D26" s="5">
-        <v>46245.17159903936</v>
+        <v>46246.170240127314</v>
       </c>
       <c r="E26" s="6" t="s">
         <v>67</v>
@@ -3204,8 +3204,8 @@
       <c r="R26" s="5">
         <v>46244</v>
       </c>
-      <c r="S26" s="7" t="s">
-        <v>42</v>
+      <c r="S26" s="11" t="s">
+        <v>33</v>
       </c>
       <c r="T26" s="6">
         <v>0</v>
@@ -3223,7 +3223,7 @@
       </c>
       <c r="C27" s="10"/>
       <c r="D27" s="9">
-        <v>46240.586119803236</v>
+        <v>46246.17176618056</v>
       </c>
       <c r="E27" s="10" t="s">
         <v>99</v>
@@ -6108,7 +6108,7 @@
       </c>
       <c r="C78" s="6"/>
       <c r="D78" s="5">
-        <v>46240.58769424769</v>
+        <v>46246.171966249996</v>
       </c>
       <c r="E78" s="6" t="s">
         <v>248</v>
@@ -6171,7 +6171,7 @@
       </c>
       <c r="C79" s="10"/>
       <c r="D79" s="9">
-        <v>46240.58769032407</v>
+        <v>46246.171974259254</v>
       </c>
       <c r="E79" s="10" t="s">
         <v>251</v>
@@ -6957,7 +6957,7 @@
       </c>
       <c r="C93" s="10"/>
       <c r="D93" s="9">
-        <v>46240.59364402777</v>
+        <v>46246.17023978009</v>
       </c>
       <c r="E93" s="10" t="s">
         <v>278</v>
@@ -7001,8 +7001,8 @@
       <c r="R93" s="9">
         <v>46395</v>
       </c>
-      <c r="S93" s="7" t="s">
-        <v>42</v>
+      <c r="S93" s="11" t="s">
+        <v>33</v>
       </c>
       <c r="T93" s="10">
         <v>0</v>

--- a/data/50001592 - VITA EXPRESS INC (Venezuela).xlsx
+++ b/data/50001592 - VITA EXPRESS INC (Venezuela).xlsx
@@ -2625,7 +2625,7 @@
       </c>
       <c r="C17" s="10"/>
       <c r="D17" s="9">
-        <v>46246.17197285879</v>
+        <v>46247.203117638885</v>
       </c>
       <c r="E17" s="10" t="s">
         <v>64</v>
@@ -2669,8 +2669,8 @@
       <c r="R17" s="9">
         <v>46245</v>
       </c>
-      <c r="S17" s="7" t="s">
-        <v>42</v>
+      <c r="S17" s="11" t="s">
+        <v>33</v>
       </c>
       <c r="T17" s="10">
         <v>0</v>
@@ -3223,7 +3223,7 @@
       </c>
       <c r="C27" s="10"/>
       <c r="D27" s="9">
-        <v>46246.17176618056</v>
+        <v>46247.20311861111</v>
       </c>
       <c r="E27" s="10" t="s">
         <v>99</v>
@@ -3267,8 +3267,8 @@
       <c r="R27" s="9">
         <v>46245</v>
       </c>
-      <c r="S27" s="7" t="s">
-        <v>42</v>
+      <c r="S27" s="11" t="s">
+        <v>33</v>
       </c>
       <c r="T27" s="10">
         <v>0</v>
@@ -6108,7 +6108,7 @@
       </c>
       <c r="C78" s="6"/>
       <c r="D78" s="5">
-        <v>46246.171966249996</v>
+        <v>46247.20311761574</v>
       </c>
       <c r="E78" s="6" t="s">
         <v>248</v>
@@ -6152,8 +6152,8 @@
       <c r="R78" s="5">
         <v>46245</v>
       </c>
-      <c r="S78" s="7" t="s">
-        <v>42</v>
+      <c r="S78" s="11" t="s">
+        <v>33</v>
       </c>
       <c r="T78" s="6">
         <v>0</v>
@@ -6171,7 +6171,7 @@
       </c>
       <c r="C79" s="10"/>
       <c r="D79" s="9">
-        <v>46246.171974259254</v>
+        <v>46247.2031178125</v>
       </c>
       <c r="E79" s="10" t="s">
         <v>251</v>
@@ -6215,8 +6215,8 @@
       <c r="R79" s="9">
         <v>46245</v>
       </c>
-      <c r="S79" s="7" t="s">
-        <v>42</v>
+      <c r="S79" s="11" t="s">
+        <v>33</v>
       </c>
       <c r="T79" s="10">
         <v>0</v>

--- a/data/50001592 - VITA EXPRESS INC (Venezuela).xlsx
+++ b/data/50001592 - VITA EXPRESS INC (Venezuela).xlsx
@@ -11,7 +11,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1813" uniqueCount="407">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1814" uniqueCount="409">
   <si>
     <t>50001592 - VITA EXPRESS INC (Venezuela)</t>
   </si>
@@ -546,28 +546,34 @@
     <t xml:space="preserve">Plano Preliminar ot 4395 </t>
   </si>
   <si>
+    <t>Gonzalo Javier Dávila Bade</t>
+  </si>
+  <si>
+    <t>gonzalo.davila@zitron.com</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Ingenieria y diseñoo:,Plano Definitivos ot 4395  </t>
+  </si>
+  <si>
+    <t>1217190619377469</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Plano Definitivos ot 4395  </t>
+  </si>
+  <si>
+    <t xml:space="preserve">Planos motor proveedor OT 4395 ,Plano Preliminar ot 4395 </t>
+  </si>
+  <si>
+    <t xml:space="preserve">Ingenieria y diseñoo:,Check Planos ot 4395  </t>
+  </si>
+  <si>
+    <t>1217190529385389</t>
+  </si>
+  <si>
     <t>Hernan Roberto Gutierrez Barrientos</t>
   </si>
   <si>
     <t>hgutierrez@zitron.com</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Ingenieria y diseñoo:,Plano Definitivos ot 4395  </t>
-  </si>
-  <si>
-    <t>1217190619377469</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Plano Definitivos ot 4395  </t>
-  </si>
-  <si>
-    <t xml:space="preserve">Planos motor proveedor OT 4395 ,Plano Preliminar ot 4395 </t>
-  </si>
-  <si>
-    <t xml:space="preserve">Ingenieria y diseñoo:,Check Planos ot 4395  </t>
-  </si>
-  <si>
-    <t>1217190529385389</t>
   </si>
   <si>
     <t>OT 4395 -ZVN 1-16-315/4 + TOB + REJ + 2FAR160/200,OT 4395 -ZVN 1-16-315/4 + TOB + REJ + 2FAR160/200,OT 4395 -ZVN 1-16-315/4 + TOB + REJ + 2FAR160/200,OT 4395 -ZVN 1-16-315/4 + TOB + REJ + 2FAR160/200,OT 4395 -ZVN 1-16-315/4 + TOB + REJ + 2FAR160/200,OT 4395 -ZVN 1-16-315/4 + TOB + REJ + 2FAR160/200,OT 4395 -ZVN 1-16-315/4 + TOB + REJ + 2FAR160/200,Propuesta Fabricación externa  ot 4395  ,Propuesta Mecanizado ot 4395  ,Propuesta Corte plasma ot 4395   ,propuesta Corte laser ot 4395  ,Ingenieria y diseñoo:,OT 4395 -ZVN 1-16-315/4 + TOB + REJ + 2FAR160/200</t>
@@ -2515,7 +2521,7 @@
       </c>
       <c r="C15" s="10"/>
       <c r="D15" s="9">
-        <v>46240.57186170139</v>
+        <v>46252.55271216435</v>
       </c>
       <c r="E15" s="10" t="s">
         <v>63</v>
@@ -2551,7 +2557,9 @@
       <c r="R15" s="10"/>
       <c r="S15" s="10"/>
       <c r="T15" s="10"/>
-      <c r="U15" s="10"/>
+      <c r="U15" s="12" t="s">
+        <v>49</v>
+      </c>
     </row>
     <row r="16" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A16" s="4" t="s">
@@ -2623,9 +2631,11 @@
       <c r="B17" s="9">
         <v>46239.57410570602</v>
       </c>
-      <c r="C17" s="10"/>
+      <c r="C17" s="9">
+        <v>46252.55268533565</v>
+      </c>
       <c r="D17" s="9">
-        <v>46247.203117638885</v>
+        <v>46252.552704629634</v>
       </c>
       <c r="E17" s="10" t="s">
         <v>64</v>
@@ -2673,10 +2683,10 @@
         <v>33</v>
       </c>
       <c r="T17" s="10">
-        <v>0</v>
-      </c>
-      <c r="U17" s="12" t="s">
-        <v>49</v>
+        <v>1</v>
+      </c>
+      <c r="U17" s="7" t="s">
+        <v>27</v>
       </c>
     </row>
     <row r="18" spans="1:21" x14ac:dyDescent="0.25">
@@ -4359,7 +4369,7 @@
       </c>
       <c r="C47" s="10"/>
       <c r="D47" s="9">
-        <v>46240.58684920139</v>
+        <v>46252.17035721065</v>
       </c>
       <c r="E47" s="10" t="s">
         <v>100</v>
@@ -4512,7 +4522,7 @@
       </c>
       <c r="C50" s="6"/>
       <c r="D50" s="5">
-        <v>46240.58698114583</v>
+        <v>46252.55284988426</v>
       </c>
       <c r="E50" s="6" t="s">
         <v>170</v>
@@ -4562,8 +4572,8 @@
       <c r="T50" s="6">
         <v>0</v>
       </c>
-      <c r="U50" s="11" t="s">
-        <v>43</v>
+      <c r="U50" s="12" t="s">
+        <v>49</v>
       </c>
     </row>
     <row r="51" spans="1:21" x14ac:dyDescent="0.25">
@@ -4575,7 +4585,7 @@
       </c>
       <c r="C51" s="10"/>
       <c r="D51" s="9">
-        <v>46240.58697746528</v>
+        <v>46251.97138391204</v>
       </c>
       <c r="E51" s="10" t="s">
         <v>175</v>
@@ -4647,10 +4657,10 @@
         <v>26</v>
       </c>
       <c r="G52" s="6" t="s">
-        <v>171</v>
+        <v>179</v>
       </c>
       <c r="H52" s="6" t="s">
-        <v>172</v>
+        <v>180</v>
       </c>
       <c r="I52" s="5">
         <v>46316</v>
@@ -4674,7 +4684,7 @@
         <v>175</v>
       </c>
       <c r="P52" s="6" t="s">
-        <v>179</v>
+        <v>181</v>
       </c>
       <c r="Q52" s="5">
         <v>46316</v>
@@ -4694,7 +4704,7 @@
     </row>
     <row r="53" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A53" s="8" t="s">
-        <v>180</v>
+        <v>182</v>
       </c>
       <c r="B53" s="9">
         <v>46239.57422061343</v>
@@ -4704,16 +4714,16 @@
         <v>46240.59657887732</v>
       </c>
       <c r="E53" s="10" t="s">
-        <v>181</v>
+        <v>183</v>
       </c>
       <c r="F53" s="10" t="s">
         <v>26</v>
       </c>
       <c r="G53" s="10" t="s">
-        <v>182</v>
+        <v>184</v>
       </c>
       <c r="H53" s="10" t="s">
-        <v>183</v>
+        <v>185</v>
       </c>
       <c r="I53" s="9">
         <v>46405</v>
@@ -4734,7 +4744,7 @@
         <v>167</v>
       </c>
       <c r="O53" s="10" t="s">
-        <v>184</v>
+        <v>186</v>
       </c>
       <c r="P53" s="10" t="s">
         <v>167</v>
@@ -4757,7 +4767,7 @@
     </row>
     <row r="54" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A54" s="4" t="s">
-        <v>185</v>
+        <v>187</v>
       </c>
       <c r="B54" s="5">
         <v>46239.57422527778</v>
@@ -4767,16 +4777,16 @@
         <v>46240.58711</v>
       </c>
       <c r="E54" s="6" t="s">
-        <v>186</v>
+        <v>188</v>
       </c>
       <c r="F54" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G54" s="6" t="s">
-        <v>182</v>
+        <v>184</v>
       </c>
       <c r="H54" s="6" t="s">
-        <v>183</v>
+        <v>185</v>
       </c>
       <c r="I54" s="5">
         <v>46405</v>
@@ -4794,13 +4804,13 @@
         <v>26</v>
       </c>
       <c r="N54" s="6" t="s">
-        <v>181</v>
+        <v>183</v>
       </c>
       <c r="O54" s="6" t="s">
-        <v>186</v>
+        <v>188</v>
       </c>
       <c r="P54" s="6" t="s">
-        <v>187</v>
+        <v>189</v>
       </c>
       <c r="Q54" s="6"/>
       <c r="R54" s="6"/>
@@ -4810,7 +4820,7 @@
     </row>
     <row r="55" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A55" s="8" t="s">
-        <v>188</v>
+        <v>190</v>
       </c>
       <c r="B55" s="9">
         <v>46239.5742288426</v>
@@ -4820,16 +4830,16 @@
         <v>46240.58710615741</v>
       </c>
       <c r="E55" s="10" t="s">
-        <v>186</v>
+        <v>188</v>
       </c>
       <c r="F55" s="10" t="s">
         <v>26</v>
       </c>
       <c r="G55" s="10" t="s">
-        <v>182</v>
+        <v>184</v>
       </c>
       <c r="H55" s="10" t="s">
-        <v>183</v>
+        <v>185</v>
       </c>
       <c r="I55" s="9">
         <v>46405</v>
@@ -4847,13 +4857,13 @@
         <v>26</v>
       </c>
       <c r="N55" s="10" t="s">
-        <v>181</v>
+        <v>183</v>
       </c>
       <c r="O55" s="10" t="s">
-        <v>186</v>
+        <v>188</v>
       </c>
       <c r="P55" s="10" t="s">
-        <v>189</v>
+        <v>191</v>
       </c>
       <c r="Q55" s="10"/>
       <c r="R55" s="10"/>
@@ -4863,7 +4873,7 @@
     </row>
     <row r="56" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A56" s="4" t="s">
-        <v>190</v>
+        <v>192</v>
       </c>
       <c r="B56" s="5">
         <v>46239.57430761574</v>
@@ -4873,16 +4883,16 @@
         <v>46240.58710263889</v>
       </c>
       <c r="E56" s="6" t="s">
-        <v>186</v>
+        <v>188</v>
       </c>
       <c r="F56" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G56" s="6" t="s">
-        <v>182</v>
+        <v>184</v>
       </c>
       <c r="H56" s="6" t="s">
-        <v>183</v>
+        <v>185</v>
       </c>
       <c r="I56" s="5">
         <v>46405</v>
@@ -4900,13 +4910,13 @@
         <v>26</v>
       </c>
       <c r="N56" s="6" t="s">
-        <v>181</v>
+        <v>183</v>
       </c>
       <c r="O56" s="6" t="s">
-        <v>186</v>
+        <v>188</v>
       </c>
       <c r="P56" s="6" t="s">
-        <v>187</v>
+        <v>189</v>
       </c>
       <c r="Q56" s="6"/>
       <c r="R56" s="6"/>
@@ -4916,7 +4926,7 @@
     </row>
     <row r="57" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A57" s="8" t="s">
-        <v>191</v>
+        <v>193</v>
       </c>
       <c r="B57" s="9">
         <v>46239.66388140046</v>
@@ -4926,16 +4936,16 @@
         <v>46240.587098715274</v>
       </c>
       <c r="E57" s="10" t="s">
-        <v>186</v>
+        <v>188</v>
       </c>
       <c r="F57" s="10" t="s">
         <v>26</v>
       </c>
       <c r="G57" s="10" t="s">
-        <v>182</v>
+        <v>184</v>
       </c>
       <c r="H57" s="10" t="s">
-        <v>183</v>
+        <v>185</v>
       </c>
       <c r="I57" s="9">
         <v>46405</v>
@@ -4953,10 +4963,10 @@
         <v>26</v>
       </c>
       <c r="N57" s="10" t="s">
-        <v>181</v>
+        <v>183</v>
       </c>
       <c r="O57" s="10" t="s">
-        <v>192</v>
+        <v>194</v>
       </c>
       <c r="P57" s="10" t="s">
         <v>26</v>
@@ -4969,7 +4979,7 @@
     </row>
     <row r="58" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A58" s="4" t="s">
-        <v>193</v>
+        <v>195</v>
       </c>
       <c r="B58" s="5">
         <v>46239.57431149305</v>
@@ -4979,7 +4989,7 @@
         <v>46239.7159622801</v>
       </c>
       <c r="E58" s="6" t="s">
-        <v>194</v>
+        <v>196</v>
       </c>
       <c r="F58" s="6" t="s">
         <v>25</v>
@@ -5003,7 +5013,7 @@
         <v>26</v>
       </c>
       <c r="O58" s="6" t="s">
-        <v>195</v>
+        <v>197</v>
       </c>
       <c r="P58" s="6" t="s">
         <v>26</v>
@@ -5016,7 +5026,7 @@
     </row>
     <row r="59" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A59" s="8" t="s">
-        <v>196</v>
+        <v>198</v>
       </c>
       <c r="B59" s="9">
         <v>46239.57431462963</v>
@@ -5026,16 +5036,16 @@
         <v>46240.587207523145</v>
       </c>
       <c r="E59" s="10" t="s">
-        <v>197</v>
+        <v>199</v>
       </c>
       <c r="F59" s="10" t="s">
         <v>26</v>
       </c>
       <c r="G59" s="10" t="s">
-        <v>198</v>
+        <v>200</v>
       </c>
       <c r="H59" s="10" t="s">
-        <v>199</v>
+        <v>201</v>
       </c>
       <c r="I59" s="9">
         <v>46332</v>
@@ -5053,13 +5063,13 @@
         <v>26</v>
       </c>
       <c r="N59" s="10" t="s">
-        <v>194</v>
+        <v>196</v>
       </c>
       <c r="O59" s="10" t="s">
         <v>112</v>
       </c>
       <c r="P59" s="10" t="s">
-        <v>200</v>
+        <v>202</v>
       </c>
       <c r="Q59" s="9">
         <v>46335</v>
@@ -5079,7 +5089,7 @@
     </row>
     <row r="60" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A60" s="4" t="s">
-        <v>201</v>
+        <v>203</v>
       </c>
       <c r="B60" s="5">
         <v>46239.57431895833</v>
@@ -5089,16 +5099,16 @@
         <v>46240.587203958334</v>
       </c>
       <c r="E60" s="6" t="s">
-        <v>202</v>
+        <v>204</v>
       </c>
       <c r="F60" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G60" s="6" t="s">
-        <v>198</v>
+        <v>200</v>
       </c>
       <c r="H60" s="6" t="s">
-        <v>199</v>
+        <v>201</v>
       </c>
       <c r="I60" s="5">
         <v>46332</v>
@@ -5116,13 +5126,13 @@
         <v>26</v>
       </c>
       <c r="N60" s="6" t="s">
-        <v>194</v>
+        <v>196</v>
       </c>
       <c r="O60" s="6" t="s">
         <v>120</v>
       </c>
       <c r="P60" s="6" t="s">
-        <v>203</v>
+        <v>205</v>
       </c>
       <c r="Q60" s="5">
         <v>46335</v>
@@ -5142,7 +5152,7 @@
     </row>
     <row r="61" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A61" s="8" t="s">
-        <v>204</v>
+        <v>206</v>
       </c>
       <c r="B61" s="9">
         <v>46239.57432314815</v>
@@ -5152,16 +5162,16 @@
         <v>46240.587200486116</v>
       </c>
       <c r="E61" s="10" t="s">
-        <v>205</v>
+        <v>207</v>
       </c>
       <c r="F61" s="10" t="s">
         <v>26</v>
       </c>
       <c r="G61" s="10" t="s">
-        <v>198</v>
+        <v>200</v>
       </c>
       <c r="H61" s="10" t="s">
-        <v>199</v>
+        <v>201</v>
       </c>
       <c r="I61" s="9">
         <v>46332</v>
@@ -5179,13 +5189,13 @@
         <v>26</v>
       </c>
       <c r="N61" s="10" t="s">
-        <v>194</v>
+        <v>196</v>
       </c>
       <c r="O61" s="10" t="s">
         <v>128</v>
       </c>
       <c r="P61" s="10" t="s">
-        <v>206</v>
+        <v>208</v>
       </c>
       <c r="Q61" s="9">
         <v>46335</v>
@@ -5205,7 +5215,7 @@
     </row>
     <row r="62" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A62" s="4" t="s">
-        <v>207</v>
+        <v>209</v>
       </c>
       <c r="B62" s="5">
         <v>46239.57432760416</v>
@@ -5215,7 +5225,7 @@
         <v>46240.58727070602</v>
       </c>
       <c r="E62" s="6" t="s">
-        <v>208</v>
+        <v>210</v>
       </c>
       <c r="F62" s="6" t="s">
         <v>26</v>
@@ -5242,13 +5252,13 @@
         <v>26</v>
       </c>
       <c r="N62" s="6" t="s">
-        <v>194</v>
+        <v>196</v>
       </c>
       <c r="O62" s="6" t="s">
-        <v>197</v>
+        <v>199</v>
       </c>
       <c r="P62" s="6" t="s">
-        <v>209</v>
+        <v>211</v>
       </c>
       <c r="Q62" s="5">
         <v>46337</v>
@@ -5268,7 +5278,7 @@
     </row>
     <row r="63" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A63" s="8" t="s">
-        <v>210</v>
+        <v>212</v>
       </c>
       <c r="B63" s="9">
         <v>46239.574331689815</v>
@@ -5278,7 +5288,7 @@
         <v>46240.58726702546</v>
       </c>
       <c r="E63" s="10" t="s">
-        <v>211</v>
+        <v>213</v>
       </c>
       <c r="F63" s="10" t="s">
         <v>26</v>
@@ -5305,13 +5315,13 @@
         <v>26</v>
       </c>
       <c r="N63" s="10" t="s">
-        <v>194</v>
+        <v>196</v>
       </c>
       <c r="O63" s="10" t="s">
-        <v>202</v>
+        <v>204</v>
       </c>
       <c r="P63" s="10" t="s">
-        <v>209</v>
+        <v>211</v>
       </c>
       <c r="Q63" s="9">
         <v>46337</v>
@@ -5331,7 +5341,7 @@
     </row>
     <row r="64" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A64" s="4" t="s">
-        <v>212</v>
+        <v>214</v>
       </c>
       <c r="B64" s="5">
         <v>46239.57433570602</v>
@@ -5341,7 +5351,7 @@
         <v>46240.58726326389</v>
       </c>
       <c r="E64" s="6" t="s">
-        <v>213</v>
+        <v>215</v>
       </c>
       <c r="F64" s="6" t="s">
         <v>26</v>
@@ -5368,13 +5378,13 @@
         <v>26</v>
       </c>
       <c r="N64" s="6" t="s">
-        <v>194</v>
+        <v>196</v>
       </c>
       <c r="O64" s="6" t="s">
-        <v>205</v>
+        <v>207</v>
       </c>
       <c r="P64" s="6" t="s">
-        <v>214</v>
+        <v>216</v>
       </c>
       <c r="Q64" s="5">
         <v>46337</v>
@@ -5394,7 +5404,7 @@
     </row>
     <row r="65" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A65" s="8" t="s">
-        <v>215</v>
+        <v>217</v>
       </c>
       <c r="B65" s="9">
         <v>46239.574339363426</v>
@@ -5404,7 +5414,7 @@
         <v>46240.57123085648</v>
       </c>
       <c r="E65" s="10" t="s">
-        <v>216</v>
+        <v>218</v>
       </c>
       <c r="F65" s="10" t="s">
         <v>25</v>
@@ -5428,7 +5438,7 @@
         <v>26</v>
       </c>
       <c r="O65" s="10" t="s">
-        <v>217</v>
+        <v>219</v>
       </c>
       <c r="P65" s="10" t="s">
         <v>26</v>
@@ -5441,7 +5451,7 @@
     </row>
     <row r="66" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A66" s="4" t="s">
-        <v>218</v>
+        <v>220</v>
       </c>
       <c r="B66" s="5">
         <v>46239.57434170139</v>
@@ -5451,16 +5461,16 @@
         <v>46240.59315164352</v>
       </c>
       <c r="E66" s="6" t="s">
-        <v>219</v>
+        <v>221</v>
       </c>
       <c r="F66" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G66" s="6" t="s">
-        <v>220</v>
+        <v>222</v>
       </c>
       <c r="H66" s="6" t="s">
-        <v>221</v>
+        <v>223</v>
       </c>
       <c r="I66" s="5">
         <v>46338</v>
@@ -5478,13 +5488,13 @@
         <v>26</v>
       </c>
       <c r="N66" s="6" t="s">
-        <v>216</v>
+        <v>218</v>
       </c>
       <c r="O66" s="6" t="s">
         <v>91</v>
       </c>
       <c r="P66" s="6" t="s">
-        <v>222</v>
+        <v>224</v>
       </c>
       <c r="Q66" s="5">
         <v>46346</v>
@@ -5504,7 +5514,7 @@
     </row>
     <row r="67" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A67" s="8" t="s">
-        <v>223</v>
+        <v>225</v>
       </c>
       <c r="B67" s="9">
         <v>46239.574346504625</v>
@@ -5514,16 +5524,16 @@
         <v>46240.593254861116</v>
       </c>
       <c r="E67" s="10" t="s">
-        <v>224</v>
+        <v>226</v>
       </c>
       <c r="F67" s="10" t="s">
         <v>26</v>
       </c>
       <c r="G67" s="10" t="s">
-        <v>220</v>
+        <v>222</v>
       </c>
       <c r="H67" s="10" t="s">
-        <v>221</v>
+        <v>223</v>
       </c>
       <c r="I67" s="9">
         <v>46349</v>
@@ -5541,13 +5551,13 @@
         <v>26</v>
       </c>
       <c r="N67" s="10" t="s">
-        <v>216</v>
+        <v>218</v>
       </c>
       <c r="O67" s="10" t="s">
-        <v>184</v>
+        <v>186</v>
       </c>
       <c r="P67" s="10" t="s">
-        <v>216</v>
+        <v>218</v>
       </c>
       <c r="Q67" s="9">
         <v>46367</v>
@@ -5567,7 +5577,7 @@
     </row>
     <row r="68" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A68" s="4" t="s">
-        <v>225</v>
+        <v>227</v>
       </c>
       <c r="B68" s="5">
         <v>46239.57435601852</v>
@@ -5577,16 +5587,16 @@
         <v>46240.58742517361</v>
       </c>
       <c r="E68" s="6" t="s">
-        <v>186</v>
+        <v>188</v>
       </c>
       <c r="F68" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G68" s="6" t="s">
-        <v>220</v>
+        <v>222</v>
       </c>
       <c r="H68" s="6" t="s">
-        <v>221</v>
+        <v>223</v>
       </c>
       <c r="I68" s="5">
         <v>46349</v>
@@ -5604,13 +5614,13 @@
         <v>26</v>
       </c>
       <c r="N68" s="6" t="s">
-        <v>224</v>
+        <v>226</v>
       </c>
       <c r="O68" s="6" t="s">
-        <v>226</v>
+        <v>228</v>
       </c>
       <c r="P68" s="6" t="s">
-        <v>227</v>
+        <v>229</v>
       </c>
       <c r="Q68" s="6"/>
       <c r="R68" s="6"/>
@@ -5620,7 +5630,7 @@
     </row>
     <row r="69" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A69" s="8" t="s">
-        <v>228</v>
+        <v>230</v>
       </c>
       <c r="B69" s="9">
         <v>46239.574361817125</v>
@@ -5630,16 +5640,16 @@
         <v>46240.58742163195</v>
       </c>
       <c r="E69" s="10" t="s">
-        <v>186</v>
+        <v>188</v>
       </c>
       <c r="F69" s="10" t="s">
         <v>26</v>
       </c>
       <c r="G69" s="10" t="s">
-        <v>220</v>
+        <v>222</v>
       </c>
       <c r="H69" s="10" t="s">
-        <v>221</v>
+        <v>223</v>
       </c>
       <c r="I69" s="9">
         <v>46349</v>
@@ -5657,13 +5667,13 @@
         <v>26</v>
       </c>
       <c r="N69" s="10" t="s">
-        <v>224</v>
+        <v>226</v>
       </c>
       <c r="O69" s="10" t="s">
+        <v>231</v>
+      </c>
+      <c r="P69" s="10" t="s">
         <v>229</v>
-      </c>
-      <c r="P69" s="10" t="s">
-        <v>227</v>
       </c>
       <c r="Q69" s="10"/>
       <c r="R69" s="10"/>
@@ -5673,7 +5683,7 @@
     </row>
     <row r="70" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A70" s="4" t="s">
-        <v>230</v>
+        <v>232</v>
       </c>
       <c r="B70" s="5">
         <v>46239.574366967594</v>
@@ -5683,16 +5693,16 @@
         <v>46240.58741825231</v>
       </c>
       <c r="E70" s="6" t="s">
-        <v>186</v>
+        <v>188</v>
       </c>
       <c r="F70" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G70" s="6" t="s">
-        <v>220</v>
+        <v>222</v>
       </c>
       <c r="H70" s="6" t="s">
-        <v>221</v>
+        <v>223</v>
       </c>
       <c r="I70" s="5">
         <v>46349</v>
@@ -5710,13 +5720,13 @@
         <v>26</v>
       </c>
       <c r="N70" s="6" t="s">
-        <v>224</v>
+        <v>226</v>
       </c>
       <c r="O70" s="6" t="s">
-        <v>231</v>
+        <v>233</v>
       </c>
       <c r="P70" s="6" t="s">
-        <v>232</v>
+        <v>234</v>
       </c>
       <c r="Q70" s="6"/>
       <c r="R70" s="6"/>
@@ -5726,7 +5736,7 @@
     </row>
     <row r="71" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A71" s="8" t="s">
-        <v>233</v>
+        <v>235</v>
       </c>
       <c r="B71" s="9">
         <v>46239.65279153935</v>
@@ -5736,16 +5746,16 @@
         <v>46240.58741491898</v>
       </c>
       <c r="E71" s="10" t="s">
-        <v>186</v>
+        <v>188</v>
       </c>
       <c r="F71" s="10" t="s">
         <v>26</v>
       </c>
       <c r="G71" s="10" t="s">
-        <v>220</v>
+        <v>222</v>
       </c>
       <c r="H71" s="10" t="s">
-        <v>221</v>
+        <v>223</v>
       </c>
       <c r="I71" s="9">
         <v>46349</v>
@@ -5763,13 +5773,13 @@
         <v>26</v>
       </c>
       <c r="N71" s="10" t="s">
-        <v>224</v>
+        <v>226</v>
       </c>
       <c r="O71" s="10" t="s">
-        <v>219</v>
+        <v>221</v>
       </c>
       <c r="P71" s="10" t="s">
-        <v>186</v>
+        <v>188</v>
       </c>
       <c r="Q71" s="10"/>
       <c r="R71" s="10"/>
@@ -5779,7 +5789,7 @@
     </row>
     <row r="72" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A72" s="4" t="s">
-        <v>234</v>
+        <v>236</v>
       </c>
       <c r="B72" s="5">
         <v>46239.57437221065</v>
@@ -5789,7 +5799,7 @@
         <v>46240.59335420139</v>
       </c>
       <c r="E72" s="6" t="s">
-        <v>235</v>
+        <v>237</v>
       </c>
       <c r="F72" s="6" t="s">
         <v>26</v>
@@ -5816,13 +5826,13 @@
         <v>26</v>
       </c>
       <c r="N72" s="6" t="s">
-        <v>216</v>
+        <v>218</v>
       </c>
       <c r="O72" s="6" t="s">
-        <v>184</v>
+        <v>186</v>
       </c>
       <c r="P72" s="6" t="s">
-        <v>216</v>
+        <v>218</v>
       </c>
       <c r="Q72" s="5">
         <v>46370</v>
@@ -5842,7 +5852,7 @@
     </row>
     <row r="73" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A73" s="8" t="s">
-        <v>236</v>
+        <v>238</v>
       </c>
       <c r="B73" s="9">
         <v>46239.574375833334</v>
@@ -5852,7 +5862,7 @@
         <v>46240.587564953705</v>
       </c>
       <c r="E73" s="10" t="s">
-        <v>186</v>
+        <v>188</v>
       </c>
       <c r="F73" s="10" t="s">
         <v>26</v>
@@ -5879,13 +5889,13 @@
         <v>26</v>
       </c>
       <c r="N73" s="10" t="s">
-        <v>235</v>
+        <v>237</v>
       </c>
       <c r="O73" s="10" t="s">
-        <v>237</v>
+        <v>239</v>
       </c>
       <c r="P73" s="10" t="s">
-        <v>238</v>
+        <v>240</v>
       </c>
       <c r="Q73" s="10"/>
       <c r="R73" s="10"/>
@@ -5895,7 +5905,7 @@
     </row>
     <row r="74" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A74" s="4" t="s">
-        <v>239</v>
+        <v>241</v>
       </c>
       <c r="B74" s="5">
         <v>46239.57437981482</v>
@@ -5905,7 +5915,7 @@
         <v>46240.587560659726</v>
       </c>
       <c r="E74" s="6" t="s">
-        <v>186</v>
+        <v>188</v>
       </c>
       <c r="F74" s="6" t="s">
         <v>26</v>
@@ -5932,13 +5942,13 @@
         <v>26</v>
       </c>
       <c r="N74" s="6" t="s">
-        <v>235</v>
+        <v>237</v>
       </c>
       <c r="O74" s="6" t="s">
-        <v>237</v>
+        <v>239</v>
       </c>
       <c r="P74" s="6" t="s">
-        <v>240</v>
+        <v>242</v>
       </c>
       <c r="Q74" s="6"/>
       <c r="R74" s="6"/>
@@ -5948,7 +5958,7 @@
     </row>
     <row r="75" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A75" s="8" t="s">
-        <v>241</v>
+        <v>243</v>
       </c>
       <c r="B75" s="9">
         <v>46239.574383750005</v>
@@ -5958,7 +5968,7 @@
         <v>46240.587557210645</v>
       </c>
       <c r="E75" s="10" t="s">
-        <v>186</v>
+        <v>188</v>
       </c>
       <c r="F75" s="10" t="s">
         <v>26</v>
@@ -5985,13 +5995,13 @@
         <v>26</v>
       </c>
       <c r="N75" s="10" t="s">
-        <v>235</v>
+        <v>237</v>
       </c>
       <c r="O75" s="10" t="s">
+        <v>244</v>
+      </c>
+      <c r="P75" s="10" t="s">
         <v>242</v>
-      </c>
-      <c r="P75" s="10" t="s">
-        <v>240</v>
       </c>
       <c r="Q75" s="10"/>
       <c r="R75" s="10"/>
@@ -6001,7 +6011,7 @@
     </row>
     <row r="76" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A76" s="4" t="s">
-        <v>243</v>
+        <v>245</v>
       </c>
       <c r="B76" s="5">
         <v>46239.65287751157</v>
@@ -6011,7 +6021,7 @@
         <v>46240.5875534838</v>
       </c>
       <c r="E76" s="6" t="s">
-        <v>186</v>
+        <v>188</v>
       </c>
       <c r="F76" s="6" t="s">
         <v>26</v>
@@ -6038,13 +6048,13 @@
         <v>26</v>
       </c>
       <c r="N76" s="6" t="s">
-        <v>235</v>
+        <v>237</v>
       </c>
       <c r="O76" s="6" t="s">
-        <v>186</v>
+        <v>188</v>
       </c>
       <c r="P76" s="6" t="s">
-        <v>186</v>
+        <v>188</v>
       </c>
       <c r="Q76" s="6"/>
       <c r="R76" s="6"/>
@@ -6054,7 +6064,7 @@
     </row>
     <row r="77" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A77" s="8" t="s">
-        <v>244</v>
+        <v>246</v>
       </c>
       <c r="B77" s="9">
         <v>46239.574387534725</v>
@@ -6064,7 +6074,7 @@
         <v>46240.57208707176</v>
       </c>
       <c r="E77" s="10" t="s">
-        <v>245</v>
+        <v>247</v>
       </c>
       <c r="F77" s="10" t="s">
         <v>25</v>
@@ -6088,7 +6098,7 @@
         <v>26</v>
       </c>
       <c r="O77" s="10" t="s">
-        <v>246</v>
+        <v>248</v>
       </c>
       <c r="P77" s="10" t="s">
         <v>26</v>
@@ -6101,7 +6111,7 @@
     </row>
     <row r="78" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A78" s="4" t="s">
-        <v>247</v>
+        <v>249</v>
       </c>
       <c r="B78" s="5">
         <v>46239.57438989583</v>
@@ -6111,16 +6121,16 @@
         <v>46247.20311761574</v>
       </c>
       <c r="E78" s="6" t="s">
-        <v>248</v>
+        <v>250</v>
       </c>
       <c r="F78" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G78" s="6" t="s">
-        <v>198</v>
+        <v>200</v>
       </c>
       <c r="H78" s="6" t="s">
-        <v>199</v>
+        <v>201</v>
       </c>
       <c r="I78" s="5">
         <v>46245</v>
@@ -6138,13 +6148,13 @@
         <v>26</v>
       </c>
       <c r="N78" s="6" t="s">
-        <v>245</v>
+        <v>247</v>
       </c>
       <c r="O78" s="6" t="s">
         <v>74</v>
       </c>
       <c r="P78" s="6" t="s">
-        <v>249</v>
+        <v>251</v>
       </c>
       <c r="Q78" s="5">
         <v>46246</v>
@@ -6164,7 +6174,7 @@
     </row>
     <row r="79" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A79" s="8" t="s">
-        <v>250</v>
+        <v>252</v>
       </c>
       <c r="B79" s="9">
         <v>46239.57439460648</v>
@@ -6174,16 +6184,16 @@
         <v>46247.2031178125</v>
       </c>
       <c r="E79" s="10" t="s">
-        <v>251</v>
+        <v>253</v>
       </c>
       <c r="F79" s="10" t="s">
         <v>26</v>
       </c>
       <c r="G79" s="10" t="s">
-        <v>198</v>
+        <v>200</v>
       </c>
       <c r="H79" s="10" t="s">
-        <v>199</v>
+        <v>201</v>
       </c>
       <c r="I79" s="9">
         <v>46245</v>
@@ -6201,13 +6211,13 @@
         <v>26</v>
       </c>
       <c r="N79" s="10" t="s">
-        <v>245</v>
+        <v>247</v>
       </c>
       <c r="O79" s="10" t="s">
         <v>79</v>
       </c>
       <c r="P79" s="10" t="s">
-        <v>249</v>
+        <v>251</v>
       </c>
       <c r="Q79" s="9">
         <v>46246</v>
@@ -6227,7 +6237,7 @@
     </row>
     <row r="80" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A80" s="4" t="s">
-        <v>252</v>
+        <v>254</v>
       </c>
       <c r="B80" s="5">
         <v>46239.5743990162</v>
@@ -6237,16 +6247,16 @@
         <v>46240.58768672454</v>
       </c>
       <c r="E80" s="6" t="s">
-        <v>253</v>
+        <v>255</v>
       </c>
       <c r="F80" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G80" s="6" t="s">
-        <v>198</v>
+        <v>200</v>
       </c>
       <c r="H80" s="6" t="s">
-        <v>199</v>
+        <v>201</v>
       </c>
       <c r="I80" s="5">
         <v>46372</v>
@@ -6264,13 +6274,13 @@
         <v>26</v>
       </c>
       <c r="N80" s="6" t="s">
-        <v>245</v>
+        <v>247</v>
       </c>
       <c r="O80" s="6" t="s">
         <v>153</v>
       </c>
       <c r="P80" s="6" t="s">
-        <v>254</v>
+        <v>256</v>
       </c>
       <c r="Q80" s="5">
         <v>46372</v>
@@ -6290,7 +6300,7 @@
     </row>
     <row r="81" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A81" s="8" t="s">
-        <v>255</v>
+        <v>257</v>
       </c>
       <c r="B81" s="9">
         <v>46239.59988357639</v>
@@ -6306,10 +6316,10 @@
         <v>26</v>
       </c>
       <c r="G81" s="10" t="s">
-        <v>198</v>
+        <v>200</v>
       </c>
       <c r="H81" s="10" t="s">
-        <v>199</v>
+        <v>201</v>
       </c>
       <c r="I81" s="9">
         <v>46302</v>
@@ -6327,7 +6337,7 @@
         <v>26</v>
       </c>
       <c r="N81" s="10" t="s">
-        <v>245</v>
+        <v>247</v>
       </c>
       <c r="O81" s="10" t="s">
         <v>164</v>
@@ -6353,7 +6363,7 @@
     </row>
     <row r="82" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A82" s="4" t="s">
-        <v>256</v>
+        <v>258</v>
       </c>
       <c r="B82" s="5">
         <v>46239.574403680555</v>
@@ -6363,7 +6373,7 @@
         <v>46240.58015300926</v>
       </c>
       <c r="E82" s="6" t="s">
-        <v>257</v>
+        <v>259</v>
       </c>
       <c r="F82" s="6" t="s">
         <v>25</v>
@@ -6387,7 +6397,7 @@
         <v>26</v>
       </c>
       <c r="O82" s="6" t="s">
-        <v>258</v>
+        <v>260</v>
       </c>
       <c r="P82" s="6" t="s">
         <v>26</v>
@@ -6400,7 +6410,7 @@
     </row>
     <row r="83" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A83" s="8" t="s">
-        <v>259</v>
+        <v>261</v>
       </c>
       <c r="B83" s="9">
         <v>46239.57440625</v>
@@ -6410,7 +6420,7 @@
         <v>46240.593524502314</v>
       </c>
       <c r="E83" s="10" t="s">
-        <v>260</v>
+        <v>262</v>
       </c>
       <c r="F83" s="10" t="s">
         <v>26</v>
@@ -6437,13 +6447,13 @@
         <v>26</v>
       </c>
       <c r="N83" s="10" t="s">
-        <v>257</v>
+        <v>259</v>
       </c>
       <c r="O83" s="10" t="s">
-        <v>184</v>
+        <v>186</v>
       </c>
       <c r="P83" s="10" t="s">
-        <v>257</v>
+        <v>259</v>
       </c>
       <c r="Q83" s="9">
         <v>46392</v>
@@ -6463,7 +6473,7 @@
     </row>
     <row r="84" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A84" s="4" t="s">
-        <v>261</v>
+        <v>263</v>
       </c>
       <c r="B84" s="5">
         <v>46239.57441001157</v>
@@ -6473,7 +6483,7 @@
         <v>46240.58779871528</v>
       </c>
       <c r="E84" s="6" t="s">
-        <v>186</v>
+        <v>188</v>
       </c>
       <c r="F84" s="6" t="s">
         <v>26</v>
@@ -6500,13 +6510,13 @@
         <v>26</v>
       </c>
       <c r="N84" s="6" t="s">
-        <v>260</v>
+        <v>262</v>
       </c>
       <c r="O84" s="6" t="s">
-        <v>186</v>
+        <v>188</v>
       </c>
       <c r="P84" s="6" t="s">
-        <v>262</v>
+        <v>264</v>
       </c>
       <c r="Q84" s="6"/>
       <c r="R84" s="6"/>
@@ -6516,7 +6526,7 @@
     </row>
     <row r="85" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A85" s="8" t="s">
-        <v>263</v>
+        <v>265</v>
       </c>
       <c r="B85" s="9">
         <v>46239.57441357639</v>
@@ -6526,7 +6536,7 @@
         <v>46240.58779524306</v>
       </c>
       <c r="E85" s="10" t="s">
-        <v>186</v>
+        <v>188</v>
       </c>
       <c r="F85" s="10" t="s">
         <v>26</v>
@@ -6553,13 +6563,13 @@
         <v>26</v>
       </c>
       <c r="N85" s="10" t="s">
-        <v>260</v>
+        <v>262</v>
       </c>
       <c r="O85" s="10" t="s">
-        <v>186</v>
+        <v>188</v>
       </c>
       <c r="P85" s="10" t="s">
-        <v>262</v>
+        <v>264</v>
       </c>
       <c r="Q85" s="10"/>
       <c r="R85" s="10"/>
@@ -6569,7 +6579,7 @@
     </row>
     <row r="86" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A86" s="4" t="s">
-        <v>264</v>
+        <v>266</v>
       </c>
       <c r="B86" s="5">
         <v>46239.57441700231</v>
@@ -6579,7 +6589,7 @@
         <v>46240.58779197917</v>
       </c>
       <c r="E86" s="6" t="s">
-        <v>186</v>
+        <v>188</v>
       </c>
       <c r="F86" s="6" t="s">
         <v>26</v>
@@ -6606,13 +6616,13 @@
         <v>26</v>
       </c>
       <c r="N86" s="6" t="s">
-        <v>260</v>
+        <v>262</v>
       </c>
       <c r="O86" s="6" t="s">
-        <v>186</v>
+        <v>188</v>
       </c>
       <c r="P86" s="6" t="s">
-        <v>265</v>
+        <v>267</v>
       </c>
       <c r="Q86" s="6"/>
       <c r="R86" s="6"/>
@@ -6622,7 +6632,7 @@
     </row>
     <row r="87" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A87" s="8" t="s">
-        <v>266</v>
+        <v>268</v>
       </c>
       <c r="B87" s="9">
         <v>46239.65295363426</v>
@@ -6632,7 +6642,7 @@
         <v>46240.58778819445</v>
       </c>
       <c r="E87" s="10" t="s">
-        <v>186</v>
+        <v>188</v>
       </c>
       <c r="F87" s="10" t="s">
         <v>26</v>
@@ -6659,13 +6669,13 @@
         <v>26</v>
       </c>
       <c r="N87" s="10" t="s">
-        <v>260</v>
+        <v>262</v>
       </c>
       <c r="O87" s="10" t="s">
-        <v>186</v>
+        <v>188</v>
       </c>
       <c r="P87" s="10" t="s">
-        <v>186</v>
+        <v>188</v>
       </c>
       <c r="Q87" s="10"/>
       <c r="R87" s="10"/>
@@ -6675,7 +6685,7 @@
     </row>
     <row r="88" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A88" s="4" t="s">
-        <v>267</v>
+        <v>269</v>
       </c>
       <c r="B88" s="5">
         <v>46239.5744203125</v>
@@ -6685,7 +6695,7 @@
         <v>46240.59358774306</v>
       </c>
       <c r="E88" s="6" t="s">
-        <v>268</v>
+        <v>270</v>
       </c>
       <c r="F88" s="6" t="s">
         <v>26</v>
@@ -6712,10 +6722,10 @@
         <v>26</v>
       </c>
       <c r="N88" s="6" t="s">
-        <v>257</v>
+        <v>259</v>
       </c>
       <c r="O88" s="6" t="s">
-        <v>184</v>
+        <v>186</v>
       </c>
       <c r="P88" s="6" t="s">
         <v>26</v>
@@ -6738,7 +6748,7 @@
     </row>
     <row r="89" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A89" s="8" t="s">
-        <v>269</v>
+        <v>271</v>
       </c>
       <c r="B89" s="9">
         <v>46239.57442366898</v>
@@ -6748,7 +6758,7 @@
         <v>46240.5880146875</v>
       </c>
       <c r="E89" s="10" t="s">
-        <v>186</v>
+        <v>188</v>
       </c>
       <c r="F89" s="10" t="s">
         <v>26</v>
@@ -6775,13 +6785,13 @@
         <v>26</v>
       </c>
       <c r="N89" s="10" t="s">
-        <v>268</v>
+        <v>270</v>
       </c>
       <c r="O89" s="10" t="s">
-        <v>270</v>
+        <v>272</v>
       </c>
       <c r="P89" s="10" t="s">
-        <v>271</v>
+        <v>273</v>
       </c>
       <c r="Q89" s="10"/>
       <c r="R89" s="10"/>
@@ -6791,7 +6801,7 @@
     </row>
     <row r="90" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A90" s="4" t="s">
-        <v>272</v>
+        <v>274</v>
       </c>
       <c r="B90" s="5">
         <v>46239.57442798611</v>
@@ -6801,7 +6811,7 @@
         <v>46240.58801127315</v>
       </c>
       <c r="E90" s="6" t="s">
-        <v>186</v>
+        <v>188</v>
       </c>
       <c r="F90" s="6" t="s">
         <v>26</v>
@@ -6828,13 +6838,13 @@
         <v>26</v>
       </c>
       <c r="N90" s="6" t="s">
-        <v>268</v>
+        <v>270</v>
       </c>
       <c r="O90" s="6" t="s">
+        <v>275</v>
+      </c>
+      <c r="P90" s="6" t="s">
         <v>273</v>
-      </c>
-      <c r="P90" s="6" t="s">
-        <v>271</v>
       </c>
       <c r="Q90" s="6"/>
       <c r="R90" s="6"/>
@@ -6844,7 +6854,7 @@
     </row>
     <row r="91" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A91" s="8" t="s">
-        <v>274</v>
+        <v>276</v>
       </c>
       <c r="B91" s="9">
         <v>46239.57443190972</v>
@@ -6854,7 +6864,7 @@
         <v>46240.58800769676</v>
       </c>
       <c r="E91" s="10" t="s">
-        <v>186</v>
+        <v>188</v>
       </c>
       <c r="F91" s="10" t="s">
         <v>26</v>
@@ -6881,13 +6891,13 @@
         <v>26</v>
       </c>
       <c r="N91" s="10" t="s">
-        <v>268</v>
+        <v>270</v>
       </c>
       <c r="O91" s="10" t="s">
+        <v>275</v>
+      </c>
+      <c r="P91" s="10" t="s">
         <v>273</v>
-      </c>
-      <c r="P91" s="10" t="s">
-        <v>271</v>
       </c>
       <c r="Q91" s="10"/>
       <c r="R91" s="10"/>
@@ -6897,7 +6907,7 @@
     </row>
     <row r="92" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A92" s="4" t="s">
-        <v>275</v>
+        <v>277</v>
       </c>
       <c r="B92" s="5">
         <v>46239.653021875</v>
@@ -6907,7 +6917,7 @@
         <v>46240.588004212965</v>
       </c>
       <c r="E92" s="6" t="s">
-        <v>192</v>
+        <v>194</v>
       </c>
       <c r="F92" s="6" t="s">
         <v>26</v>
@@ -6934,13 +6944,13 @@
         <v>26</v>
       </c>
       <c r="N92" s="6" t="s">
-        <v>268</v>
+        <v>270</v>
       </c>
       <c r="O92" s="6" t="s">
-        <v>273</v>
+        <v>275</v>
       </c>
       <c r="P92" s="6" t="s">
-        <v>276</v>
+        <v>278</v>
       </c>
       <c r="Q92" s="6"/>
       <c r="R92" s="6"/>
@@ -6950,7 +6960,7 @@
     </row>
     <row r="93" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A93" s="8" t="s">
-        <v>277</v>
+        <v>279</v>
       </c>
       <c r="B93" s="9">
         <v>46239.57443621528</v>
@@ -6960,7 +6970,7 @@
         <v>46246.17023978009</v>
       </c>
       <c r="E93" s="10" t="s">
-        <v>278</v>
+        <v>280</v>
       </c>
       <c r="F93" s="10" t="s">
         <v>26</v>
@@ -6987,13 +6997,13 @@
         <v>26</v>
       </c>
       <c r="N93" s="10" t="s">
-        <v>257</v>
+        <v>259</v>
       </c>
       <c r="O93" s="10" t="s">
-        <v>279</v>
+        <v>281</v>
       </c>
       <c r="P93" s="10" t="s">
-        <v>280</v>
+        <v>282</v>
       </c>
       <c r="Q93" s="9">
         <v>46245</v>
@@ -7013,7 +7023,7 @@
     </row>
     <row r="94" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A94" s="4" t="s">
-        <v>281</v>
+        <v>283</v>
       </c>
       <c r="B94" s="5">
         <v>46239.57444033565</v>
@@ -7023,7 +7033,7 @@
         <v>46240.58943795139</v>
       </c>
       <c r="E94" s="6" t="s">
-        <v>186</v>
+        <v>188</v>
       </c>
       <c r="F94" s="6" t="s">
         <v>26</v>
@@ -7050,13 +7060,13 @@
         <v>26</v>
       </c>
       <c r="N94" s="6" t="s">
-        <v>278</v>
+        <v>280</v>
       </c>
       <c r="O94" s="6" t="s">
-        <v>282</v>
+        <v>284</v>
       </c>
       <c r="P94" s="6" t="s">
-        <v>278</v>
+        <v>280</v>
       </c>
       <c r="Q94" s="6"/>
       <c r="R94" s="6"/>
@@ -7066,7 +7076,7 @@
     </row>
     <row r="95" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A95" s="8" t="s">
-        <v>283</v>
+        <v>285</v>
       </c>
       <c r="B95" s="9">
         <v>46239.57444496528</v>
@@ -7076,7 +7086,7 @@
         <v>46240.589434444446</v>
       </c>
       <c r="E95" s="10" t="s">
-        <v>186</v>
+        <v>188</v>
       </c>
       <c r="F95" s="10" t="s">
         <v>26</v>
@@ -7103,13 +7113,13 @@
         <v>26</v>
       </c>
       <c r="N95" s="10" t="s">
-        <v>278</v>
+        <v>280</v>
       </c>
       <c r="O95" s="10" t="s">
-        <v>282</v>
+        <v>284</v>
       </c>
       <c r="P95" s="10" t="s">
-        <v>284</v>
+        <v>286</v>
       </c>
       <c r="Q95" s="10"/>
       <c r="R95" s="10"/>
@@ -7119,7 +7129,7 @@
     </row>
     <row r="96" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A96" s="4" t="s">
-        <v>285</v>
+        <v>287</v>
       </c>
       <c r="B96" s="5">
         <v>46239.57445002315</v>
@@ -7129,7 +7139,7 @@
         <v>46240.58943064815</v>
       </c>
       <c r="E96" s="6" t="s">
-        <v>186</v>
+        <v>188</v>
       </c>
       <c r="F96" s="6" t="s">
         <v>26</v>
@@ -7156,13 +7166,13 @@
         <v>26</v>
       </c>
       <c r="N96" s="6" t="s">
-        <v>278</v>
+        <v>280</v>
       </c>
       <c r="O96" s="6" t="s">
+        <v>288</v>
+      </c>
+      <c r="P96" s="6" t="s">
         <v>286</v>
-      </c>
-      <c r="P96" s="6" t="s">
-        <v>284</v>
       </c>
       <c r="Q96" s="6"/>
       <c r="R96" s="6"/>
@@ -7172,7 +7182,7 @@
     </row>
     <row r="97" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A97" s="8" t="s">
-        <v>287</v>
+        <v>289</v>
       </c>
       <c r="B97" s="9">
         <v>46239.65309570602</v>
@@ -7182,7 +7192,7 @@
         <v>46240.58942697917</v>
       </c>
       <c r="E97" s="10" t="s">
-        <v>186</v>
+        <v>188</v>
       </c>
       <c r="F97" s="10" t="s">
         <v>26</v>
@@ -7209,10 +7219,10 @@
         <v>26</v>
       </c>
       <c r="N97" s="10" t="s">
-        <v>278</v>
+        <v>280</v>
       </c>
       <c r="O97" s="10" t="s">
-        <v>186</v>
+        <v>188</v>
       </c>
       <c r="P97" s="10" t="s">
         <v>26</v>
@@ -7225,7 +7235,7 @@
     </row>
     <row r="98" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A98" s="4" t="s">
-        <v>288</v>
+        <v>290</v>
       </c>
       <c r="B98" s="5">
         <v>46239.57450405092</v>
@@ -7235,7 +7245,7 @@
         <v>46240.59374053241</v>
       </c>
       <c r="E98" s="6" t="s">
-        <v>289</v>
+        <v>291</v>
       </c>
       <c r="F98" s="6" t="s">
         <v>26</v>
@@ -7262,13 +7272,13 @@
         <v>26</v>
       </c>
       <c r="N98" s="6" t="s">
-        <v>257</v>
+        <v>259</v>
       </c>
       <c r="O98" s="6" t="s">
-        <v>184</v>
+        <v>186</v>
       </c>
       <c r="P98" s="6" t="s">
-        <v>290</v>
+        <v>292</v>
       </c>
       <c r="Q98" s="5">
         <v>46400</v>
@@ -7288,7 +7298,7 @@
     </row>
     <row r="99" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A99" s="8" t="s">
-        <v>291</v>
+        <v>293</v>
       </c>
       <c r="B99" s="9">
         <v>46239.57451060185</v>
@@ -7298,7 +7308,7 @@
         <v>46240.58955791667</v>
       </c>
       <c r="E99" s="10" t="s">
-        <v>186</v>
+        <v>188</v>
       </c>
       <c r="F99" s="10" t="s">
         <v>26</v>
@@ -7325,13 +7335,13 @@
         <v>26</v>
       </c>
       <c r="N99" s="10" t="s">
-        <v>289</v>
+        <v>291</v>
       </c>
       <c r="O99" s="10" t="s">
-        <v>186</v>
+        <v>188</v>
       </c>
       <c r="P99" s="10" t="s">
-        <v>292</v>
+        <v>294</v>
       </c>
       <c r="Q99" s="10"/>
       <c r="R99" s="10"/>
@@ -7341,7 +7351,7 @@
     </row>
     <row r="100" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A100" s="4" t="s">
-        <v>293</v>
+        <v>295</v>
       </c>
       <c r="B100" s="5">
         <v>46239.57451451389</v>
@@ -7351,7 +7361,7 @@
         <v>46240.58955409723</v>
       </c>
       <c r="E100" s="6" t="s">
-        <v>186</v>
+        <v>188</v>
       </c>
       <c r="F100" s="6" t="s">
         <v>26</v>
@@ -7378,13 +7388,13 @@
         <v>26</v>
       </c>
       <c r="N100" s="6" t="s">
-        <v>289</v>
+        <v>291</v>
       </c>
       <c r="O100" s="6" t="s">
-        <v>186</v>
+        <v>188</v>
       </c>
       <c r="P100" s="6" t="s">
-        <v>294</v>
+        <v>296</v>
       </c>
       <c r="Q100" s="6"/>
       <c r="R100" s="6"/>
@@ -7394,7 +7404,7 @@
     </row>
     <row r="101" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A101" s="8" t="s">
-        <v>295</v>
+        <v>297</v>
       </c>
       <c r="B101" s="9">
         <v>46239.57451872685</v>
@@ -7404,7 +7414,7 @@
         <v>46240.589550289355</v>
       </c>
       <c r="E101" s="10" t="s">
-        <v>186</v>
+        <v>188</v>
       </c>
       <c r="F101" s="10" t="s">
         <v>26</v>
@@ -7431,13 +7441,13 @@
         <v>26</v>
       </c>
       <c r="N101" s="10" t="s">
-        <v>289</v>
+        <v>291</v>
       </c>
       <c r="O101" s="10" t="s">
-        <v>186</v>
+        <v>188</v>
       </c>
       <c r="P101" s="10" t="s">
-        <v>294</v>
+        <v>296</v>
       </c>
       <c r="Q101" s="10"/>
       <c r="R101" s="10"/>
@@ -7447,7 +7457,7 @@
     </row>
     <row r="102" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A102" s="4" t="s">
-        <v>296</v>
+        <v>298</v>
       </c>
       <c r="B102" s="5">
         <v>46239.65315884259</v>
@@ -7457,7 +7467,7 @@
         <v>46240.58954619213</v>
       </c>
       <c r="E102" s="6" t="s">
-        <v>186</v>
+        <v>188</v>
       </c>
       <c r="F102" s="6" t="s">
         <v>26</v>
@@ -7484,10 +7494,10 @@
         <v>26</v>
       </c>
       <c r="N102" s="6" t="s">
-        <v>289</v>
+        <v>291</v>
       </c>
       <c r="O102" s="6" t="s">
-        <v>192</v>
+        <v>194</v>
       </c>
       <c r="P102" s="6" t="s">
         <v>26</v>
@@ -7500,7 +7510,7 @@
     </row>
     <row r="103" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A103" s="8" t="s">
-        <v>297</v>
+        <v>299</v>
       </c>
       <c r="B103" s="9">
         <v>46239.57452252315</v>
@@ -7510,7 +7520,7 @@
         <v>46240.594121284725</v>
       </c>
       <c r="E103" s="10" t="s">
-        <v>298</v>
+        <v>300</v>
       </c>
       <c r="F103" s="10" t="s">
         <v>26</v>
@@ -7537,13 +7547,13 @@
         <v>26</v>
       </c>
       <c r="N103" s="10" t="s">
-        <v>257</v>
+        <v>259</v>
       </c>
       <c r="O103" s="10" t="s">
-        <v>299</v>
+        <v>301</v>
       </c>
       <c r="P103" s="10" t="s">
-        <v>300</v>
+        <v>302</v>
       </c>
       <c r="Q103" s="9">
         <v>46401</v>
@@ -7563,7 +7573,7 @@
     </row>
     <row r="104" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A104" s="4" t="s">
-        <v>301</v>
+        <v>303</v>
       </c>
       <c r="B104" s="5">
         <v>46239.57452674769</v>
@@ -7573,7 +7583,7 @@
         <v>46240.58973622685</v>
       </c>
       <c r="E104" s="6" t="s">
-        <v>186</v>
+        <v>188</v>
       </c>
       <c r="F104" s="6" t="s">
         <v>26</v>
@@ -7600,13 +7610,13 @@
         <v>26</v>
       </c>
       <c r="N104" s="6" t="s">
-        <v>298</v>
+        <v>300</v>
       </c>
       <c r="O104" s="6" t="s">
-        <v>186</v>
+        <v>188</v>
       </c>
       <c r="P104" s="6" t="s">
-        <v>302</v>
+        <v>304</v>
       </c>
       <c r="Q104" s="6"/>
       <c r="R104" s="6"/>
@@ -7616,7 +7626,7 @@
     </row>
     <row r="105" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A105" s="8" t="s">
-        <v>303</v>
+        <v>305</v>
       </c>
       <c r="B105" s="9">
         <v>46239.574530763886</v>
@@ -7626,7 +7636,7 @@
         <v>46240.58973244213</v>
       </c>
       <c r="E105" s="10" t="s">
-        <v>186</v>
+        <v>188</v>
       </c>
       <c r="F105" s="10" t="s">
         <v>26</v>
@@ -7653,13 +7663,13 @@
         <v>26</v>
       </c>
       <c r="N105" s="10" t="s">
-        <v>298</v>
+        <v>300</v>
       </c>
       <c r="O105" s="10" t="s">
-        <v>186</v>
+        <v>188</v>
       </c>
       <c r="P105" s="10" t="s">
-        <v>298</v>
+        <v>300</v>
       </c>
       <c r="Q105" s="10"/>
       <c r="R105" s="10"/>
@@ -7669,7 +7679,7 @@
     </row>
     <row r="106" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A106" s="4" t="s">
-        <v>304</v>
+        <v>306</v>
       </c>
       <c r="B106" s="5">
         <v>46239.5745340162</v>
@@ -7679,7 +7689,7 @@
         <v>46240.589728692124</v>
       </c>
       <c r="E106" s="6" t="s">
-        <v>186</v>
+        <v>188</v>
       </c>
       <c r="F106" s="6" t="s">
         <v>26</v>
@@ -7706,13 +7716,13 @@
         <v>26</v>
       </c>
       <c r="N106" s="6" t="s">
-        <v>298</v>
+        <v>300</v>
       </c>
       <c r="O106" s="6" t="s">
-        <v>186</v>
+        <v>188</v>
       </c>
       <c r="P106" s="6" t="s">
-        <v>305</v>
+        <v>307</v>
       </c>
       <c r="Q106" s="6"/>
       <c r="R106" s="6"/>
@@ -7722,7 +7732,7 @@
     </row>
     <row r="107" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A107" s="8" t="s">
-        <v>306</v>
+        <v>308</v>
       </c>
       <c r="B107" s="9">
         <v>46239.65323541667</v>
@@ -7732,7 +7742,7 @@
         <v>46240.58972483796</v>
       </c>
       <c r="E107" s="10" t="s">
-        <v>186</v>
+        <v>188</v>
       </c>
       <c r="F107" s="10" t="s">
         <v>26</v>
@@ -7759,13 +7769,13 @@
         <v>26</v>
       </c>
       <c r="N107" s="10" t="s">
-        <v>298</v>
+        <v>300</v>
       </c>
       <c r="O107" s="10" t="s">
-        <v>192</v>
+        <v>194</v>
       </c>
       <c r="P107" s="10" t="s">
-        <v>186</v>
+        <v>188</v>
       </c>
       <c r="Q107" s="10"/>
       <c r="R107" s="10"/>
@@ -7775,7 +7785,7 @@
     </row>
     <row r="108" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A108" s="4" t="s">
-        <v>307</v>
+        <v>309</v>
       </c>
       <c r="B108" s="5">
         <v>46239.57453762731</v>
@@ -7785,7 +7795,7 @@
         <v>46240.59673913194</v>
       </c>
       <c r="E108" s="6" t="s">
-        <v>300</v>
+        <v>302</v>
       </c>
       <c r="F108" s="6" t="s">
         <v>26</v>
@@ -7812,13 +7822,13 @@
         <v>26</v>
       </c>
       <c r="N108" s="6" t="s">
-        <v>257</v>
+        <v>259</v>
       </c>
       <c r="O108" s="6" t="s">
-        <v>308</v>
+        <v>310</v>
       </c>
       <c r="P108" s="6" t="s">
-        <v>309</v>
+        <v>311</v>
       </c>
       <c r="Q108" s="5">
         <v>46402</v>
@@ -7838,7 +7848,7 @@
     </row>
     <row r="109" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A109" s="8" t="s">
-        <v>310</v>
+        <v>312</v>
       </c>
       <c r="B109" s="9">
         <v>46239.57454184028</v>
@@ -7848,7 +7858,7 @@
         <v>46240.59276476852</v>
       </c>
       <c r="E109" s="10" t="s">
-        <v>186</v>
+        <v>188</v>
       </c>
       <c r="F109" s="10" t="s">
         <v>26</v>
@@ -7875,13 +7885,13 @@
         <v>26</v>
       </c>
       <c r="N109" s="10" t="s">
-        <v>300</v>
+        <v>302</v>
       </c>
       <c r="O109" s="10" t="s">
-        <v>186</v>
+        <v>188</v>
       </c>
       <c r="P109" s="10" t="s">
-        <v>311</v>
+        <v>313</v>
       </c>
       <c r="Q109" s="10"/>
       <c r="R109" s="10"/>
@@ -7891,7 +7901,7 @@
     </row>
     <row r="110" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A110" s="4" t="s">
-        <v>312</v>
+        <v>314</v>
       </c>
       <c r="B110" s="5">
         <v>46239.57454601851</v>
@@ -7901,7 +7911,7 @@
         <v>46240.59276085648</v>
       </c>
       <c r="E110" s="6" t="s">
-        <v>186</v>
+        <v>188</v>
       </c>
       <c r="F110" s="6" t="s">
         <v>26</v>
@@ -7928,13 +7938,13 @@
         <v>26</v>
       </c>
       <c r="N110" s="6" t="s">
-        <v>300</v>
+        <v>302</v>
       </c>
       <c r="O110" s="6" t="s">
-        <v>184</v>
+        <v>186</v>
       </c>
       <c r="P110" s="6" t="s">
-        <v>311</v>
+        <v>313</v>
       </c>
       <c r="Q110" s="6"/>
       <c r="R110" s="6"/>
@@ -7944,7 +7954,7 @@
     </row>
     <row r="111" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A111" s="8" t="s">
-        <v>313</v>
+        <v>315</v>
       </c>
       <c r="B111" s="9">
         <v>46239.57455318287</v>
@@ -7954,7 +7964,7 @@
         <v>46240.59275711805</v>
       </c>
       <c r="E111" s="10" t="s">
-        <v>186</v>
+        <v>188</v>
       </c>
       <c r="F111" s="10" t="s">
         <v>26</v>
@@ -7981,13 +7991,13 @@
         <v>26</v>
       </c>
       <c r="N111" s="10" t="s">
-        <v>300</v>
+        <v>302</v>
       </c>
       <c r="O111" s="10" t="s">
-        <v>184</v>
+        <v>186</v>
       </c>
       <c r="P111" s="10" t="s">
-        <v>311</v>
+        <v>313</v>
       </c>
       <c r="Q111" s="10"/>
       <c r="R111" s="10"/>
@@ -7997,7 +8007,7 @@
     </row>
     <row r="112" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A112" s="4" t="s">
-        <v>314</v>
+        <v>316</v>
       </c>
       <c r="B112" s="5">
         <v>46239.65330143519</v>
@@ -8007,7 +8017,7 @@
         <v>46240.59275344908</v>
       </c>
       <c r="E112" s="6" t="s">
-        <v>186</v>
+        <v>188</v>
       </c>
       <c r="F112" s="6" t="s">
         <v>26</v>
@@ -8034,10 +8044,10 @@
         <v>26</v>
       </c>
       <c r="N112" s="6" t="s">
-        <v>300</v>
+        <v>302</v>
       </c>
       <c r="O112" s="6" t="s">
-        <v>186</v>
+        <v>188</v>
       </c>
       <c r="P112" s="6" t="s">
         <v>26</v>
@@ -8050,7 +8060,7 @@
     </row>
     <row r="113" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A113" s="8" t="s">
-        <v>315</v>
+        <v>317</v>
       </c>
       <c r="B113" s="9">
         <v>46239.57455898148</v>
@@ -8060,7 +8070,7 @@
         <v>46240.59432991898</v>
       </c>
       <c r="E113" s="10" t="s">
-        <v>309</v>
+        <v>311</v>
       </c>
       <c r="F113" s="10" t="s">
         <v>26</v>
@@ -8087,10 +8097,10 @@
         <v>26</v>
       </c>
       <c r="N113" s="10" t="s">
-        <v>257</v>
+        <v>259</v>
       </c>
       <c r="O113" s="10" t="s">
-        <v>316</v>
+        <v>318</v>
       </c>
       <c r="P113" s="10" t="s">
         <v>26</v>
@@ -8113,7 +8123,7 @@
     </row>
     <row r="114" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A114" s="4" t="s">
-        <v>317</v>
+        <v>319</v>
       </c>
       <c r="B114" s="5">
         <v>46239.57456341435</v>
@@ -8123,7 +8133,7 @@
         <v>46240.59289621528</v>
       </c>
       <c r="E114" s="6" t="s">
-        <v>186</v>
+        <v>188</v>
       </c>
       <c r="F114" s="6" t="s">
         <v>26</v>
@@ -8150,13 +8160,13 @@
         <v>26</v>
       </c>
       <c r="N114" s="6" t="s">
-        <v>309</v>
+        <v>311</v>
       </c>
       <c r="O114" s="6" t="s">
-        <v>186</v>
+        <v>188</v>
       </c>
       <c r="P114" s="6" t="s">
-        <v>318</v>
+        <v>320</v>
       </c>
       <c r="Q114" s="6"/>
       <c r="R114" s="6"/>
@@ -8166,7 +8176,7 @@
     </row>
     <row r="115" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A115" s="8" t="s">
-        <v>319</v>
+        <v>321</v>
       </c>
       <c r="B115" s="9">
         <v>46239.57456761574</v>
@@ -8176,7 +8186,7 @@
         <v>46240.59289185185</v>
       </c>
       <c r="E115" s="10" t="s">
-        <v>186</v>
+        <v>188</v>
       </c>
       <c r="F115" s="10" t="s">
         <v>26</v>
@@ -8203,13 +8213,13 @@
         <v>26</v>
       </c>
       <c r="N115" s="10" t="s">
-        <v>309</v>
+        <v>311</v>
       </c>
       <c r="O115" s="10" t="s">
-        <v>186</v>
+        <v>188</v>
       </c>
       <c r="P115" s="10" t="s">
-        <v>318</v>
+        <v>320</v>
       </c>
       <c r="Q115" s="10"/>
       <c r="R115" s="10"/>
@@ -8219,7 +8229,7 @@
     </row>
     <row r="116" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A116" s="4" t="s">
-        <v>320</v>
+        <v>322</v>
       </c>
       <c r="B116" s="5">
         <v>46239.574571840276</v>
@@ -8229,7 +8239,7 @@
         <v>46240.59288778935</v>
       </c>
       <c r="E116" s="6" t="s">
-        <v>186</v>
+        <v>188</v>
       </c>
       <c r="F116" s="6" t="s">
         <v>26</v>
@@ -8256,13 +8266,13 @@
         <v>26</v>
       </c>
       <c r="N116" s="6" t="s">
-        <v>309</v>
+        <v>311</v>
       </c>
       <c r="O116" s="6" t="s">
-        <v>186</v>
+        <v>188</v>
       </c>
       <c r="P116" s="6" t="s">
-        <v>318</v>
+        <v>320</v>
       </c>
       <c r="Q116" s="6"/>
       <c r="R116" s="6"/>
@@ -8272,7 +8282,7 @@
     </row>
     <row r="117" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A117" s="8" t="s">
-        <v>321</v>
+        <v>323</v>
       </c>
       <c r="B117" s="9">
         <v>46239.65337195602</v>
@@ -8282,7 +8292,7 @@
         <v>46240.59288347222</v>
       </c>
       <c r="E117" s="10" t="s">
-        <v>186</v>
+        <v>188</v>
       </c>
       <c r="F117" s="10" t="s">
         <v>26</v>
@@ -8309,13 +8319,13 @@
         <v>26</v>
       </c>
       <c r="N117" s="10" t="s">
-        <v>309</v>
+        <v>311</v>
       </c>
       <c r="O117" s="10" t="s">
-        <v>192</v>
+        <v>194</v>
       </c>
       <c r="P117" s="10" t="s">
-        <v>186</v>
+        <v>188</v>
       </c>
       <c r="Q117" s="10"/>
       <c r="R117" s="10"/>
@@ -8325,7 +8335,7 @@
     </row>
     <row r="118" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A118" s="4" t="s">
-        <v>322</v>
+        <v>324</v>
       </c>
       <c r="B118" s="5">
         <v>46239.57457591435</v>
@@ -8335,7 +8345,7 @@
         <v>46240.58467253472</v>
       </c>
       <c r="E118" s="6" t="s">
-        <v>323</v>
+        <v>325</v>
       </c>
       <c r="F118" s="6" t="s">
         <v>25</v>
@@ -8359,7 +8369,7 @@
         <v>26</v>
       </c>
       <c r="O118" s="6" t="s">
-        <v>324</v>
+        <v>326</v>
       </c>
       <c r="P118" s="6" t="s">
         <v>26</v>
@@ -8372,7 +8382,7 @@
     </row>
     <row r="119" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A119" s="8" t="s">
-        <v>325</v>
+        <v>327</v>
       </c>
       <c r="B119" s="9">
         <v>46239.57457920139</v>
@@ -8382,16 +8392,16 @@
         <v>46240.595475775466</v>
       </c>
       <c r="E119" s="10" t="s">
-        <v>326</v>
+        <v>328</v>
       </c>
       <c r="F119" s="10" t="s">
         <v>26</v>
       </c>
       <c r="G119" s="10" t="s">
-        <v>327</v>
+        <v>329</v>
       </c>
       <c r="H119" s="10" t="s">
-        <v>328</v>
+        <v>330</v>
       </c>
       <c r="I119" s="9">
         <v>46407</v>
@@ -8409,13 +8419,13 @@
         <v>26</v>
       </c>
       <c r="N119" s="10" t="s">
-        <v>323</v>
+        <v>325</v>
       </c>
       <c r="O119" s="10" t="s">
-        <v>329</v>
+        <v>331</v>
       </c>
       <c r="P119" s="10" t="s">
-        <v>330</v>
+        <v>332</v>
       </c>
       <c r="Q119" s="9">
         <v>46407</v>
@@ -8435,7 +8445,7 @@
     </row>
     <row r="120" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A120" s="4" t="s">
-        <v>331</v>
+        <v>333</v>
       </c>
       <c r="B120" s="5">
         <v>46239.57458372685</v>
@@ -8445,16 +8455,16 @@
         <v>46240.595126388886</v>
       </c>
       <c r="E120" s="6" t="s">
-        <v>186</v>
+        <v>188</v>
       </c>
       <c r="F120" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G120" s="6" t="s">
-        <v>327</v>
+        <v>329</v>
       </c>
       <c r="H120" s="6" t="s">
-        <v>328</v>
+        <v>330</v>
       </c>
       <c r="I120" s="5">
         <v>46407</v>
@@ -8472,13 +8482,13 @@
         <v>26</v>
       </c>
       <c r="N120" s="6" t="s">
-        <v>326</v>
+        <v>328</v>
       </c>
       <c r="O120" s="6" t="s">
-        <v>186</v>
+        <v>188</v>
       </c>
       <c r="P120" s="6" t="s">
-        <v>332</v>
+        <v>334</v>
       </c>
       <c r="Q120" s="6"/>
       <c r="R120" s="6"/>
@@ -8488,7 +8498,7 @@
     </row>
     <row r="121" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A121" s="8" t="s">
-        <v>333</v>
+        <v>335</v>
       </c>
       <c r="B121" s="9">
         <v>46239.574587662035</v>
@@ -8498,16 +8508,16 @@
         <v>46240.59512229166</v>
       </c>
       <c r="E121" s="10" t="s">
-        <v>186</v>
+        <v>188</v>
       </c>
       <c r="F121" s="10" t="s">
         <v>26</v>
       </c>
       <c r="G121" s="10" t="s">
-        <v>327</v>
+        <v>329</v>
       </c>
       <c r="H121" s="10" t="s">
-        <v>328</v>
+        <v>330</v>
       </c>
       <c r="I121" s="9">
         <v>46407</v>
@@ -8525,13 +8535,13 @@
         <v>26</v>
       </c>
       <c r="N121" s="10" t="s">
-        <v>326</v>
+        <v>328</v>
       </c>
       <c r="O121" s="10" t="s">
-        <v>186</v>
+        <v>188</v>
       </c>
       <c r="P121" s="10" t="s">
-        <v>334</v>
+        <v>336</v>
       </c>
       <c r="Q121" s="10"/>
       <c r="R121" s="10"/>
@@ -8541,7 +8551,7 @@
     </row>
     <row r="122" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A122" s="4" t="s">
-        <v>335</v>
+        <v>337</v>
       </c>
       <c r="B122" s="5">
         <v>46239.57459146991</v>
@@ -8551,16 +8561,16 @@
         <v>46240.59511797453</v>
       </c>
       <c r="E122" s="6" t="s">
-        <v>186</v>
+        <v>188</v>
       </c>
       <c r="F122" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G122" s="6" t="s">
-        <v>327</v>
+        <v>329</v>
       </c>
       <c r="H122" s="6" t="s">
-        <v>328</v>
+        <v>330</v>
       </c>
       <c r="I122" s="5">
         <v>46407</v>
@@ -8578,13 +8588,13 @@
         <v>26</v>
       </c>
       <c r="N122" s="6" t="s">
-        <v>326</v>
+        <v>328</v>
       </c>
       <c r="O122" s="6" t="s">
-        <v>186</v>
+        <v>188</v>
       </c>
       <c r="P122" s="6" t="s">
-        <v>332</v>
+        <v>334</v>
       </c>
       <c r="Q122" s="6"/>
       <c r="R122" s="6"/>
@@ -8594,7 +8604,7 @@
     </row>
     <row r="123" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A123" s="8" t="s">
-        <v>336</v>
+        <v>338</v>
       </c>
       <c r="B123" s="9">
         <v>46239.65343762732</v>
@@ -8604,16 +8614,16 @@
         <v>46240.5951130787</v>
       </c>
       <c r="E123" s="10" t="s">
-        <v>186</v>
+        <v>188</v>
       </c>
       <c r="F123" s="10" t="s">
         <v>26</v>
       </c>
       <c r="G123" s="10" t="s">
-        <v>327</v>
+        <v>329</v>
       </c>
       <c r="H123" s="10" t="s">
-        <v>328</v>
+        <v>330</v>
       </c>
       <c r="I123" s="9">
         <v>46407</v>
@@ -8631,10 +8641,10 @@
         <v>26</v>
       </c>
       <c r="N123" s="10" t="s">
-        <v>326</v>
+        <v>328</v>
       </c>
       <c r="O123" s="10" t="s">
-        <v>186</v>
+        <v>188</v>
       </c>
       <c r="P123" s="10" t="s">
         <v>26</v>
@@ -8647,7 +8657,7 @@
     </row>
     <row r="124" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A124" s="4" t="s">
-        <v>337</v>
+        <v>339</v>
       </c>
       <c r="B124" s="5">
         <v>46239.665801446754</v>
@@ -8663,10 +8673,10 @@
         <v>26</v>
       </c>
       <c r="G124" s="6" t="s">
-        <v>327</v>
+        <v>329</v>
       </c>
       <c r="H124" s="6" t="s">
-        <v>328</v>
+        <v>330</v>
       </c>
       <c r="I124" s="5">
         <v>46407</v>
@@ -8684,13 +8694,13 @@
         <v>26</v>
       </c>
       <c r="N124" s="6" t="s">
-        <v>326</v>
+        <v>328</v>
       </c>
       <c r="O124" s="6" t="s">
         <v>56</v>
       </c>
       <c r="P124" s="6" t="s">
-        <v>338</v>
+        <v>340</v>
       </c>
       <c r="Q124" s="6"/>
       <c r="R124" s="6"/>
@@ -8700,7 +8710,7 @@
     </row>
     <row r="125" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A125" s="8" t="s">
-        <v>339</v>
+        <v>341</v>
       </c>
       <c r="B125" s="9">
         <v>46239.665817581015</v>
@@ -8716,10 +8726,10 @@
         <v>26</v>
       </c>
       <c r="G125" s="10" t="s">
-        <v>327</v>
+        <v>329</v>
       </c>
       <c r="H125" s="10" t="s">
-        <v>328</v>
+        <v>330</v>
       </c>
       <c r="I125" s="9">
         <v>46407</v>
@@ -8737,13 +8747,13 @@
         <v>26</v>
       </c>
       <c r="N125" s="10" t="s">
-        <v>326</v>
+        <v>328</v>
       </c>
       <c r="O125" s="10" t="s">
         <v>56</v>
       </c>
       <c r="P125" s="10" t="s">
-        <v>340</v>
+        <v>342</v>
       </c>
       <c r="Q125" s="10"/>
       <c r="R125" s="10"/>
@@ -8753,7 +8763,7 @@
     </row>
     <row r="126" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A126" s="4" t="s">
-        <v>341</v>
+        <v>343</v>
       </c>
       <c r="B126" s="5">
         <v>46239.66583704861</v>
@@ -8769,10 +8779,10 @@
         <v>26</v>
       </c>
       <c r="G126" s="6" t="s">
-        <v>327</v>
+        <v>329</v>
       </c>
       <c r="H126" s="6" t="s">
-        <v>328</v>
+        <v>330</v>
       </c>
       <c r="I126" s="5">
         <v>46407</v>
@@ -8790,13 +8800,13 @@
         <v>26</v>
       </c>
       <c r="N126" s="6" t="s">
-        <v>326</v>
+        <v>328</v>
       </c>
       <c r="O126" s="6" t="s">
         <v>56</v>
       </c>
       <c r="P126" s="6" t="s">
-        <v>342</v>
+        <v>344</v>
       </c>
       <c r="Q126" s="6"/>
       <c r="R126" s="6"/>
@@ -8806,7 +8816,7 @@
     </row>
     <row r="127" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A127" s="8" t="s">
-        <v>343</v>
+        <v>345</v>
       </c>
       <c r="B127" s="9">
         <v>46239.66587196759</v>
@@ -8822,10 +8832,10 @@
         <v>26</v>
       </c>
       <c r="G127" s="10" t="s">
-        <v>327</v>
+        <v>329</v>
       </c>
       <c r="H127" s="10" t="s">
-        <v>328</v>
+        <v>330</v>
       </c>
       <c r="I127" s="9">
         <v>46407</v>
@@ -8843,13 +8853,13 @@
         <v>26</v>
       </c>
       <c r="N127" s="10" t="s">
-        <v>326</v>
+        <v>328</v>
       </c>
       <c r="O127" s="10" t="s">
         <v>56</v>
       </c>
       <c r="P127" s="10" t="s">
-        <v>344</v>
+        <v>346</v>
       </c>
       <c r="Q127" s="10"/>
       <c r="R127" s="10"/>
@@ -8859,7 +8869,7 @@
     </row>
     <row r="128" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A128" s="4" t="s">
-        <v>345</v>
+        <v>347</v>
       </c>
       <c r="B128" s="5">
         <v>46239.57459537037</v>
@@ -8869,7 +8879,7 @@
         <v>46240.595416041666</v>
       </c>
       <c r="E128" s="6" t="s">
-        <v>346</v>
+        <v>348</v>
       </c>
       <c r="F128" s="6" t="s">
         <v>26</v>
@@ -8896,10 +8906,10 @@
         <v>26</v>
       </c>
       <c r="N128" s="6" t="s">
-        <v>323</v>
+        <v>325</v>
       </c>
       <c r="O128" s="6" t="s">
-        <v>347</v>
+        <v>349</v>
       </c>
       <c r="P128" s="6" t="s">
         <v>26</v>
@@ -8922,7 +8932,7 @@
     </row>
     <row r="129" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A129" s="8" t="s">
-        <v>348</v>
+        <v>350</v>
       </c>
       <c r="B129" s="9">
         <v>46239.57459956019</v>
@@ -8932,7 +8942,7 @@
         <v>46240.59525278935</v>
       </c>
       <c r="E129" s="10" t="s">
-        <v>186</v>
+        <v>188</v>
       </c>
       <c r="F129" s="10" t="s">
         <v>26</v>
@@ -8959,13 +8969,13 @@
         <v>26</v>
       </c>
       <c r="N129" s="10" t="s">
-        <v>346</v>
+        <v>348</v>
       </c>
       <c r="O129" s="10" t="s">
-        <v>186</v>
+        <v>188</v>
       </c>
       <c r="P129" s="10" t="s">
-        <v>349</v>
+        <v>351</v>
       </c>
       <c r="Q129" s="10"/>
       <c r="R129" s="10"/>
@@ -8975,7 +8985,7 @@
     </row>
     <row r="130" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A130" s="4" t="s">
-        <v>350</v>
+        <v>352</v>
       </c>
       <c r="B130" s="5">
         <v>46239.57460317129</v>
@@ -8985,7 +8995,7 @@
         <v>46240.595248032405</v>
       </c>
       <c r="E130" s="6" t="s">
-        <v>186</v>
+        <v>188</v>
       </c>
       <c r="F130" s="6" t="s">
         <v>26</v>
@@ -9012,13 +9022,13 @@
         <v>26</v>
       </c>
       <c r="N130" s="6" t="s">
-        <v>346</v>
+        <v>348</v>
       </c>
       <c r="O130" s="6" t="s">
-        <v>186</v>
+        <v>188</v>
       </c>
       <c r="P130" s="6" t="s">
-        <v>349</v>
+        <v>351</v>
       </c>
       <c r="Q130" s="6"/>
       <c r="R130" s="6"/>
@@ -9028,7 +9038,7 @@
     </row>
     <row r="131" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A131" s="8" t="s">
-        <v>351</v>
+        <v>353</v>
       </c>
       <c r="B131" s="9">
         <v>46239.57460717593</v>
@@ -9038,7 +9048,7 @@
         <v>46240.595243749995</v>
       </c>
       <c r="E131" s="10" t="s">
-        <v>186</v>
+        <v>188</v>
       </c>
       <c r="F131" s="10" t="s">
         <v>26</v>
@@ -9065,13 +9075,13 @@
         <v>26</v>
       </c>
       <c r="N131" s="10" t="s">
-        <v>346</v>
+        <v>348</v>
       </c>
       <c r="O131" s="10" t="s">
-        <v>186</v>
+        <v>188</v>
       </c>
       <c r="P131" s="10" t="s">
-        <v>352</v>
+        <v>354</v>
       </c>
       <c r="Q131" s="10"/>
       <c r="R131" s="10"/>
@@ -9081,7 +9091,7 @@
     </row>
     <row r="132" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A132" s="4" t="s">
-        <v>353</v>
+        <v>355</v>
       </c>
       <c r="B132" s="5">
         <v>46239.653502546294</v>
@@ -9091,7 +9101,7 @@
         <v>46240.595240069444</v>
       </c>
       <c r="E132" s="6" t="s">
-        <v>186</v>
+        <v>188</v>
       </c>
       <c r="F132" s="6" t="s">
         <v>26</v>
@@ -9118,10 +9128,10 @@
         <v>26</v>
       </c>
       <c r="N132" s="6" t="s">
-        <v>346</v>
+        <v>348</v>
       </c>
       <c r="O132" s="6" t="s">
-        <v>192</v>
+        <v>194</v>
       </c>
       <c r="P132" s="6" t="s">
         <v>26</v>
@@ -9134,7 +9144,7 @@
     </row>
     <row r="133" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A133" s="8" t="s">
-        <v>354</v>
+        <v>356</v>
       </c>
       <c r="B133" s="9">
         <v>46239.67035252315</v>
@@ -9144,7 +9154,7 @@
         <v>46240.59523623843</v>
       </c>
       <c r="E133" s="10" t="s">
-        <v>355</v>
+        <v>357</v>
       </c>
       <c r="F133" s="10" t="s">
         <v>26</v>
@@ -9171,13 +9181,13 @@
         <v>26</v>
       </c>
       <c r="N133" s="10" t="s">
-        <v>346</v>
+        <v>348</v>
       </c>
       <c r="O133" s="10" t="s">
         <v>56</v>
       </c>
       <c r="P133" s="10" t="s">
-        <v>356</v>
+        <v>358</v>
       </c>
       <c r="Q133" s="10"/>
       <c r="R133" s="10"/>
@@ -9187,7 +9197,7 @@
     </row>
     <row r="134" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A134" s="4" t="s">
-        <v>357</v>
+        <v>359</v>
       </c>
       <c r="B134" s="5">
         <v>46239.670362372686</v>
@@ -9197,7 +9207,7 @@
         <v>46240.595232673615</v>
       </c>
       <c r="E134" s="6" t="s">
-        <v>358</v>
+        <v>360</v>
       </c>
       <c r="F134" s="6" t="s">
         <v>26</v>
@@ -9224,13 +9234,13 @@
         <v>26</v>
       </c>
       <c r="N134" s="6" t="s">
-        <v>346</v>
+        <v>348</v>
       </c>
       <c r="O134" s="6" t="s">
         <v>56</v>
       </c>
       <c r="P134" s="6" t="s">
-        <v>359</v>
+        <v>361</v>
       </c>
       <c r="Q134" s="6"/>
       <c r="R134" s="6"/>
@@ -9240,7 +9250,7 @@
     </row>
     <row r="135" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A135" s="8" t="s">
-        <v>360</v>
+        <v>362</v>
       </c>
       <c r="B135" s="9">
         <v>46239.67036836805</v>
@@ -9250,7 +9260,7 @@
         <v>46240.59522915509</v>
       </c>
       <c r="E135" s="10" t="s">
-        <v>361</v>
+        <v>363</v>
       </c>
       <c r="F135" s="10" t="s">
         <v>26</v>
@@ -9277,13 +9287,13 @@
         <v>26</v>
       </c>
       <c r="N135" s="10" t="s">
-        <v>346</v>
+        <v>348</v>
       </c>
       <c r="O135" s="10" t="s">
         <v>56</v>
       </c>
       <c r="P135" s="10" t="s">
-        <v>362</v>
+        <v>364</v>
       </c>
       <c r="Q135" s="10"/>
       <c r="R135" s="10"/>
@@ -9293,7 +9303,7 @@
     </row>
     <row r="136" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A136" s="4" t="s">
-        <v>363</v>
+        <v>365</v>
       </c>
       <c r="B136" s="5">
         <v>46239.670374050926</v>
@@ -9303,7 +9313,7 @@
         <v>46240.5952253588</v>
       </c>
       <c r="E136" s="6" t="s">
-        <v>364</v>
+        <v>366</v>
       </c>
       <c r="F136" s="6" t="s">
         <v>26</v>
@@ -9330,13 +9340,13 @@
         <v>26</v>
       </c>
       <c r="N136" s="6" t="s">
-        <v>346</v>
+        <v>348</v>
       </c>
       <c r="O136" s="6" t="s">
         <v>56</v>
       </c>
       <c r="P136" s="6" t="s">
-        <v>365</v>
+        <v>367</v>
       </c>
       <c r="Q136" s="6"/>
       <c r="R136" s="6"/>
@@ -9346,7 +9356,7 @@
     </row>
     <row r="137" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A137" s="8" t="s">
-        <v>366</v>
+        <v>368</v>
       </c>
       <c r="B137" s="9">
         <v>46239.57461079861</v>
@@ -9356,16 +9366,16 @@
         <v>46240.59608133102</v>
       </c>
       <c r="E137" s="10" t="s">
-        <v>367</v>
+        <v>369</v>
       </c>
       <c r="F137" s="10" t="s">
         <v>26</v>
       </c>
       <c r="G137" s="10" t="s">
-        <v>220</v>
+        <v>222</v>
       </c>
       <c r="H137" s="10" t="s">
-        <v>221</v>
+        <v>223</v>
       </c>
       <c r="I137" s="9">
         <v>46412</v>
@@ -9383,13 +9393,13 @@
         <v>26</v>
       </c>
       <c r="N137" s="10" t="s">
-        <v>323</v>
+        <v>325</v>
       </c>
       <c r="O137" s="10" t="s">
-        <v>368</v>
+        <v>370</v>
       </c>
       <c r="P137" s="10" t="s">
-        <v>323</v>
+        <v>325</v>
       </c>
       <c r="Q137" s="9">
         <v>46412</v>
@@ -9409,7 +9419,7 @@
     </row>
     <row r="138" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A138" s="4" t="s">
-        <v>369</v>
+        <v>371</v>
       </c>
       <c r="B138" s="5">
         <v>46239.57461494213</v>
@@ -9419,16 +9429,16 @@
         <v>46240.59571179398</v>
       </c>
       <c r="E138" s="6" t="s">
-        <v>186</v>
+        <v>188</v>
       </c>
       <c r="F138" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G138" s="6" t="s">
-        <v>220</v>
+        <v>222</v>
       </c>
       <c r="H138" s="6" t="s">
-        <v>221</v>
+        <v>223</v>
       </c>
       <c r="I138" s="5">
         <v>46412</v>
@@ -9446,13 +9456,13 @@
         <v>26</v>
       </c>
       <c r="N138" s="6" t="s">
-        <v>367</v>
+        <v>369</v>
       </c>
       <c r="O138" s="6" t="s">
-        <v>186</v>
+        <v>188</v>
       </c>
       <c r="P138" s="6" t="s">
-        <v>370</v>
+        <v>372</v>
       </c>
       <c r="Q138" s="6"/>
       <c r="R138" s="6"/>
@@ -9462,7 +9472,7 @@
     </row>
     <row r="139" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A139" s="8" t="s">
-        <v>371</v>
+        <v>373</v>
       </c>
       <c r="B139" s="9">
         <v>46239.574618680555</v>
@@ -9472,16 +9482,16 @@
         <v>46240.595708611116</v>
       </c>
       <c r="E139" s="10" t="s">
-        <v>186</v>
+        <v>188</v>
       </c>
       <c r="F139" s="10" t="s">
         <v>26</v>
       </c>
       <c r="G139" s="10" t="s">
-        <v>220</v>
+        <v>222</v>
       </c>
       <c r="H139" s="10" t="s">
-        <v>221</v>
+        <v>223</v>
       </c>
       <c r="I139" s="9">
         <v>46412</v>
@@ -9499,13 +9509,13 @@
         <v>26</v>
       </c>
       <c r="N139" s="10" t="s">
-        <v>367</v>
+        <v>369</v>
       </c>
       <c r="O139" s="10" t="s">
-        <v>186</v>
+        <v>188</v>
       </c>
       <c r="P139" s="10" t="s">
-        <v>370</v>
+        <v>372</v>
       </c>
       <c r="Q139" s="10"/>
       <c r="R139" s="10"/>
@@ -9515,7 +9525,7 @@
     </row>
     <row r="140" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A140" s="4" t="s">
-        <v>372</v>
+        <v>374</v>
       </c>
       <c r="B140" s="5">
         <v>46239.57462254629</v>
@@ -9525,16 +9535,16 @@
         <v>46240.59570520833</v>
       </c>
       <c r="E140" s="6" t="s">
-        <v>186</v>
+        <v>188</v>
       </c>
       <c r="F140" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G140" s="6" t="s">
-        <v>220</v>
+        <v>222</v>
       </c>
       <c r="H140" s="6" t="s">
-        <v>221</v>
+        <v>223</v>
       </c>
       <c r="I140" s="5">
         <v>46412</v>
@@ -9552,13 +9562,13 @@
         <v>26</v>
       </c>
       <c r="N140" s="6" t="s">
-        <v>367</v>
+        <v>369</v>
       </c>
       <c r="O140" s="6" t="s">
-        <v>186</v>
+        <v>188</v>
       </c>
       <c r="P140" s="6" t="s">
-        <v>373</v>
+        <v>375</v>
       </c>
       <c r="Q140" s="6"/>
       <c r="R140" s="6"/>
@@ -9568,7 +9578,7 @@
     </row>
     <row r="141" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A141" s="8" t="s">
-        <v>374</v>
+        <v>376</v>
       </c>
       <c r="B141" s="9">
         <v>46239.65356868056</v>
@@ -9578,16 +9588,16 @@
         <v>46240.59570181713</v>
       </c>
       <c r="E141" s="10" t="s">
-        <v>186</v>
+        <v>188</v>
       </c>
       <c r="F141" s="10" t="s">
         <v>26</v>
       </c>
       <c r="G141" s="10" t="s">
-        <v>220</v>
+        <v>222</v>
       </c>
       <c r="H141" s="10" t="s">
-        <v>221</v>
+        <v>223</v>
       </c>
       <c r="I141" s="9">
         <v>46412</v>
@@ -9605,13 +9615,13 @@
         <v>26</v>
       </c>
       <c r="N141" s="10" t="s">
-        <v>367</v>
+        <v>369</v>
       </c>
       <c r="O141" s="10" t="s">
-        <v>192</v>
+        <v>194</v>
       </c>
       <c r="P141" s="10" t="s">
-        <v>367</v>
+        <v>369</v>
       </c>
       <c r="Q141" s="10"/>
       <c r="R141" s="10"/>
@@ -9621,7 +9631,7 @@
     </row>
     <row r="142" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A142" s="4" t="s">
-        <v>375</v>
+        <v>377</v>
       </c>
       <c r="B142" s="5">
         <v>46239.675931875</v>
@@ -9637,10 +9647,10 @@
         <v>26</v>
       </c>
       <c r="G142" s="6" t="s">
-        <v>220</v>
+        <v>222</v>
       </c>
       <c r="H142" s="6" t="s">
-        <v>221</v>
+        <v>223</v>
       </c>
       <c r="I142" s="5">
         <v>46412</v>
@@ -9658,13 +9668,13 @@
         <v>26</v>
       </c>
       <c r="N142" s="6" t="s">
-        <v>367</v>
+        <v>369</v>
       </c>
       <c r="O142" s="6" t="s">
-        <v>355</v>
+        <v>357</v>
       </c>
       <c r="P142" s="6" t="s">
-        <v>367</v>
+        <v>369</v>
       </c>
       <c r="Q142" s="6"/>
       <c r="R142" s="6"/>
@@ -9674,7 +9684,7 @@
     </row>
     <row r="143" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A143" s="8" t="s">
-        <v>376</v>
+        <v>378</v>
       </c>
       <c r="B143" s="9">
         <v>46239.67595826389</v>
@@ -9684,16 +9694,16 @@
         <v>46240.59569465277</v>
       </c>
       <c r="E143" s="10" t="s">
-        <v>377</v>
+        <v>379</v>
       </c>
       <c r="F143" s="10" t="s">
         <v>26</v>
       </c>
       <c r="G143" s="10" t="s">
-        <v>220</v>
+        <v>222</v>
       </c>
       <c r="H143" s="10" t="s">
-        <v>221</v>
+        <v>223</v>
       </c>
       <c r="I143" s="9">
         <v>46412</v>
@@ -9711,13 +9721,13 @@
         <v>26</v>
       </c>
       <c r="N143" s="10" t="s">
-        <v>367</v>
+        <v>369</v>
       </c>
       <c r="O143" s="10" t="s">
-        <v>358</v>
+        <v>360</v>
       </c>
       <c r="P143" s="10" t="s">
-        <v>378</v>
+        <v>380</v>
       </c>
       <c r="Q143" s="10"/>
       <c r="R143" s="10"/>
@@ -9727,7 +9737,7 @@
     </row>
     <row r="144" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A144" s="4" t="s">
-        <v>379</v>
+        <v>381</v>
       </c>
       <c r="B144" s="5">
         <v>46239.67596550926</v>
@@ -9743,10 +9753,10 @@
         <v>26</v>
       </c>
       <c r="G144" s="6" t="s">
-        <v>220</v>
+        <v>222</v>
       </c>
       <c r="H144" s="6" t="s">
-        <v>221</v>
+        <v>223</v>
       </c>
       <c r="I144" s="5">
         <v>46412</v>
@@ -9764,13 +9774,13 @@
         <v>26</v>
       </c>
       <c r="N144" s="6" t="s">
-        <v>367</v>
+        <v>369</v>
       </c>
       <c r="O144" s="6" t="s">
-        <v>361</v>
+        <v>363</v>
       </c>
       <c r="P144" s="6" t="s">
-        <v>378</v>
+        <v>380</v>
       </c>
       <c r="Q144" s="6"/>
       <c r="R144" s="6"/>
@@ -9780,7 +9790,7 @@
     </row>
     <row r="145" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A145" s="8" t="s">
-        <v>380</v>
+        <v>382</v>
       </c>
       <c r="B145" s="9">
         <v>46239.67597105324</v>
@@ -9790,16 +9800,16 @@
         <v>46240.59568726852</v>
       </c>
       <c r="E145" s="10" t="s">
-        <v>377</v>
+        <v>379</v>
       </c>
       <c r="F145" s="10" t="s">
         <v>26</v>
       </c>
       <c r="G145" s="10" t="s">
-        <v>220</v>
+        <v>222</v>
       </c>
       <c r="H145" s="10" t="s">
-        <v>221</v>
+        <v>223</v>
       </c>
       <c r="I145" s="9">
         <v>46412</v>
@@ -9817,13 +9827,13 @@
         <v>26</v>
       </c>
       <c r="N145" s="10" t="s">
-        <v>367</v>
+        <v>369</v>
       </c>
       <c r="O145" s="10" t="s">
-        <v>364</v>
+        <v>366</v>
       </c>
       <c r="P145" s="10" t="s">
-        <v>381</v>
+        <v>383</v>
       </c>
       <c r="Q145" s="10"/>
       <c r="R145" s="10"/>
@@ -9833,7 +9843,7 @@
     </row>
     <row r="146" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A146" s="4" t="s">
-        <v>382</v>
+        <v>384</v>
       </c>
       <c r="B146" s="5">
         <v>46239.574665231485</v>
@@ -9843,16 +9853,16 @@
         <v>46240.59601453703</v>
       </c>
       <c r="E146" s="6" t="s">
-        <v>383</v>
+        <v>385</v>
       </c>
       <c r="F146" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G146" s="6" t="s">
-        <v>220</v>
+        <v>222</v>
       </c>
       <c r="H146" s="6" t="s">
-        <v>221</v>
+        <v>223</v>
       </c>
       <c r="I146" s="5">
         <v>46413</v>
@@ -9870,13 +9880,13 @@
         <v>26</v>
       </c>
       <c r="N146" s="6" t="s">
-        <v>323</v>
+        <v>325</v>
       </c>
       <c r="O146" s="6" t="s">
-        <v>384</v>
+        <v>386</v>
       </c>
       <c r="P146" s="6" t="s">
-        <v>385</v>
+        <v>387</v>
       </c>
       <c r="Q146" s="5">
         <v>46413</v>
@@ -9896,7 +9906,7 @@
     </row>
     <row r="147" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A147" s="8" t="s">
-        <v>386</v>
+        <v>388</v>
       </c>
       <c r="B147" s="9">
         <v>46239.57467313657</v>
@@ -9906,16 +9916,16 @@
         <v>46240.5962641088</v>
       </c>
       <c r="E147" s="10" t="s">
-        <v>186</v>
+        <v>188</v>
       </c>
       <c r="F147" s="10" t="s">
         <v>26</v>
       </c>
       <c r="G147" s="10" t="s">
-        <v>220</v>
+        <v>222</v>
       </c>
       <c r="H147" s="10" t="s">
-        <v>221</v>
+        <v>223</v>
       </c>
       <c r="I147" s="9">
         <v>46413</v>
@@ -9933,13 +9943,13 @@
         <v>26</v>
       </c>
       <c r="N147" s="10" t="s">
-        <v>383</v>
+        <v>385</v>
       </c>
       <c r="O147" s="10" t="s">
-        <v>186</v>
+        <v>188</v>
       </c>
       <c r="P147" s="10" t="s">
-        <v>387</v>
+        <v>389</v>
       </c>
       <c r="Q147" s="10"/>
       <c r="R147" s="10"/>
@@ -9949,7 +9959,7 @@
     </row>
     <row r="148" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A148" s="4" t="s">
-        <v>388</v>
+        <v>390</v>
       </c>
       <c r="B148" s="5">
         <v>46239.57467765047</v>
@@ -9959,16 +9969,16 @@
         <v>46240.5962597801</v>
       </c>
       <c r="E148" s="6" t="s">
-        <v>186</v>
+        <v>188</v>
       </c>
       <c r="F148" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G148" s="6" t="s">
-        <v>220</v>
+        <v>222</v>
       </c>
       <c r="H148" s="6" t="s">
-        <v>221</v>
+        <v>223</v>
       </c>
       <c r="I148" s="5">
         <v>46413</v>
@@ -9986,13 +9996,13 @@
         <v>26</v>
       </c>
       <c r="N148" s="6" t="s">
-        <v>383</v>
+        <v>385</v>
       </c>
       <c r="O148" s="6" t="s">
-        <v>186</v>
+        <v>188</v>
       </c>
       <c r="P148" s="6" t="s">
-        <v>389</v>
+        <v>391</v>
       </c>
       <c r="Q148" s="6"/>
       <c r="R148" s="6"/>
@@ -10002,7 +10012,7 @@
     </row>
     <row r="149" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A149" s="8" t="s">
-        <v>390</v>
+        <v>392</v>
       </c>
       <c r="B149" s="9">
         <v>46239.57468208333</v>
@@ -10012,16 +10022,16 @@
         <v>46240.596255625</v>
       </c>
       <c r="E149" s="10" t="s">
-        <v>186</v>
+        <v>188</v>
       </c>
       <c r="F149" s="10" t="s">
         <v>26</v>
       </c>
       <c r="G149" s="10" t="s">
-        <v>220</v>
+        <v>222</v>
       </c>
       <c r="H149" s="10" t="s">
-        <v>221</v>
+        <v>223</v>
       </c>
       <c r="I149" s="9">
         <v>46413</v>
@@ -10039,13 +10049,13 @@
         <v>26</v>
       </c>
       <c r="N149" s="10" t="s">
-        <v>383</v>
+        <v>385</v>
       </c>
       <c r="O149" s="10" t="s">
-        <v>186</v>
+        <v>188</v>
       </c>
       <c r="P149" s="10" t="s">
-        <v>389</v>
+        <v>391</v>
       </c>
       <c r="Q149" s="10"/>
       <c r="R149" s="10"/>
@@ -10055,7 +10065,7 @@
     </row>
     <row r="150" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A150" s="4" t="s">
-        <v>391</v>
+        <v>393</v>
       </c>
       <c r="B150" s="5">
         <v>46239.653672326385</v>
@@ -10065,16 +10075,16 @@
         <v>46240.59625209491</v>
       </c>
       <c r="E150" s="6" t="s">
-        <v>186</v>
+        <v>188</v>
       </c>
       <c r="F150" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G150" s="6" t="s">
-        <v>220</v>
+        <v>222</v>
       </c>
       <c r="H150" s="6" t="s">
-        <v>221</v>
+        <v>223</v>
       </c>
       <c r="I150" s="5">
         <v>46413</v>
@@ -10092,10 +10102,10 @@
         <v>26</v>
       </c>
       <c r="N150" s="6" t="s">
-        <v>383</v>
+        <v>385</v>
       </c>
       <c r="O150" s="6" t="s">
-        <v>192</v>
+        <v>194</v>
       </c>
       <c r="P150" s="6" t="s">
         <v>26</v>
@@ -10108,7 +10118,7 @@
     </row>
     <row r="151" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A151" s="8" t="s">
-        <v>392</v>
+        <v>394</v>
       </c>
       <c r="B151" s="9">
         <v>46239.67752369213</v>
@@ -10124,10 +10134,10 @@
         <v>26</v>
       </c>
       <c r="G151" s="10" t="s">
-        <v>220</v>
+        <v>222</v>
       </c>
       <c r="H151" s="10" t="s">
-        <v>221</v>
+        <v>223</v>
       </c>
       <c r="I151" s="9">
         <v>46413</v>
@@ -10145,10 +10155,10 @@
         <v>26</v>
       </c>
       <c r="N151" s="10" t="s">
-        <v>383</v>
+        <v>385</v>
       </c>
       <c r="O151" s="10" t="s">
-        <v>355</v>
+        <v>357</v>
       </c>
       <c r="P151" s="10" t="s">
         <v>26</v>
@@ -10161,7 +10171,7 @@
     </row>
     <row r="152" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A152" s="4" t="s">
-        <v>393</v>
+        <v>395</v>
       </c>
       <c r="B152" s="5">
         <v>46239.67753166667</v>
@@ -10177,10 +10187,10 @@
         <v>26</v>
       </c>
       <c r="G152" s="6" t="s">
-        <v>220</v>
+        <v>222</v>
       </c>
       <c r="H152" s="6" t="s">
-        <v>221</v>
+        <v>223</v>
       </c>
       <c r="I152" s="5">
         <v>46413</v>
@@ -10198,10 +10208,10 @@
         <v>26</v>
       </c>
       <c r="N152" s="6" t="s">
-        <v>383</v>
+        <v>385</v>
       </c>
       <c r="O152" s="6" t="s">
-        <v>377</v>
+        <v>379</v>
       </c>
       <c r="P152" s="6" t="s">
         <v>26</v>
@@ -10214,7 +10224,7 @@
     </row>
     <row r="153" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A153" s="8" t="s">
-        <v>394</v>
+        <v>396</v>
       </c>
       <c r="B153" s="9">
         <v>46239.677537361116</v>
@@ -10230,10 +10240,10 @@
         <v>26</v>
       </c>
       <c r="G153" s="10" t="s">
-        <v>220</v>
+        <v>222</v>
       </c>
       <c r="H153" s="10" t="s">
-        <v>221</v>
+        <v>223</v>
       </c>
       <c r="I153" s="9">
         <v>46413</v>
@@ -10251,7 +10261,7 @@
         <v>26</v>
       </c>
       <c r="N153" s="10" t="s">
-        <v>383</v>
+        <v>385</v>
       </c>
       <c r="O153" s="10" t="s">
         <v>56</v>
@@ -10267,7 +10277,7 @@
     </row>
     <row r="154" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A154" s="4" t="s">
-        <v>395</v>
+        <v>397</v>
       </c>
       <c r="B154" s="5">
         <v>46239.67754380787</v>
@@ -10283,10 +10293,10 @@
         <v>26</v>
       </c>
       <c r="G154" s="6" t="s">
-        <v>220</v>
+        <v>222</v>
       </c>
       <c r="H154" s="6" t="s">
-        <v>221</v>
+        <v>223</v>
       </c>
       <c r="I154" s="5">
         <v>46413</v>
@@ -10304,10 +10314,10 @@
         <v>26</v>
       </c>
       <c r="N154" s="6" t="s">
-        <v>383</v>
+        <v>385</v>
       </c>
       <c r="O154" s="6" t="s">
-        <v>377</v>
+        <v>379</v>
       </c>
       <c r="P154" s="6" t="s">
         <v>26</v>
@@ -10320,7 +10330,7 @@
     </row>
     <row r="155" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A155" s="8" t="s">
-        <v>396</v>
+        <v>398</v>
       </c>
       <c r="B155" s="9">
         <v>46239.57468613426</v>
@@ -10330,7 +10340,7 @@
         <v>46240.58500695602</v>
       </c>
       <c r="E155" s="10" t="s">
-        <v>397</v>
+        <v>399</v>
       </c>
       <c r="F155" s="10" t="s">
         <v>25</v>
@@ -10354,7 +10364,7 @@
         <v>26</v>
       </c>
       <c r="O155" s="10" t="s">
-        <v>398</v>
+        <v>400</v>
       </c>
       <c r="P155" s="10" t="s">
         <v>26</v>
@@ -10367,7 +10377,7 @@
     </row>
     <row r="156" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A156" s="4" t="s">
-        <v>399</v>
+        <v>401</v>
       </c>
       <c r="B156" s="5">
         <v>46239.57468942129</v>
@@ -10377,16 +10387,16 @@
         <v>46240.596291608796</v>
       </c>
       <c r="E156" s="6" t="s">
-        <v>400</v>
+        <v>402</v>
       </c>
       <c r="F156" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G156" s="6" t="s">
-        <v>401</v>
+        <v>403</v>
       </c>
       <c r="H156" s="6" t="s">
-        <v>402</v>
+        <v>404</v>
       </c>
       <c r="I156" s="5">
         <v>46414</v>
@@ -10404,13 +10414,13 @@
         <v>26</v>
       </c>
       <c r="N156" s="6" t="s">
-        <v>397</v>
+        <v>399</v>
       </c>
       <c r="O156" s="6" t="s">
-        <v>403</v>
+        <v>405</v>
       </c>
       <c r="P156" s="6" t="s">
-        <v>397</v>
+        <v>399</v>
       </c>
       <c r="Q156" s="5">
         <v>46422</v>
@@ -10430,7 +10440,7 @@
     </row>
     <row r="157" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A157" s="8" t="s">
-        <v>404</v>
+        <v>406</v>
       </c>
       <c r="B157" s="9">
         <v>46239.57469508101</v>
@@ -10440,16 +10450,16 @@
         <v>46240.596288217595</v>
       </c>
       <c r="E157" s="10" t="s">
-        <v>405</v>
+        <v>407</v>
       </c>
       <c r="F157" s="10" t="s">
         <v>26</v>
       </c>
       <c r="G157" s="10" t="s">
-        <v>401</v>
+        <v>403</v>
       </c>
       <c r="H157" s="10" t="s">
-        <v>402</v>
+        <v>404</v>
       </c>
       <c r="I157" s="9">
         <v>46414</v>
@@ -10467,13 +10477,13 @@
         <v>26</v>
       </c>
       <c r="N157" s="10" t="s">
-        <v>397</v>
+        <v>399</v>
       </c>
       <c r="O157" s="10" t="s">
-        <v>406</v>
+        <v>408</v>
       </c>
       <c r="P157" s="10" t="s">
-        <v>397</v>
+        <v>399</v>
       </c>
       <c r="Q157" s="9">
         <v>46422</v>

--- a/data/50001592 - VITA EXPRESS INC (Venezuela).xlsx
+++ b/data/50001592 - VITA EXPRESS INC (Venezuela).xlsx
@@ -4522,7 +4522,7 @@
       </c>
       <c r="C50" s="6"/>
       <c r="D50" s="5">
-        <v>46252.55284988426</v>
+        <v>46252.6039508449</v>
       </c>
       <c r="E50" s="6" t="s">
         <v>170</v>

--- a/data/50001592 - VITA EXPRESS INC (Venezuela).xlsx
+++ b/data/50001592 - VITA EXPRESS INC (Venezuela).xlsx
@@ -4522,7 +4522,7 @@
       </c>
       <c r="C50" s="6"/>
       <c r="D50" s="5">
-        <v>46252.6039508449</v>
+        <v>46252.97856043981</v>
       </c>
       <c r="E50" s="6" t="s">
         <v>170</v>

--- a/data/50001592 - VITA EXPRESS INC (Venezuela).xlsx
+++ b/data/50001592 - VITA EXPRESS INC (Venezuela).xlsx
@@ -11,7 +11,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1814" uniqueCount="409">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1814" uniqueCount="410">
   <si>
     <t>50001592 - VITA EXPRESS INC (Venezuela)</t>
   </si>
@@ -553,6 +553,9 @@
   </si>
   <si>
     <t xml:space="preserve">Ingenieria y diseñoo:,Plano Definitivos ot 4395  </t>
+  </si>
+  <si>
+    <t>Media</t>
   </si>
   <si>
     <t>1217190619377469</t>
@@ -4522,7 +4525,7 @@
       </c>
       <c r="C50" s="6"/>
       <c r="D50" s="5">
-        <v>46252.97856043981</v>
+        <v>46255.20385244213</v>
       </c>
       <c r="E50" s="6" t="s">
         <v>170</v>
@@ -4566,8 +4569,8 @@
       <c r="R50" s="5">
         <v>46245</v>
       </c>
-      <c r="S50" s="7" t="s">
-        <v>42</v>
+      <c r="S50" s="12" t="s">
+        <v>174</v>
       </c>
       <c r="T50" s="6">
         <v>0</v>
@@ -4578,7 +4581,7 @@
     </row>
     <row r="51" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A51" s="8" t="s">
-        <v>174</v>
+        <v>175</v>
       </c>
       <c r="B51" s="9">
         <v>46239.574207060185</v>
@@ -4588,7 +4591,7 @@
         <v>46251.97138391204</v>
       </c>
       <c r="E51" s="10" t="s">
-        <v>175</v>
+        <v>176</v>
       </c>
       <c r="F51" s="10" t="s">
         <v>26</v>
@@ -4618,10 +4621,10 @@
         <v>167</v>
       </c>
       <c r="O51" s="10" t="s">
-        <v>176</v>
+        <v>177</v>
       </c>
       <c r="P51" s="10" t="s">
-        <v>177</v>
+        <v>178</v>
       </c>
       <c r="Q51" s="9">
         <v>46315</v>
@@ -4641,7 +4644,7 @@
     </row>
     <row r="52" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A52" s="4" t="s">
-        <v>178</v>
+        <v>179</v>
       </c>
       <c r="B52" s="5">
         <v>46239.57421190973</v>
@@ -4657,10 +4660,10 @@
         <v>26</v>
       </c>
       <c r="G52" s="6" t="s">
-        <v>179</v>
+        <v>180</v>
       </c>
       <c r="H52" s="6" t="s">
-        <v>180</v>
+        <v>181</v>
       </c>
       <c r="I52" s="5">
         <v>46316</v>
@@ -4681,10 +4684,10 @@
         <v>167</v>
       </c>
       <c r="O52" s="6" t="s">
-        <v>175</v>
+        <v>176</v>
       </c>
       <c r="P52" s="6" t="s">
-        <v>181</v>
+        <v>182</v>
       </c>
       <c r="Q52" s="5">
         <v>46316</v>
@@ -4704,7 +4707,7 @@
     </row>
     <row r="53" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A53" s="8" t="s">
-        <v>182</v>
+        <v>183</v>
       </c>
       <c r="B53" s="9">
         <v>46239.57422061343</v>
@@ -4714,16 +4717,16 @@
         <v>46240.59657887732</v>
       </c>
       <c r="E53" s="10" t="s">
-        <v>183</v>
+        <v>184</v>
       </c>
       <c r="F53" s="10" t="s">
         <v>26</v>
       </c>
       <c r="G53" s="10" t="s">
-        <v>184</v>
+        <v>185</v>
       </c>
       <c r="H53" s="10" t="s">
-        <v>185</v>
+        <v>186</v>
       </c>
       <c r="I53" s="9">
         <v>46405</v>
@@ -4744,7 +4747,7 @@
         <v>167</v>
       </c>
       <c r="O53" s="10" t="s">
-        <v>186</v>
+        <v>187</v>
       </c>
       <c r="P53" s="10" t="s">
         <v>167</v>
@@ -4767,7 +4770,7 @@
     </row>
     <row r="54" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A54" s="4" t="s">
-        <v>187</v>
+        <v>188</v>
       </c>
       <c r="B54" s="5">
         <v>46239.57422527778</v>
@@ -4777,16 +4780,16 @@
         <v>46240.58711</v>
       </c>
       <c r="E54" s="6" t="s">
-        <v>188</v>
+        <v>189</v>
       </c>
       <c r="F54" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G54" s="6" t="s">
-        <v>184</v>
+        <v>185</v>
       </c>
       <c r="H54" s="6" t="s">
-        <v>185</v>
+        <v>186</v>
       </c>
       <c r="I54" s="5">
         <v>46405</v>
@@ -4804,13 +4807,13 @@
         <v>26</v>
       </c>
       <c r="N54" s="6" t="s">
-        <v>183</v>
+        <v>184</v>
       </c>
       <c r="O54" s="6" t="s">
-        <v>188</v>
+        <v>189</v>
       </c>
       <c r="P54" s="6" t="s">
-        <v>189</v>
+        <v>190</v>
       </c>
       <c r="Q54" s="6"/>
       <c r="R54" s="6"/>
@@ -4820,7 +4823,7 @@
     </row>
     <row r="55" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A55" s="8" t="s">
-        <v>190</v>
+        <v>191</v>
       </c>
       <c r="B55" s="9">
         <v>46239.5742288426</v>
@@ -4830,16 +4833,16 @@
         <v>46240.58710615741</v>
       </c>
       <c r="E55" s="10" t="s">
-        <v>188</v>
+        <v>189</v>
       </c>
       <c r="F55" s="10" t="s">
         <v>26</v>
       </c>
       <c r="G55" s="10" t="s">
-        <v>184</v>
+        <v>185</v>
       </c>
       <c r="H55" s="10" t="s">
-        <v>185</v>
+        <v>186</v>
       </c>
       <c r="I55" s="9">
         <v>46405</v>
@@ -4857,13 +4860,13 @@
         <v>26</v>
       </c>
       <c r="N55" s="10" t="s">
-        <v>183</v>
+        <v>184</v>
       </c>
       <c r="O55" s="10" t="s">
-        <v>188</v>
+        <v>189</v>
       </c>
       <c r="P55" s="10" t="s">
-        <v>191</v>
+        <v>192</v>
       </c>
       <c r="Q55" s="10"/>
       <c r="R55" s="10"/>
@@ -4873,7 +4876,7 @@
     </row>
     <row r="56" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A56" s="4" t="s">
-        <v>192</v>
+        <v>193</v>
       </c>
       <c r="B56" s="5">
         <v>46239.57430761574</v>
@@ -4883,16 +4886,16 @@
         <v>46240.58710263889</v>
       </c>
       <c r="E56" s="6" t="s">
-        <v>188</v>
+        <v>189</v>
       </c>
       <c r="F56" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G56" s="6" t="s">
-        <v>184</v>
+        <v>185</v>
       </c>
       <c r="H56" s="6" t="s">
-        <v>185</v>
+        <v>186</v>
       </c>
       <c r="I56" s="5">
         <v>46405</v>
@@ -4910,13 +4913,13 @@
         <v>26</v>
       </c>
       <c r="N56" s="6" t="s">
-        <v>183</v>
+        <v>184</v>
       </c>
       <c r="O56" s="6" t="s">
-        <v>188</v>
+        <v>189</v>
       </c>
       <c r="P56" s="6" t="s">
-        <v>189</v>
+        <v>190</v>
       </c>
       <c r="Q56" s="6"/>
       <c r="R56" s="6"/>
@@ -4926,7 +4929,7 @@
     </row>
     <row r="57" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A57" s="8" t="s">
-        <v>193</v>
+        <v>194</v>
       </c>
       <c r="B57" s="9">
         <v>46239.66388140046</v>
@@ -4936,16 +4939,16 @@
         <v>46240.587098715274</v>
       </c>
       <c r="E57" s="10" t="s">
-        <v>188</v>
+        <v>189</v>
       </c>
       <c r="F57" s="10" t="s">
         <v>26</v>
       </c>
       <c r="G57" s="10" t="s">
-        <v>184</v>
+        <v>185</v>
       </c>
       <c r="H57" s="10" t="s">
-        <v>185</v>
+        <v>186</v>
       </c>
       <c r="I57" s="9">
         <v>46405</v>
@@ -4963,10 +4966,10 @@
         <v>26</v>
       </c>
       <c r="N57" s="10" t="s">
-        <v>183</v>
+        <v>184</v>
       </c>
       <c r="O57" s="10" t="s">
-        <v>194</v>
+        <v>195</v>
       </c>
       <c r="P57" s="10" t="s">
         <v>26</v>
@@ -4979,7 +4982,7 @@
     </row>
     <row r="58" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A58" s="4" t="s">
-        <v>195</v>
+        <v>196</v>
       </c>
       <c r="B58" s="5">
         <v>46239.57431149305</v>
@@ -4989,7 +4992,7 @@
         <v>46239.7159622801</v>
       </c>
       <c r="E58" s="6" t="s">
-        <v>196</v>
+        <v>197</v>
       </c>
       <c r="F58" s="6" t="s">
         <v>25</v>
@@ -5013,7 +5016,7 @@
         <v>26</v>
       </c>
       <c r="O58" s="6" t="s">
-        <v>197</v>
+        <v>198</v>
       </c>
       <c r="P58" s="6" t="s">
         <v>26</v>
@@ -5026,7 +5029,7 @@
     </row>
     <row r="59" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A59" s="8" t="s">
-        <v>198</v>
+        <v>199</v>
       </c>
       <c r="B59" s="9">
         <v>46239.57431462963</v>
@@ -5036,16 +5039,16 @@
         <v>46240.587207523145</v>
       </c>
       <c r="E59" s="10" t="s">
-        <v>199</v>
+        <v>200</v>
       </c>
       <c r="F59" s="10" t="s">
         <v>26</v>
       </c>
       <c r="G59" s="10" t="s">
-        <v>200</v>
+        <v>201</v>
       </c>
       <c r="H59" s="10" t="s">
-        <v>201</v>
+        <v>202</v>
       </c>
       <c r="I59" s="9">
         <v>46332</v>
@@ -5063,13 +5066,13 @@
         <v>26</v>
       </c>
       <c r="N59" s="10" t="s">
-        <v>196</v>
+        <v>197</v>
       </c>
       <c r="O59" s="10" t="s">
         <v>112</v>
       </c>
       <c r="P59" s="10" t="s">
-        <v>202</v>
+        <v>203</v>
       </c>
       <c r="Q59" s="9">
         <v>46335</v>
@@ -5089,7 +5092,7 @@
     </row>
     <row r="60" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A60" s="4" t="s">
-        <v>203</v>
+        <v>204</v>
       </c>
       <c r="B60" s="5">
         <v>46239.57431895833</v>
@@ -5099,16 +5102,16 @@
         <v>46240.587203958334</v>
       </c>
       <c r="E60" s="6" t="s">
-        <v>204</v>
+        <v>205</v>
       </c>
       <c r="F60" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G60" s="6" t="s">
-        <v>200</v>
+        <v>201</v>
       </c>
       <c r="H60" s="6" t="s">
-        <v>201</v>
+        <v>202</v>
       </c>
       <c r="I60" s="5">
         <v>46332</v>
@@ -5126,13 +5129,13 @@
         <v>26</v>
       </c>
       <c r="N60" s="6" t="s">
-        <v>196</v>
+        <v>197</v>
       </c>
       <c r="O60" s="6" t="s">
         <v>120</v>
       </c>
       <c r="P60" s="6" t="s">
-        <v>205</v>
+        <v>206</v>
       </c>
       <c r="Q60" s="5">
         <v>46335</v>
@@ -5152,7 +5155,7 @@
     </row>
     <row r="61" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A61" s="8" t="s">
-        <v>206</v>
+        <v>207</v>
       </c>
       <c r="B61" s="9">
         <v>46239.57432314815</v>
@@ -5162,16 +5165,16 @@
         <v>46240.587200486116</v>
       </c>
       <c r="E61" s="10" t="s">
-        <v>207</v>
+        <v>208</v>
       </c>
       <c r="F61" s="10" t="s">
         <v>26</v>
       </c>
       <c r="G61" s="10" t="s">
-        <v>200</v>
+        <v>201</v>
       </c>
       <c r="H61" s="10" t="s">
-        <v>201</v>
+        <v>202</v>
       </c>
       <c r="I61" s="9">
         <v>46332</v>
@@ -5189,13 +5192,13 @@
         <v>26</v>
       </c>
       <c r="N61" s="10" t="s">
-        <v>196</v>
+        <v>197</v>
       </c>
       <c r="O61" s="10" t="s">
         <v>128</v>
       </c>
       <c r="P61" s="10" t="s">
-        <v>208</v>
+        <v>209</v>
       </c>
       <c r="Q61" s="9">
         <v>46335</v>
@@ -5215,7 +5218,7 @@
     </row>
     <row r="62" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A62" s="4" t="s">
-        <v>209</v>
+        <v>210</v>
       </c>
       <c r="B62" s="5">
         <v>46239.57432760416</v>
@@ -5225,7 +5228,7 @@
         <v>46240.58727070602</v>
       </c>
       <c r="E62" s="6" t="s">
-        <v>210</v>
+        <v>211</v>
       </c>
       <c r="F62" s="6" t="s">
         <v>26</v>
@@ -5252,13 +5255,13 @@
         <v>26</v>
       </c>
       <c r="N62" s="6" t="s">
-        <v>196</v>
+        <v>197</v>
       </c>
       <c r="O62" s="6" t="s">
-        <v>199</v>
+        <v>200</v>
       </c>
       <c r="P62" s="6" t="s">
-        <v>211</v>
+        <v>212</v>
       </c>
       <c r="Q62" s="5">
         <v>46337</v>
@@ -5278,7 +5281,7 @@
     </row>
     <row r="63" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A63" s="8" t="s">
-        <v>212</v>
+        <v>213</v>
       </c>
       <c r="B63" s="9">
         <v>46239.574331689815</v>
@@ -5288,7 +5291,7 @@
         <v>46240.58726702546</v>
       </c>
       <c r="E63" s="10" t="s">
-        <v>213</v>
+        <v>214</v>
       </c>
       <c r="F63" s="10" t="s">
         <v>26</v>
@@ -5315,13 +5318,13 @@
         <v>26</v>
       </c>
       <c r="N63" s="10" t="s">
-        <v>196</v>
+        <v>197</v>
       </c>
       <c r="O63" s="10" t="s">
-        <v>204</v>
+        <v>205</v>
       </c>
       <c r="P63" s="10" t="s">
-        <v>211</v>
+        <v>212</v>
       </c>
       <c r="Q63" s="9">
         <v>46337</v>
@@ -5341,7 +5344,7 @@
     </row>
     <row r="64" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A64" s="4" t="s">
-        <v>214</v>
+        <v>215</v>
       </c>
       <c r="B64" s="5">
         <v>46239.57433570602</v>
@@ -5351,7 +5354,7 @@
         <v>46240.58726326389</v>
       </c>
       <c r="E64" s="6" t="s">
-        <v>215</v>
+        <v>216</v>
       </c>
       <c r="F64" s="6" t="s">
         <v>26</v>
@@ -5378,13 +5381,13 @@
         <v>26</v>
       </c>
       <c r="N64" s="6" t="s">
-        <v>196</v>
+        <v>197</v>
       </c>
       <c r="O64" s="6" t="s">
-        <v>207</v>
+        <v>208</v>
       </c>
       <c r="P64" s="6" t="s">
-        <v>216</v>
+        <v>217</v>
       </c>
       <c r="Q64" s="5">
         <v>46337</v>
@@ -5404,7 +5407,7 @@
     </row>
     <row r="65" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A65" s="8" t="s">
-        <v>217</v>
+        <v>218</v>
       </c>
       <c r="B65" s="9">
         <v>46239.574339363426</v>
@@ -5414,7 +5417,7 @@
         <v>46240.57123085648</v>
       </c>
       <c r="E65" s="10" t="s">
-        <v>218</v>
+        <v>219</v>
       </c>
       <c r="F65" s="10" t="s">
         <v>25</v>
@@ -5438,7 +5441,7 @@
         <v>26</v>
       </c>
       <c r="O65" s="10" t="s">
-        <v>219</v>
+        <v>220</v>
       </c>
       <c r="P65" s="10" t="s">
         <v>26</v>
@@ -5451,7 +5454,7 @@
     </row>
     <row r="66" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A66" s="4" t="s">
-        <v>220</v>
+        <v>221</v>
       </c>
       <c r="B66" s="5">
         <v>46239.57434170139</v>
@@ -5461,16 +5464,16 @@
         <v>46240.59315164352</v>
       </c>
       <c r="E66" s="6" t="s">
-        <v>221</v>
+        <v>222</v>
       </c>
       <c r="F66" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G66" s="6" t="s">
-        <v>222</v>
+        <v>223</v>
       </c>
       <c r="H66" s="6" t="s">
-        <v>223</v>
+        <v>224</v>
       </c>
       <c r="I66" s="5">
         <v>46338</v>
@@ -5488,13 +5491,13 @@
         <v>26</v>
       </c>
       <c r="N66" s="6" t="s">
-        <v>218</v>
+        <v>219</v>
       </c>
       <c r="O66" s="6" t="s">
         <v>91</v>
       </c>
       <c r="P66" s="6" t="s">
-        <v>224</v>
+        <v>225</v>
       </c>
       <c r="Q66" s="5">
         <v>46346</v>
@@ -5514,7 +5517,7 @@
     </row>
     <row r="67" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A67" s="8" t="s">
-        <v>225</v>
+        <v>226</v>
       </c>
       <c r="B67" s="9">
         <v>46239.574346504625</v>
@@ -5524,16 +5527,16 @@
         <v>46240.593254861116</v>
       </c>
       <c r="E67" s="10" t="s">
-        <v>226</v>
+        <v>227</v>
       </c>
       <c r="F67" s="10" t="s">
         <v>26</v>
       </c>
       <c r="G67" s="10" t="s">
-        <v>222</v>
+        <v>223</v>
       </c>
       <c r="H67" s="10" t="s">
-        <v>223</v>
+        <v>224</v>
       </c>
       <c r="I67" s="9">
         <v>46349</v>
@@ -5551,13 +5554,13 @@
         <v>26</v>
       </c>
       <c r="N67" s="10" t="s">
-        <v>218</v>
+        <v>219</v>
       </c>
       <c r="O67" s="10" t="s">
-        <v>186</v>
+        <v>187</v>
       </c>
       <c r="P67" s="10" t="s">
-        <v>218</v>
+        <v>219</v>
       </c>
       <c r="Q67" s="9">
         <v>46367</v>
@@ -5577,7 +5580,7 @@
     </row>
     <row r="68" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A68" s="4" t="s">
-        <v>227</v>
+        <v>228</v>
       </c>
       <c r="B68" s="5">
         <v>46239.57435601852</v>
@@ -5587,16 +5590,16 @@
         <v>46240.58742517361</v>
       </c>
       <c r="E68" s="6" t="s">
-        <v>188</v>
+        <v>189</v>
       </c>
       <c r="F68" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G68" s="6" t="s">
-        <v>222</v>
+        <v>223</v>
       </c>
       <c r="H68" s="6" t="s">
-        <v>223</v>
+        <v>224</v>
       </c>
       <c r="I68" s="5">
         <v>46349</v>
@@ -5614,13 +5617,13 @@
         <v>26</v>
       </c>
       <c r="N68" s="6" t="s">
-        <v>226</v>
+        <v>227</v>
       </c>
       <c r="O68" s="6" t="s">
-        <v>228</v>
+        <v>229</v>
       </c>
       <c r="P68" s="6" t="s">
-        <v>229</v>
+        <v>230</v>
       </c>
       <c r="Q68" s="6"/>
       <c r="R68" s="6"/>
@@ -5630,7 +5633,7 @@
     </row>
     <row r="69" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A69" s="8" t="s">
-        <v>230</v>
+        <v>231</v>
       </c>
       <c r="B69" s="9">
         <v>46239.574361817125</v>
@@ -5640,16 +5643,16 @@
         <v>46240.58742163195</v>
       </c>
       <c r="E69" s="10" t="s">
-        <v>188</v>
+        <v>189</v>
       </c>
       <c r="F69" s="10" t="s">
         <v>26</v>
       </c>
       <c r="G69" s="10" t="s">
-        <v>222</v>
+        <v>223</v>
       </c>
       <c r="H69" s="10" t="s">
-        <v>223</v>
+        <v>224</v>
       </c>
       <c r="I69" s="9">
         <v>46349</v>
@@ -5667,13 +5670,13 @@
         <v>26</v>
       </c>
       <c r="N69" s="10" t="s">
-        <v>226</v>
+        <v>227</v>
       </c>
       <c r="O69" s="10" t="s">
-        <v>231</v>
+        <v>232</v>
       </c>
       <c r="P69" s="10" t="s">
-        <v>229</v>
+        <v>230</v>
       </c>
       <c r="Q69" s="10"/>
       <c r="R69" s="10"/>
@@ -5683,7 +5686,7 @@
     </row>
     <row r="70" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A70" s="4" t="s">
-        <v>232</v>
+        <v>233</v>
       </c>
       <c r="B70" s="5">
         <v>46239.574366967594</v>
@@ -5693,16 +5696,16 @@
         <v>46240.58741825231</v>
       </c>
       <c r="E70" s="6" t="s">
-        <v>188</v>
+        <v>189</v>
       </c>
       <c r="F70" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G70" s="6" t="s">
-        <v>222</v>
+        <v>223</v>
       </c>
       <c r="H70" s="6" t="s">
-        <v>223</v>
+        <v>224</v>
       </c>
       <c r="I70" s="5">
         <v>46349</v>
@@ -5720,13 +5723,13 @@
         <v>26</v>
       </c>
       <c r="N70" s="6" t="s">
-        <v>226</v>
+        <v>227</v>
       </c>
       <c r="O70" s="6" t="s">
-        <v>233</v>
+        <v>234</v>
       </c>
       <c r="P70" s="6" t="s">
-        <v>234</v>
+        <v>235</v>
       </c>
       <c r="Q70" s="6"/>
       <c r="R70" s="6"/>
@@ -5736,7 +5739,7 @@
     </row>
     <row r="71" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A71" s="8" t="s">
-        <v>235</v>
+        <v>236</v>
       </c>
       <c r="B71" s="9">
         <v>46239.65279153935</v>
@@ -5746,16 +5749,16 @@
         <v>46240.58741491898</v>
       </c>
       <c r="E71" s="10" t="s">
-        <v>188</v>
+        <v>189</v>
       </c>
       <c r="F71" s="10" t="s">
         <v>26</v>
       </c>
       <c r="G71" s="10" t="s">
-        <v>222</v>
+        <v>223</v>
       </c>
       <c r="H71" s="10" t="s">
-        <v>223</v>
+        <v>224</v>
       </c>
       <c r="I71" s="9">
         <v>46349</v>
@@ -5773,13 +5776,13 @@
         <v>26</v>
       </c>
       <c r="N71" s="10" t="s">
-        <v>226</v>
+        <v>227</v>
       </c>
       <c r="O71" s="10" t="s">
-        <v>221</v>
+        <v>222</v>
       </c>
       <c r="P71" s="10" t="s">
-        <v>188</v>
+        <v>189</v>
       </c>
       <c r="Q71" s="10"/>
       <c r="R71" s="10"/>
@@ -5789,7 +5792,7 @@
     </row>
     <row r="72" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A72" s="4" t="s">
-        <v>236</v>
+        <v>237</v>
       </c>
       <c r="B72" s="5">
         <v>46239.57437221065</v>
@@ -5799,7 +5802,7 @@
         <v>46240.59335420139</v>
       </c>
       <c r="E72" s="6" t="s">
-        <v>237</v>
+        <v>238</v>
       </c>
       <c r="F72" s="6" t="s">
         <v>26</v>
@@ -5826,13 +5829,13 @@
         <v>26</v>
       </c>
       <c r="N72" s="6" t="s">
-        <v>218</v>
+        <v>219</v>
       </c>
       <c r="O72" s="6" t="s">
-        <v>186</v>
+        <v>187</v>
       </c>
       <c r="P72" s="6" t="s">
-        <v>218</v>
+        <v>219</v>
       </c>
       <c r="Q72" s="5">
         <v>46370</v>
@@ -5852,7 +5855,7 @@
     </row>
     <row r="73" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A73" s="8" t="s">
-        <v>238</v>
+        <v>239</v>
       </c>
       <c r="B73" s="9">
         <v>46239.574375833334</v>
@@ -5862,7 +5865,7 @@
         <v>46240.587564953705</v>
       </c>
       <c r="E73" s="10" t="s">
-        <v>188</v>
+        <v>189</v>
       </c>
       <c r="F73" s="10" t="s">
         <v>26</v>
@@ -5889,13 +5892,13 @@
         <v>26</v>
       </c>
       <c r="N73" s="10" t="s">
-        <v>237</v>
+        <v>238</v>
       </c>
       <c r="O73" s="10" t="s">
-        <v>239</v>
+        <v>240</v>
       </c>
       <c r="P73" s="10" t="s">
-        <v>240</v>
+        <v>241</v>
       </c>
       <c r="Q73" s="10"/>
       <c r="R73" s="10"/>
@@ -5905,7 +5908,7 @@
     </row>
     <row r="74" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A74" s="4" t="s">
-        <v>241</v>
+        <v>242</v>
       </c>
       <c r="B74" s="5">
         <v>46239.57437981482</v>
@@ -5915,7 +5918,7 @@
         <v>46240.587560659726</v>
       </c>
       <c r="E74" s="6" t="s">
-        <v>188</v>
+        <v>189</v>
       </c>
       <c r="F74" s="6" t="s">
         <v>26</v>
@@ -5942,13 +5945,13 @@
         <v>26</v>
       </c>
       <c r="N74" s="6" t="s">
-        <v>237</v>
+        <v>238</v>
       </c>
       <c r="O74" s="6" t="s">
-        <v>239</v>
+        <v>240</v>
       </c>
       <c r="P74" s="6" t="s">
-        <v>242</v>
+        <v>243</v>
       </c>
       <c r="Q74" s="6"/>
       <c r="R74" s="6"/>
@@ -5958,7 +5961,7 @@
     </row>
     <row r="75" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A75" s="8" t="s">
-        <v>243</v>
+        <v>244</v>
       </c>
       <c r="B75" s="9">
         <v>46239.574383750005</v>
@@ -5968,7 +5971,7 @@
         <v>46240.587557210645</v>
       </c>
       <c r="E75" s="10" t="s">
-        <v>188</v>
+        <v>189</v>
       </c>
       <c r="F75" s="10" t="s">
         <v>26</v>
@@ -5995,13 +5998,13 @@
         <v>26</v>
       </c>
       <c r="N75" s="10" t="s">
-        <v>237</v>
+        <v>238</v>
       </c>
       <c r="O75" s="10" t="s">
-        <v>244</v>
+        <v>245</v>
       </c>
       <c r="P75" s="10" t="s">
-        <v>242</v>
+        <v>243</v>
       </c>
       <c r="Q75" s="10"/>
       <c r="R75" s="10"/>
@@ -6011,7 +6014,7 @@
     </row>
     <row r="76" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A76" s="4" t="s">
-        <v>245</v>
+        <v>246</v>
       </c>
       <c r="B76" s="5">
         <v>46239.65287751157</v>
@@ -6021,7 +6024,7 @@
         <v>46240.5875534838</v>
       </c>
       <c r="E76" s="6" t="s">
-        <v>188</v>
+        <v>189</v>
       </c>
       <c r="F76" s="6" t="s">
         <v>26</v>
@@ -6048,13 +6051,13 @@
         <v>26</v>
       </c>
       <c r="N76" s="6" t="s">
-        <v>237</v>
+        <v>238</v>
       </c>
       <c r="O76" s="6" t="s">
-        <v>188</v>
+        <v>189</v>
       </c>
       <c r="P76" s="6" t="s">
-        <v>188</v>
+        <v>189</v>
       </c>
       <c r="Q76" s="6"/>
       <c r="R76" s="6"/>
@@ -6064,7 +6067,7 @@
     </row>
     <row r="77" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A77" s="8" t="s">
-        <v>246</v>
+        <v>247</v>
       </c>
       <c r="B77" s="9">
         <v>46239.574387534725</v>
@@ -6074,7 +6077,7 @@
         <v>46240.57208707176</v>
       </c>
       <c r="E77" s="10" t="s">
-        <v>247</v>
+        <v>248</v>
       </c>
       <c r="F77" s="10" t="s">
         <v>25</v>
@@ -6098,7 +6101,7 @@
         <v>26</v>
       </c>
       <c r="O77" s="10" t="s">
-        <v>248</v>
+        <v>249</v>
       </c>
       <c r="P77" s="10" t="s">
         <v>26</v>
@@ -6111,7 +6114,7 @@
     </row>
     <row r="78" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A78" s="4" t="s">
-        <v>249</v>
+        <v>250</v>
       </c>
       <c r="B78" s="5">
         <v>46239.57438989583</v>
@@ -6121,16 +6124,16 @@
         <v>46247.20311761574</v>
       </c>
       <c r="E78" s="6" t="s">
-        <v>250</v>
+        <v>251</v>
       </c>
       <c r="F78" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G78" s="6" t="s">
-        <v>200</v>
+        <v>201</v>
       </c>
       <c r="H78" s="6" t="s">
-        <v>201</v>
+        <v>202</v>
       </c>
       <c r="I78" s="5">
         <v>46245</v>
@@ -6148,13 +6151,13 @@
         <v>26</v>
       </c>
       <c r="N78" s="6" t="s">
-        <v>247</v>
+        <v>248</v>
       </c>
       <c r="O78" s="6" t="s">
         <v>74</v>
       </c>
       <c r="P78" s="6" t="s">
-        <v>251</v>
+        <v>252</v>
       </c>
       <c r="Q78" s="5">
         <v>46246</v>
@@ -6174,7 +6177,7 @@
     </row>
     <row r="79" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A79" s="8" t="s">
-        <v>252</v>
+        <v>253</v>
       </c>
       <c r="B79" s="9">
         <v>46239.57439460648</v>
@@ -6184,16 +6187,16 @@
         <v>46247.2031178125</v>
       </c>
       <c r="E79" s="10" t="s">
-        <v>253</v>
+        <v>254</v>
       </c>
       <c r="F79" s="10" t="s">
         <v>26</v>
       </c>
       <c r="G79" s="10" t="s">
-        <v>200</v>
+        <v>201</v>
       </c>
       <c r="H79" s="10" t="s">
-        <v>201</v>
+        <v>202</v>
       </c>
       <c r="I79" s="9">
         <v>46245</v>
@@ -6211,13 +6214,13 @@
         <v>26</v>
       </c>
       <c r="N79" s="10" t="s">
-        <v>247</v>
+        <v>248</v>
       </c>
       <c r="O79" s="10" t="s">
         <v>79</v>
       </c>
       <c r="P79" s="10" t="s">
-        <v>251</v>
+        <v>252</v>
       </c>
       <c r="Q79" s="9">
         <v>46246</v>
@@ -6237,7 +6240,7 @@
     </row>
     <row r="80" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A80" s="4" t="s">
-        <v>254</v>
+        <v>255</v>
       </c>
       <c r="B80" s="5">
         <v>46239.5743990162</v>
@@ -6247,16 +6250,16 @@
         <v>46240.58768672454</v>
       </c>
       <c r="E80" s="6" t="s">
-        <v>255</v>
+        <v>256</v>
       </c>
       <c r="F80" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G80" s="6" t="s">
-        <v>200</v>
+        <v>201</v>
       </c>
       <c r="H80" s="6" t="s">
-        <v>201</v>
+        <v>202</v>
       </c>
       <c r="I80" s="5">
         <v>46372</v>
@@ -6274,13 +6277,13 @@
         <v>26</v>
       </c>
       <c r="N80" s="6" t="s">
-        <v>247</v>
+        <v>248</v>
       </c>
       <c r="O80" s="6" t="s">
         <v>153</v>
       </c>
       <c r="P80" s="6" t="s">
-        <v>256</v>
+        <v>257</v>
       </c>
       <c r="Q80" s="5">
         <v>46372</v>
@@ -6300,7 +6303,7 @@
     </row>
     <row r="81" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A81" s="8" t="s">
-        <v>257</v>
+        <v>258</v>
       </c>
       <c r="B81" s="9">
         <v>46239.59988357639</v>
@@ -6316,10 +6319,10 @@
         <v>26</v>
       </c>
       <c r="G81" s="10" t="s">
-        <v>200</v>
+        <v>201</v>
       </c>
       <c r="H81" s="10" t="s">
-        <v>201</v>
+        <v>202</v>
       </c>
       <c r="I81" s="9">
         <v>46302</v>
@@ -6337,7 +6340,7 @@
         <v>26</v>
       </c>
       <c r="N81" s="10" t="s">
-        <v>247</v>
+        <v>248</v>
       </c>
       <c r="O81" s="10" t="s">
         <v>164</v>
@@ -6363,7 +6366,7 @@
     </row>
     <row r="82" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A82" s="4" t="s">
-        <v>258</v>
+        <v>259</v>
       </c>
       <c r="B82" s="5">
         <v>46239.574403680555</v>
@@ -6373,7 +6376,7 @@
         <v>46240.58015300926</v>
       </c>
       <c r="E82" s="6" t="s">
-        <v>259</v>
+        <v>260</v>
       </c>
       <c r="F82" s="6" t="s">
         <v>25</v>
@@ -6397,7 +6400,7 @@
         <v>26</v>
       </c>
       <c r="O82" s="6" t="s">
-        <v>260</v>
+        <v>261</v>
       </c>
       <c r="P82" s="6" t="s">
         <v>26</v>
@@ -6410,7 +6413,7 @@
     </row>
     <row r="83" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A83" s="8" t="s">
-        <v>261</v>
+        <v>262</v>
       </c>
       <c r="B83" s="9">
         <v>46239.57440625</v>
@@ -6420,7 +6423,7 @@
         <v>46240.593524502314</v>
       </c>
       <c r="E83" s="10" t="s">
-        <v>262</v>
+        <v>263</v>
       </c>
       <c r="F83" s="10" t="s">
         <v>26</v>
@@ -6447,13 +6450,13 @@
         <v>26</v>
       </c>
       <c r="N83" s="10" t="s">
-        <v>259</v>
+        <v>260</v>
       </c>
       <c r="O83" s="10" t="s">
-        <v>186</v>
+        <v>187</v>
       </c>
       <c r="P83" s="10" t="s">
-        <v>259</v>
+        <v>260</v>
       </c>
       <c r="Q83" s="9">
         <v>46392</v>
@@ -6473,7 +6476,7 @@
     </row>
     <row r="84" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A84" s="4" t="s">
-        <v>263</v>
+        <v>264</v>
       </c>
       <c r="B84" s="5">
         <v>46239.57441001157</v>
@@ -6483,7 +6486,7 @@
         <v>46240.58779871528</v>
       </c>
       <c r="E84" s="6" t="s">
-        <v>188</v>
+        <v>189</v>
       </c>
       <c r="F84" s="6" t="s">
         <v>26</v>
@@ -6510,13 +6513,13 @@
         <v>26</v>
       </c>
       <c r="N84" s="6" t="s">
-        <v>262</v>
+        <v>263</v>
       </c>
       <c r="O84" s="6" t="s">
-        <v>188</v>
+        <v>189</v>
       </c>
       <c r="P84" s="6" t="s">
-        <v>264</v>
+        <v>265</v>
       </c>
       <c r="Q84" s="6"/>
       <c r="R84" s="6"/>
@@ -6526,7 +6529,7 @@
     </row>
     <row r="85" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A85" s="8" t="s">
-        <v>265</v>
+        <v>266</v>
       </c>
       <c r="B85" s="9">
         <v>46239.57441357639</v>
@@ -6536,7 +6539,7 @@
         <v>46240.58779524306</v>
       </c>
       <c r="E85" s="10" t="s">
-        <v>188</v>
+        <v>189</v>
       </c>
       <c r="F85" s="10" t="s">
         <v>26</v>
@@ -6563,13 +6566,13 @@
         <v>26</v>
       </c>
       <c r="N85" s="10" t="s">
-        <v>262</v>
+        <v>263</v>
       </c>
       <c r="O85" s="10" t="s">
-        <v>188</v>
+        <v>189</v>
       </c>
       <c r="P85" s="10" t="s">
-        <v>264</v>
+        <v>265</v>
       </c>
       <c r="Q85" s="10"/>
       <c r="R85" s="10"/>
@@ -6579,7 +6582,7 @@
     </row>
     <row r="86" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A86" s="4" t="s">
-        <v>266</v>
+        <v>267</v>
       </c>
       <c r="B86" s="5">
         <v>46239.57441700231</v>
@@ -6589,7 +6592,7 @@
         <v>46240.58779197917</v>
       </c>
       <c r="E86" s="6" t="s">
-        <v>188</v>
+        <v>189</v>
       </c>
       <c r="F86" s="6" t="s">
         <v>26</v>
@@ -6616,13 +6619,13 @@
         <v>26</v>
       </c>
       <c r="N86" s="6" t="s">
-        <v>262</v>
+        <v>263</v>
       </c>
       <c r="O86" s="6" t="s">
-        <v>188</v>
+        <v>189</v>
       </c>
       <c r="P86" s="6" t="s">
-        <v>267</v>
+        <v>268</v>
       </c>
       <c r="Q86" s="6"/>
       <c r="R86" s="6"/>
@@ -6632,7 +6635,7 @@
     </row>
     <row r="87" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A87" s="8" t="s">
-        <v>268</v>
+        <v>269</v>
       </c>
       <c r="B87" s="9">
         <v>46239.65295363426</v>
@@ -6642,7 +6645,7 @@
         <v>46240.58778819445</v>
       </c>
       <c r="E87" s="10" t="s">
-        <v>188</v>
+        <v>189</v>
       </c>
       <c r="F87" s="10" t="s">
         <v>26</v>
@@ -6669,13 +6672,13 @@
         <v>26</v>
       </c>
       <c r="N87" s="10" t="s">
-        <v>262</v>
+        <v>263</v>
       </c>
       <c r="O87" s="10" t="s">
-        <v>188</v>
+        <v>189</v>
       </c>
       <c r="P87" s="10" t="s">
-        <v>188</v>
+        <v>189</v>
       </c>
       <c r="Q87" s="10"/>
       <c r="R87" s="10"/>
@@ -6685,7 +6688,7 @@
     </row>
     <row r="88" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A88" s="4" t="s">
-        <v>269</v>
+        <v>270</v>
       </c>
       <c r="B88" s="5">
         <v>46239.5744203125</v>
@@ -6695,7 +6698,7 @@
         <v>46240.59358774306</v>
       </c>
       <c r="E88" s="6" t="s">
-        <v>270</v>
+        <v>271</v>
       </c>
       <c r="F88" s="6" t="s">
         <v>26</v>
@@ -6722,10 +6725,10 @@
         <v>26</v>
       </c>
       <c r="N88" s="6" t="s">
-        <v>259</v>
+        <v>260</v>
       </c>
       <c r="O88" s="6" t="s">
-        <v>186</v>
+        <v>187</v>
       </c>
       <c r="P88" s="6" t="s">
         <v>26</v>
@@ -6748,7 +6751,7 @@
     </row>
     <row r="89" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A89" s="8" t="s">
-        <v>271</v>
+        <v>272</v>
       </c>
       <c r="B89" s="9">
         <v>46239.57442366898</v>
@@ -6758,7 +6761,7 @@
         <v>46240.5880146875</v>
       </c>
       <c r="E89" s="10" t="s">
-        <v>188</v>
+        <v>189</v>
       </c>
       <c r="F89" s="10" t="s">
         <v>26</v>
@@ -6785,13 +6788,13 @@
         <v>26</v>
       </c>
       <c r="N89" s="10" t="s">
-        <v>270</v>
+        <v>271</v>
       </c>
       <c r="O89" s="10" t="s">
-        <v>272</v>
+        <v>273</v>
       </c>
       <c r="P89" s="10" t="s">
-        <v>273</v>
+        <v>274</v>
       </c>
       <c r="Q89" s="10"/>
       <c r="R89" s="10"/>
@@ -6801,7 +6804,7 @@
     </row>
     <row r="90" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A90" s="4" t="s">
-        <v>274</v>
+        <v>275</v>
       </c>
       <c r="B90" s="5">
         <v>46239.57442798611</v>
@@ -6811,7 +6814,7 @@
         <v>46240.58801127315</v>
       </c>
       <c r="E90" s="6" t="s">
-        <v>188</v>
+        <v>189</v>
       </c>
       <c r="F90" s="6" t="s">
         <v>26</v>
@@ -6838,13 +6841,13 @@
         <v>26</v>
       </c>
       <c r="N90" s="6" t="s">
-        <v>270</v>
+        <v>271</v>
       </c>
       <c r="O90" s="6" t="s">
-        <v>275</v>
+        <v>276</v>
       </c>
       <c r="P90" s="6" t="s">
-        <v>273</v>
+        <v>274</v>
       </c>
       <c r="Q90" s="6"/>
       <c r="R90" s="6"/>
@@ -6854,7 +6857,7 @@
     </row>
     <row r="91" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A91" s="8" t="s">
-        <v>276</v>
+        <v>277</v>
       </c>
       <c r="B91" s="9">
         <v>46239.57443190972</v>
@@ -6864,7 +6867,7 @@
         <v>46240.58800769676</v>
       </c>
       <c r="E91" s="10" t="s">
-        <v>188</v>
+        <v>189</v>
       </c>
       <c r="F91" s="10" t="s">
         <v>26</v>
@@ -6891,13 +6894,13 @@
         <v>26</v>
       </c>
       <c r="N91" s="10" t="s">
-        <v>270</v>
+        <v>271</v>
       </c>
       <c r="O91" s="10" t="s">
-        <v>275</v>
+        <v>276</v>
       </c>
       <c r="P91" s="10" t="s">
-        <v>273</v>
+        <v>274</v>
       </c>
       <c r="Q91" s="10"/>
       <c r="R91" s="10"/>
@@ -6907,7 +6910,7 @@
     </row>
     <row r="92" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A92" s="4" t="s">
-        <v>277</v>
+        <v>278</v>
       </c>
       <c r="B92" s="5">
         <v>46239.653021875</v>
@@ -6917,7 +6920,7 @@
         <v>46240.588004212965</v>
       </c>
       <c r="E92" s="6" t="s">
-        <v>194</v>
+        <v>195</v>
       </c>
       <c r="F92" s="6" t="s">
         <v>26</v>
@@ -6944,13 +6947,13 @@
         <v>26</v>
       </c>
       <c r="N92" s="6" t="s">
-        <v>270</v>
+        <v>271</v>
       </c>
       <c r="O92" s="6" t="s">
-        <v>275</v>
+        <v>276</v>
       </c>
       <c r="P92" s="6" t="s">
-        <v>278</v>
+        <v>279</v>
       </c>
       <c r="Q92" s="6"/>
       <c r="R92" s="6"/>
@@ -6960,7 +6963,7 @@
     </row>
     <row r="93" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A93" s="8" t="s">
-        <v>279</v>
+        <v>280</v>
       </c>
       <c r="B93" s="9">
         <v>46239.57443621528</v>
@@ -6970,7 +6973,7 @@
         <v>46246.17023978009</v>
       </c>
       <c r="E93" s="10" t="s">
-        <v>280</v>
+        <v>281</v>
       </c>
       <c r="F93" s="10" t="s">
         <v>26</v>
@@ -6997,13 +7000,13 @@
         <v>26</v>
       </c>
       <c r="N93" s="10" t="s">
-        <v>259</v>
+        <v>260</v>
       </c>
       <c r="O93" s="10" t="s">
-        <v>281</v>
+        <v>282</v>
       </c>
       <c r="P93" s="10" t="s">
-        <v>282</v>
+        <v>283</v>
       </c>
       <c r="Q93" s="9">
         <v>46245</v>
@@ -7023,7 +7026,7 @@
     </row>
     <row r="94" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A94" s="4" t="s">
-        <v>283</v>
+        <v>284</v>
       </c>
       <c r="B94" s="5">
         <v>46239.57444033565</v>
@@ -7033,7 +7036,7 @@
         <v>46240.58943795139</v>
       </c>
       <c r="E94" s="6" t="s">
-        <v>188</v>
+        <v>189</v>
       </c>
       <c r="F94" s="6" t="s">
         <v>26</v>
@@ -7060,13 +7063,13 @@
         <v>26</v>
       </c>
       <c r="N94" s="6" t="s">
-        <v>280</v>
+        <v>281</v>
       </c>
       <c r="O94" s="6" t="s">
-        <v>284</v>
+        <v>285</v>
       </c>
       <c r="P94" s="6" t="s">
-        <v>280</v>
+        <v>281</v>
       </c>
       <c r="Q94" s="6"/>
       <c r="R94" s="6"/>
@@ -7076,7 +7079,7 @@
     </row>
     <row r="95" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A95" s="8" t="s">
-        <v>285</v>
+        <v>286</v>
       </c>
       <c r="B95" s="9">
         <v>46239.57444496528</v>
@@ -7086,7 +7089,7 @@
         <v>46240.589434444446</v>
       </c>
       <c r="E95" s="10" t="s">
-        <v>188</v>
+        <v>189</v>
       </c>
       <c r="F95" s="10" t="s">
         <v>26</v>
@@ -7113,13 +7116,13 @@
         <v>26</v>
       </c>
       <c r="N95" s="10" t="s">
-        <v>280</v>
+        <v>281</v>
       </c>
       <c r="O95" s="10" t="s">
-        <v>284</v>
+        <v>285</v>
       </c>
       <c r="P95" s="10" t="s">
-        <v>286</v>
+        <v>287</v>
       </c>
       <c r="Q95" s="10"/>
       <c r="R95" s="10"/>
@@ -7129,7 +7132,7 @@
     </row>
     <row r="96" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A96" s="4" t="s">
-        <v>287</v>
+        <v>288</v>
       </c>
       <c r="B96" s="5">
         <v>46239.57445002315</v>
@@ -7139,7 +7142,7 @@
         <v>46240.58943064815</v>
       </c>
       <c r="E96" s="6" t="s">
-        <v>188</v>
+        <v>189</v>
       </c>
       <c r="F96" s="6" t="s">
         <v>26</v>
@@ -7166,13 +7169,13 @@
         <v>26</v>
       </c>
       <c r="N96" s="6" t="s">
-        <v>280</v>
+        <v>281</v>
       </c>
       <c r="O96" s="6" t="s">
-        <v>288</v>
+        <v>289</v>
       </c>
       <c r="P96" s="6" t="s">
-        <v>286</v>
+        <v>287</v>
       </c>
       <c r="Q96" s="6"/>
       <c r="R96" s="6"/>
@@ -7182,7 +7185,7 @@
     </row>
     <row r="97" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A97" s="8" t="s">
-        <v>289</v>
+        <v>290</v>
       </c>
       <c r="B97" s="9">
         <v>46239.65309570602</v>
@@ -7192,7 +7195,7 @@
         <v>46240.58942697917</v>
       </c>
       <c r="E97" s="10" t="s">
-        <v>188</v>
+        <v>189</v>
       </c>
       <c r="F97" s="10" t="s">
         <v>26</v>
@@ -7219,10 +7222,10 @@
         <v>26</v>
       </c>
       <c r="N97" s="10" t="s">
-        <v>280</v>
+        <v>281</v>
       </c>
       <c r="O97" s="10" t="s">
-        <v>188</v>
+        <v>189</v>
       </c>
       <c r="P97" s="10" t="s">
         <v>26</v>
@@ -7235,7 +7238,7 @@
     </row>
     <row r="98" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A98" s="4" t="s">
-        <v>290</v>
+        <v>291</v>
       </c>
       <c r="B98" s="5">
         <v>46239.57450405092</v>
@@ -7245,7 +7248,7 @@
         <v>46240.59374053241</v>
       </c>
       <c r="E98" s="6" t="s">
-        <v>291</v>
+        <v>292</v>
       </c>
       <c r="F98" s="6" t="s">
         <v>26</v>
@@ -7272,13 +7275,13 @@
         <v>26</v>
       </c>
       <c r="N98" s="6" t="s">
-        <v>259</v>
+        <v>260</v>
       </c>
       <c r="O98" s="6" t="s">
-        <v>186</v>
+        <v>187</v>
       </c>
       <c r="P98" s="6" t="s">
-        <v>292</v>
+        <v>293</v>
       </c>
       <c r="Q98" s="5">
         <v>46400</v>
@@ -7298,7 +7301,7 @@
     </row>
     <row r="99" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A99" s="8" t="s">
-        <v>293</v>
+        <v>294</v>
       </c>
       <c r="B99" s="9">
         <v>46239.57451060185</v>
@@ -7308,7 +7311,7 @@
         <v>46240.58955791667</v>
       </c>
       <c r="E99" s="10" t="s">
-        <v>188</v>
+        <v>189</v>
       </c>
       <c r="F99" s="10" t="s">
         <v>26</v>
@@ -7335,13 +7338,13 @@
         <v>26</v>
       </c>
       <c r="N99" s="10" t="s">
-        <v>291</v>
+        <v>292</v>
       </c>
       <c r="O99" s="10" t="s">
-        <v>188</v>
+        <v>189</v>
       </c>
       <c r="P99" s="10" t="s">
-        <v>294</v>
+        <v>295</v>
       </c>
       <c r="Q99" s="10"/>
       <c r="R99" s="10"/>
@@ -7351,7 +7354,7 @@
     </row>
     <row r="100" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A100" s="4" t="s">
-        <v>295</v>
+        <v>296</v>
       </c>
       <c r="B100" s="5">
         <v>46239.57451451389</v>
@@ -7361,7 +7364,7 @@
         <v>46240.58955409723</v>
       </c>
       <c r="E100" s="6" t="s">
-        <v>188</v>
+        <v>189</v>
       </c>
       <c r="F100" s="6" t="s">
         <v>26</v>
@@ -7388,13 +7391,13 @@
         <v>26</v>
       </c>
       <c r="N100" s="6" t="s">
-        <v>291</v>
+        <v>292</v>
       </c>
       <c r="O100" s="6" t="s">
-        <v>188</v>
+        <v>189</v>
       </c>
       <c r="P100" s="6" t="s">
-        <v>296</v>
+        <v>297</v>
       </c>
       <c r="Q100" s="6"/>
       <c r="R100" s="6"/>
@@ -7404,7 +7407,7 @@
     </row>
     <row r="101" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A101" s="8" t="s">
-        <v>297</v>
+        <v>298</v>
       </c>
       <c r="B101" s="9">
         <v>46239.57451872685</v>
@@ -7414,7 +7417,7 @@
         <v>46240.589550289355</v>
       </c>
       <c r="E101" s="10" t="s">
-        <v>188</v>
+        <v>189</v>
       </c>
       <c r="F101" s="10" t="s">
         <v>26</v>
@@ -7441,13 +7444,13 @@
         <v>26</v>
       </c>
       <c r="N101" s="10" t="s">
-        <v>291</v>
+        <v>292</v>
       </c>
       <c r="O101" s="10" t="s">
-        <v>188</v>
+        <v>189</v>
       </c>
       <c r="P101" s="10" t="s">
-        <v>296</v>
+        <v>297</v>
       </c>
       <c r="Q101" s="10"/>
       <c r="R101" s="10"/>
@@ -7457,7 +7460,7 @@
     </row>
     <row r="102" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A102" s="4" t="s">
-        <v>298</v>
+        <v>299</v>
       </c>
       <c r="B102" s="5">
         <v>46239.65315884259</v>
@@ -7467,7 +7470,7 @@
         <v>46240.58954619213</v>
       </c>
       <c r="E102" s="6" t="s">
-        <v>188</v>
+        <v>189</v>
       </c>
       <c r="F102" s="6" t="s">
         <v>26</v>
@@ -7494,10 +7497,10 @@
         <v>26</v>
       </c>
       <c r="N102" s="6" t="s">
-        <v>291</v>
+        <v>292</v>
       </c>
       <c r="O102" s="6" t="s">
-        <v>194</v>
+        <v>195</v>
       </c>
       <c r="P102" s="6" t="s">
         <v>26</v>
@@ -7510,7 +7513,7 @@
     </row>
     <row r="103" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A103" s="8" t="s">
-        <v>299</v>
+        <v>300</v>
       </c>
       <c r="B103" s="9">
         <v>46239.57452252315</v>
@@ -7520,7 +7523,7 @@
         <v>46240.594121284725</v>
       </c>
       <c r="E103" s="10" t="s">
-        <v>300</v>
+        <v>301</v>
       </c>
       <c r="F103" s="10" t="s">
         <v>26</v>
@@ -7547,13 +7550,13 @@
         <v>26</v>
       </c>
       <c r="N103" s="10" t="s">
-        <v>259</v>
+        <v>260</v>
       </c>
       <c r="O103" s="10" t="s">
-        <v>301</v>
+        <v>302</v>
       </c>
       <c r="P103" s="10" t="s">
-        <v>302</v>
+        <v>303</v>
       </c>
       <c r="Q103" s="9">
         <v>46401</v>
@@ -7573,7 +7576,7 @@
     </row>
     <row r="104" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A104" s="4" t="s">
-        <v>303</v>
+        <v>304</v>
       </c>
       <c r="B104" s="5">
         <v>46239.57452674769</v>
@@ -7583,7 +7586,7 @@
         <v>46240.58973622685</v>
       </c>
       <c r="E104" s="6" t="s">
-        <v>188</v>
+        <v>189</v>
       </c>
       <c r="F104" s="6" t="s">
         <v>26</v>
@@ -7610,13 +7613,13 @@
         <v>26</v>
       </c>
       <c r="N104" s="6" t="s">
-        <v>300</v>
+        <v>301</v>
       </c>
       <c r="O104" s="6" t="s">
-        <v>188</v>
+        <v>189</v>
       </c>
       <c r="P104" s="6" t="s">
-        <v>304</v>
+        <v>305</v>
       </c>
       <c r="Q104" s="6"/>
       <c r="R104" s="6"/>
@@ -7626,7 +7629,7 @@
     </row>
     <row r="105" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A105" s="8" t="s">
-        <v>305</v>
+        <v>306</v>
       </c>
       <c r="B105" s="9">
         <v>46239.574530763886</v>
@@ -7636,7 +7639,7 @@
         <v>46240.58973244213</v>
       </c>
       <c r="E105" s="10" t="s">
-        <v>188</v>
+        <v>189</v>
       </c>
       <c r="F105" s="10" t="s">
         <v>26</v>
@@ -7663,13 +7666,13 @@
         <v>26</v>
       </c>
       <c r="N105" s="10" t="s">
-        <v>300</v>
+        <v>301</v>
       </c>
       <c r="O105" s="10" t="s">
-        <v>188</v>
+        <v>189</v>
       </c>
       <c r="P105" s="10" t="s">
-        <v>300</v>
+        <v>301</v>
       </c>
       <c r="Q105" s="10"/>
       <c r="R105" s="10"/>
@@ -7679,7 +7682,7 @@
     </row>
     <row r="106" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A106" s="4" t="s">
-        <v>306</v>
+        <v>307</v>
       </c>
       <c r="B106" s="5">
         <v>46239.5745340162</v>
@@ -7689,7 +7692,7 @@
         <v>46240.589728692124</v>
       </c>
       <c r="E106" s="6" t="s">
-        <v>188</v>
+        <v>189</v>
       </c>
       <c r="F106" s="6" t="s">
         <v>26</v>
@@ -7716,13 +7719,13 @@
         <v>26</v>
       </c>
       <c r="N106" s="6" t="s">
-        <v>300</v>
+        <v>301</v>
       </c>
       <c r="O106" s="6" t="s">
-        <v>188</v>
+        <v>189</v>
       </c>
       <c r="P106" s="6" t="s">
-        <v>307</v>
+        <v>308</v>
       </c>
       <c r="Q106" s="6"/>
       <c r="R106" s="6"/>
@@ -7732,7 +7735,7 @@
     </row>
     <row r="107" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A107" s="8" t="s">
-        <v>308</v>
+        <v>309</v>
       </c>
       <c r="B107" s="9">
         <v>46239.65323541667</v>
@@ -7742,7 +7745,7 @@
         <v>46240.58972483796</v>
       </c>
       <c r="E107" s="10" t="s">
-        <v>188</v>
+        <v>189</v>
       </c>
       <c r="F107" s="10" t="s">
         <v>26</v>
@@ -7769,13 +7772,13 @@
         <v>26</v>
       </c>
       <c r="N107" s="10" t="s">
-        <v>300</v>
+        <v>301</v>
       </c>
       <c r="O107" s="10" t="s">
-        <v>194</v>
+        <v>195</v>
       </c>
       <c r="P107" s="10" t="s">
-        <v>188</v>
+        <v>189</v>
       </c>
       <c r="Q107" s="10"/>
       <c r="R107" s="10"/>
@@ -7785,7 +7788,7 @@
     </row>
     <row r="108" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A108" s="4" t="s">
-        <v>309</v>
+        <v>310</v>
       </c>
       <c r="B108" s="5">
         <v>46239.57453762731</v>
@@ -7795,7 +7798,7 @@
         <v>46240.59673913194</v>
       </c>
       <c r="E108" s="6" t="s">
-        <v>302</v>
+        <v>303</v>
       </c>
       <c r="F108" s="6" t="s">
         <v>26</v>
@@ -7822,13 +7825,13 @@
         <v>26</v>
       </c>
       <c r="N108" s="6" t="s">
-        <v>259</v>
+        <v>260</v>
       </c>
       <c r="O108" s="6" t="s">
-        <v>310</v>
+        <v>311</v>
       </c>
       <c r="P108" s="6" t="s">
-        <v>311</v>
+        <v>312</v>
       </c>
       <c r="Q108" s="5">
         <v>46402</v>
@@ -7848,7 +7851,7 @@
     </row>
     <row r="109" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A109" s="8" t="s">
-        <v>312</v>
+        <v>313</v>
       </c>
       <c r="B109" s="9">
         <v>46239.57454184028</v>
@@ -7858,7 +7861,7 @@
         <v>46240.59276476852</v>
       </c>
       <c r="E109" s="10" t="s">
-        <v>188</v>
+        <v>189</v>
       </c>
       <c r="F109" s="10" t="s">
         <v>26</v>
@@ -7885,13 +7888,13 @@
         <v>26</v>
       </c>
       <c r="N109" s="10" t="s">
-        <v>302</v>
+        <v>303</v>
       </c>
       <c r="O109" s="10" t="s">
-        <v>188</v>
+        <v>189</v>
       </c>
       <c r="P109" s="10" t="s">
-        <v>313</v>
+        <v>314</v>
       </c>
       <c r="Q109" s="10"/>
       <c r="R109" s="10"/>
@@ -7901,7 +7904,7 @@
     </row>
     <row r="110" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A110" s="4" t="s">
-        <v>314</v>
+        <v>315</v>
       </c>
       <c r="B110" s="5">
         <v>46239.57454601851</v>
@@ -7911,7 +7914,7 @@
         <v>46240.59276085648</v>
       </c>
       <c r="E110" s="6" t="s">
-        <v>188</v>
+        <v>189</v>
       </c>
       <c r="F110" s="6" t="s">
         <v>26</v>
@@ -7938,13 +7941,13 @@
         <v>26</v>
       </c>
       <c r="N110" s="6" t="s">
-        <v>302</v>
+        <v>303</v>
       </c>
       <c r="O110" s="6" t="s">
-        <v>186</v>
+        <v>187</v>
       </c>
       <c r="P110" s="6" t="s">
-        <v>313</v>
+        <v>314</v>
       </c>
       <c r="Q110" s="6"/>
       <c r="R110" s="6"/>
@@ -7954,7 +7957,7 @@
     </row>
     <row r="111" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A111" s="8" t="s">
-        <v>315</v>
+        <v>316</v>
       </c>
       <c r="B111" s="9">
         <v>46239.57455318287</v>
@@ -7964,7 +7967,7 @@
         <v>46240.59275711805</v>
       </c>
       <c r="E111" s="10" t="s">
-        <v>188</v>
+        <v>189</v>
       </c>
       <c r="F111" s="10" t="s">
         <v>26</v>
@@ -7991,13 +7994,13 @@
         <v>26</v>
       </c>
       <c r="N111" s="10" t="s">
-        <v>302</v>
+        <v>303</v>
       </c>
       <c r="O111" s="10" t="s">
-        <v>186</v>
+        <v>187</v>
       </c>
       <c r="P111" s="10" t="s">
-        <v>313</v>
+        <v>314</v>
       </c>
       <c r="Q111" s="10"/>
       <c r="R111" s="10"/>
@@ -8007,7 +8010,7 @@
     </row>
     <row r="112" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A112" s="4" t="s">
-        <v>316</v>
+        <v>317</v>
       </c>
       <c r="B112" s="5">
         <v>46239.65330143519</v>
@@ -8017,7 +8020,7 @@
         <v>46240.59275344908</v>
       </c>
       <c r="E112" s="6" t="s">
-        <v>188</v>
+        <v>189</v>
       </c>
       <c r="F112" s="6" t="s">
         <v>26</v>
@@ -8044,10 +8047,10 @@
         <v>26</v>
       </c>
       <c r="N112" s="6" t="s">
-        <v>302</v>
+        <v>303</v>
       </c>
       <c r="O112" s="6" t="s">
-        <v>188</v>
+        <v>189</v>
       </c>
       <c r="P112" s="6" t="s">
         <v>26</v>
@@ -8060,7 +8063,7 @@
     </row>
     <row r="113" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A113" s="8" t="s">
-        <v>317</v>
+        <v>318</v>
       </c>
       <c r="B113" s="9">
         <v>46239.57455898148</v>
@@ -8070,7 +8073,7 @@
         <v>46240.59432991898</v>
       </c>
       <c r="E113" s="10" t="s">
-        <v>311</v>
+        <v>312</v>
       </c>
       <c r="F113" s="10" t="s">
         <v>26</v>
@@ -8097,10 +8100,10 @@
         <v>26</v>
       </c>
       <c r="N113" s="10" t="s">
-        <v>259</v>
+        <v>260</v>
       </c>
       <c r="O113" s="10" t="s">
-        <v>318</v>
+        <v>319</v>
       </c>
       <c r="P113" s="10" t="s">
         <v>26</v>
@@ -8123,7 +8126,7 @@
     </row>
     <row r="114" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A114" s="4" t="s">
-        <v>319</v>
+        <v>320</v>
       </c>
       <c r="B114" s="5">
         <v>46239.57456341435</v>
@@ -8133,7 +8136,7 @@
         <v>46240.59289621528</v>
       </c>
       <c r="E114" s="6" t="s">
-        <v>188</v>
+        <v>189</v>
       </c>
       <c r="F114" s="6" t="s">
         <v>26</v>
@@ -8160,13 +8163,13 @@
         <v>26</v>
       </c>
       <c r="N114" s="6" t="s">
-        <v>311</v>
+        <v>312</v>
       </c>
       <c r="O114" s="6" t="s">
-        <v>188</v>
+        <v>189</v>
       </c>
       <c r="P114" s="6" t="s">
-        <v>320</v>
+        <v>321</v>
       </c>
       <c r="Q114" s="6"/>
       <c r="R114" s="6"/>
@@ -8176,7 +8179,7 @@
     </row>
     <row r="115" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A115" s="8" t="s">
-        <v>321</v>
+        <v>322</v>
       </c>
       <c r="B115" s="9">
         <v>46239.57456761574</v>
@@ -8186,7 +8189,7 @@
         <v>46240.59289185185</v>
       </c>
       <c r="E115" s="10" t="s">
-        <v>188</v>
+        <v>189</v>
       </c>
       <c r="F115" s="10" t="s">
         <v>26</v>
@@ -8213,13 +8216,13 @@
         <v>26</v>
       </c>
       <c r="N115" s="10" t="s">
-        <v>311</v>
+        <v>312</v>
       </c>
       <c r="O115" s="10" t="s">
-        <v>188</v>
+        <v>189</v>
       </c>
       <c r="P115" s="10" t="s">
-        <v>320</v>
+        <v>321</v>
       </c>
       <c r="Q115" s="10"/>
       <c r="R115" s="10"/>
@@ -8229,7 +8232,7 @@
     </row>
     <row r="116" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A116" s="4" t="s">
-        <v>322</v>
+        <v>323</v>
       </c>
       <c r="B116" s="5">
         <v>46239.574571840276</v>
@@ -8239,7 +8242,7 @@
         <v>46240.59288778935</v>
       </c>
       <c r="E116" s="6" t="s">
-        <v>188</v>
+        <v>189</v>
       </c>
       <c r="F116" s="6" t="s">
         <v>26</v>
@@ -8266,13 +8269,13 @@
         <v>26</v>
       </c>
       <c r="N116" s="6" t="s">
-        <v>311</v>
+        <v>312</v>
       </c>
       <c r="O116" s="6" t="s">
-        <v>188</v>
+        <v>189</v>
       </c>
       <c r="P116" s="6" t="s">
-        <v>320</v>
+        <v>321</v>
       </c>
       <c r="Q116" s="6"/>
       <c r="R116" s="6"/>
@@ -8282,7 +8285,7 @@
     </row>
     <row r="117" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A117" s="8" t="s">
-        <v>323</v>
+        <v>324</v>
       </c>
       <c r="B117" s="9">
         <v>46239.65337195602</v>
@@ -8292,7 +8295,7 @@
         <v>46240.59288347222</v>
       </c>
       <c r="E117" s="10" t="s">
-        <v>188</v>
+        <v>189</v>
       </c>
       <c r="F117" s="10" t="s">
         <v>26</v>
@@ -8319,13 +8322,13 @@
         <v>26</v>
       </c>
       <c r="N117" s="10" t="s">
-        <v>311</v>
+        <v>312</v>
       </c>
       <c r="O117" s="10" t="s">
-        <v>194</v>
+        <v>195</v>
       </c>
       <c r="P117" s="10" t="s">
-        <v>188</v>
+        <v>189</v>
       </c>
       <c r="Q117" s="10"/>
       <c r="R117" s="10"/>
@@ -8335,7 +8338,7 @@
     </row>
     <row r="118" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A118" s="4" t="s">
-        <v>324</v>
+        <v>325</v>
       </c>
       <c r="B118" s="5">
         <v>46239.57457591435</v>
@@ -8345,7 +8348,7 @@
         <v>46240.58467253472</v>
       </c>
       <c r="E118" s="6" t="s">
-        <v>325</v>
+        <v>326</v>
       </c>
       <c r="F118" s="6" t="s">
         <v>25</v>
@@ -8369,7 +8372,7 @@
         <v>26</v>
       </c>
       <c r="O118" s="6" t="s">
-        <v>326</v>
+        <v>327</v>
       </c>
       <c r="P118" s="6" t="s">
         <v>26</v>
@@ -8382,7 +8385,7 @@
     </row>
     <row r="119" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A119" s="8" t="s">
-        <v>327</v>
+        <v>328</v>
       </c>
       <c r="B119" s="9">
         <v>46239.57457920139</v>
@@ -8392,16 +8395,16 @@
         <v>46240.595475775466</v>
       </c>
       <c r="E119" s="10" t="s">
-        <v>328</v>
+        <v>329</v>
       </c>
       <c r="F119" s="10" t="s">
         <v>26</v>
       </c>
       <c r="G119" s="10" t="s">
-        <v>329</v>
+        <v>330</v>
       </c>
       <c r="H119" s="10" t="s">
-        <v>330</v>
+        <v>331</v>
       </c>
       <c r="I119" s="9">
         <v>46407</v>
@@ -8419,13 +8422,13 @@
         <v>26</v>
       </c>
       <c r="N119" s="10" t="s">
-        <v>325</v>
+        <v>326</v>
       </c>
       <c r="O119" s="10" t="s">
-        <v>331</v>
+        <v>332</v>
       </c>
       <c r="P119" s="10" t="s">
-        <v>332</v>
+        <v>333</v>
       </c>
       <c r="Q119" s="9">
         <v>46407</v>
@@ -8445,7 +8448,7 @@
     </row>
     <row r="120" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A120" s="4" t="s">
-        <v>333</v>
+        <v>334</v>
       </c>
       <c r="B120" s="5">
         <v>46239.57458372685</v>
@@ -8455,16 +8458,16 @@
         <v>46240.595126388886</v>
       </c>
       <c r="E120" s="6" t="s">
-        <v>188</v>
+        <v>189</v>
       </c>
       <c r="F120" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G120" s="6" t="s">
-        <v>329</v>
+        <v>330</v>
       </c>
       <c r="H120" s="6" t="s">
-        <v>330</v>
+        <v>331</v>
       </c>
       <c r="I120" s="5">
         <v>46407</v>
@@ -8482,13 +8485,13 @@
         <v>26</v>
       </c>
       <c r="N120" s="6" t="s">
-        <v>328</v>
+        <v>329</v>
       </c>
       <c r="O120" s="6" t="s">
-        <v>188</v>
+        <v>189</v>
       </c>
       <c r="P120" s="6" t="s">
-        <v>334</v>
+        <v>335</v>
       </c>
       <c r="Q120" s="6"/>
       <c r="R120" s="6"/>
@@ -8498,7 +8501,7 @@
     </row>
     <row r="121" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A121" s="8" t="s">
-        <v>335</v>
+        <v>336</v>
       </c>
       <c r="B121" s="9">
         <v>46239.574587662035</v>
@@ -8508,16 +8511,16 @@
         <v>46240.59512229166</v>
       </c>
       <c r="E121" s="10" t="s">
-        <v>188</v>
+        <v>189</v>
       </c>
       <c r="F121" s="10" t="s">
         <v>26</v>
       </c>
       <c r="G121" s="10" t="s">
-        <v>329</v>
+        <v>330</v>
       </c>
       <c r="H121" s="10" t="s">
-        <v>330</v>
+        <v>331</v>
       </c>
       <c r="I121" s="9">
         <v>46407</v>
@@ -8535,13 +8538,13 @@
         <v>26</v>
       </c>
       <c r="N121" s="10" t="s">
-        <v>328</v>
+        <v>329</v>
       </c>
       <c r="O121" s="10" t="s">
-        <v>188</v>
+        <v>189</v>
       </c>
       <c r="P121" s="10" t="s">
-        <v>336</v>
+        <v>337</v>
       </c>
       <c r="Q121" s="10"/>
       <c r="R121" s="10"/>
@@ -8551,7 +8554,7 @@
     </row>
     <row r="122" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A122" s="4" t="s">
-        <v>337</v>
+        <v>338</v>
       </c>
       <c r="B122" s="5">
         <v>46239.57459146991</v>
@@ -8561,16 +8564,16 @@
         <v>46240.59511797453</v>
       </c>
       <c r="E122" s="6" t="s">
-        <v>188</v>
+        <v>189</v>
       </c>
       <c r="F122" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G122" s="6" t="s">
-        <v>329</v>
+        <v>330</v>
       </c>
       <c r="H122" s="6" t="s">
-        <v>330</v>
+        <v>331</v>
       </c>
       <c r="I122" s="5">
         <v>46407</v>
@@ -8588,13 +8591,13 @@
         <v>26</v>
       </c>
       <c r="N122" s="6" t="s">
-        <v>328</v>
+        <v>329</v>
       </c>
       <c r="O122" s="6" t="s">
-        <v>188</v>
+        <v>189</v>
       </c>
       <c r="P122" s="6" t="s">
-        <v>334</v>
+        <v>335</v>
       </c>
       <c r="Q122" s="6"/>
       <c r="R122" s="6"/>
@@ -8604,7 +8607,7 @@
     </row>
     <row r="123" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A123" s="8" t="s">
-        <v>338</v>
+        <v>339</v>
       </c>
       <c r="B123" s="9">
         <v>46239.65343762732</v>
@@ -8614,16 +8617,16 @@
         <v>46240.5951130787</v>
       </c>
       <c r="E123" s="10" t="s">
-        <v>188</v>
+        <v>189</v>
       </c>
       <c r="F123" s="10" t="s">
         <v>26</v>
       </c>
       <c r="G123" s="10" t="s">
-        <v>329</v>
+        <v>330</v>
       </c>
       <c r="H123" s="10" t="s">
-        <v>330</v>
+        <v>331</v>
       </c>
       <c r="I123" s="9">
         <v>46407</v>
@@ -8641,10 +8644,10 @@
         <v>26</v>
       </c>
       <c r="N123" s="10" t="s">
-        <v>328</v>
+        <v>329</v>
       </c>
       <c r="O123" s="10" t="s">
-        <v>188</v>
+        <v>189</v>
       </c>
       <c r="P123" s="10" t="s">
         <v>26</v>
@@ -8657,7 +8660,7 @@
     </row>
     <row r="124" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A124" s="4" t="s">
-        <v>339</v>
+        <v>340</v>
       </c>
       <c r="B124" s="5">
         <v>46239.665801446754</v>
@@ -8673,10 +8676,10 @@
         <v>26</v>
       </c>
       <c r="G124" s="6" t="s">
-        <v>329</v>
+        <v>330</v>
       </c>
       <c r="H124" s="6" t="s">
-        <v>330</v>
+        <v>331</v>
       </c>
       <c r="I124" s="5">
         <v>46407</v>
@@ -8694,13 +8697,13 @@
         <v>26</v>
       </c>
       <c r="N124" s="6" t="s">
-        <v>328</v>
+        <v>329</v>
       </c>
       <c r="O124" s="6" t="s">
         <v>56</v>
       </c>
       <c r="P124" s="6" t="s">
-        <v>340</v>
+        <v>341</v>
       </c>
       <c r="Q124" s="6"/>
       <c r="R124" s="6"/>
@@ -8710,7 +8713,7 @@
     </row>
     <row r="125" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A125" s="8" t="s">
-        <v>341</v>
+        <v>342</v>
       </c>
       <c r="B125" s="9">
         <v>46239.665817581015</v>
@@ -8726,10 +8729,10 @@
         <v>26</v>
       </c>
       <c r="G125" s="10" t="s">
-        <v>329</v>
+        <v>330</v>
       </c>
       <c r="H125" s="10" t="s">
-        <v>330</v>
+        <v>331</v>
       </c>
       <c r="I125" s="9">
         <v>46407</v>
@@ -8747,13 +8750,13 @@
         <v>26</v>
       </c>
       <c r="N125" s="10" t="s">
-        <v>328</v>
+        <v>329</v>
       </c>
       <c r="O125" s="10" t="s">
         <v>56</v>
       </c>
       <c r="P125" s="10" t="s">
-        <v>342</v>
+        <v>343</v>
       </c>
       <c r="Q125" s="10"/>
       <c r="R125" s="10"/>
@@ -8763,7 +8766,7 @@
     </row>
     <row r="126" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A126" s="4" t="s">
-        <v>343</v>
+        <v>344</v>
       </c>
       <c r="B126" s="5">
         <v>46239.66583704861</v>
@@ -8779,10 +8782,10 @@
         <v>26</v>
       </c>
       <c r="G126" s="6" t="s">
-        <v>329</v>
+        <v>330</v>
       </c>
       <c r="H126" s="6" t="s">
-        <v>330</v>
+        <v>331</v>
       </c>
       <c r="I126" s="5">
         <v>46407</v>
@@ -8800,13 +8803,13 @@
         <v>26</v>
       </c>
       <c r="N126" s="6" t="s">
-        <v>328</v>
+        <v>329</v>
       </c>
       <c r="O126" s="6" t="s">
         <v>56</v>
       </c>
       <c r="P126" s="6" t="s">
-        <v>344</v>
+        <v>345</v>
       </c>
       <c r="Q126" s="6"/>
       <c r="R126" s="6"/>
@@ -8816,7 +8819,7 @@
     </row>
     <row r="127" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A127" s="8" t="s">
-        <v>345</v>
+        <v>346</v>
       </c>
       <c r="B127" s="9">
         <v>46239.66587196759</v>
@@ -8832,10 +8835,10 @@
         <v>26</v>
       </c>
       <c r="G127" s="10" t="s">
-        <v>329</v>
+        <v>330</v>
       </c>
       <c r="H127" s="10" t="s">
-        <v>330</v>
+        <v>331</v>
       </c>
       <c r="I127" s="9">
         <v>46407</v>
@@ -8853,13 +8856,13 @@
         <v>26</v>
       </c>
       <c r="N127" s="10" t="s">
-        <v>328</v>
+        <v>329</v>
       </c>
       <c r="O127" s="10" t="s">
         <v>56</v>
       </c>
       <c r="P127" s="10" t="s">
-        <v>346</v>
+        <v>347</v>
       </c>
       <c r="Q127" s="10"/>
       <c r="R127" s="10"/>
@@ -8869,7 +8872,7 @@
     </row>
     <row r="128" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A128" s="4" t="s">
-        <v>347</v>
+        <v>348</v>
       </c>
       <c r="B128" s="5">
         <v>46239.57459537037</v>
@@ -8879,7 +8882,7 @@
         <v>46240.595416041666</v>
       </c>
       <c r="E128" s="6" t="s">
-        <v>348</v>
+        <v>349</v>
       </c>
       <c r="F128" s="6" t="s">
         <v>26</v>
@@ -8906,10 +8909,10 @@
         <v>26</v>
       </c>
       <c r="N128" s="6" t="s">
-        <v>325</v>
+        <v>326</v>
       </c>
       <c r="O128" s="6" t="s">
-        <v>349</v>
+        <v>350</v>
       </c>
       <c r="P128" s="6" t="s">
         <v>26</v>
@@ -8932,7 +8935,7 @@
     </row>
     <row r="129" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A129" s="8" t="s">
-        <v>350</v>
+        <v>351</v>
       </c>
       <c r="B129" s="9">
         <v>46239.57459956019</v>
@@ -8942,7 +8945,7 @@
         <v>46240.59525278935</v>
       </c>
       <c r="E129" s="10" t="s">
-        <v>188</v>
+        <v>189</v>
       </c>
       <c r="F129" s="10" t="s">
         <v>26</v>
@@ -8969,13 +8972,13 @@
         <v>26</v>
       </c>
       <c r="N129" s="10" t="s">
-        <v>348</v>
+        <v>349</v>
       </c>
       <c r="O129" s="10" t="s">
-        <v>188</v>
+        <v>189</v>
       </c>
       <c r="P129" s="10" t="s">
-        <v>351</v>
+        <v>352</v>
       </c>
       <c r="Q129" s="10"/>
       <c r="R129" s="10"/>
@@ -8985,7 +8988,7 @@
     </row>
     <row r="130" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A130" s="4" t="s">
-        <v>352</v>
+        <v>353</v>
       </c>
       <c r="B130" s="5">
         <v>46239.57460317129</v>
@@ -8995,7 +8998,7 @@
         <v>46240.595248032405</v>
       </c>
       <c r="E130" s="6" t="s">
-        <v>188</v>
+        <v>189</v>
       </c>
       <c r="F130" s="6" t="s">
         <v>26</v>
@@ -9022,13 +9025,13 @@
         <v>26</v>
       </c>
       <c r="N130" s="6" t="s">
-        <v>348</v>
+        <v>349</v>
       </c>
       <c r="O130" s="6" t="s">
-        <v>188</v>
+        <v>189</v>
       </c>
       <c r="P130" s="6" t="s">
-        <v>351</v>
+        <v>352</v>
       </c>
       <c r="Q130" s="6"/>
       <c r="R130" s="6"/>
@@ -9038,7 +9041,7 @@
     </row>
     <row r="131" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A131" s="8" t="s">
-        <v>353</v>
+        <v>354</v>
       </c>
       <c r="B131" s="9">
         <v>46239.57460717593</v>
@@ -9048,7 +9051,7 @@
         <v>46240.595243749995</v>
       </c>
       <c r="E131" s="10" t="s">
-        <v>188</v>
+        <v>189</v>
       </c>
       <c r="F131" s="10" t="s">
         <v>26</v>
@@ -9075,13 +9078,13 @@
         <v>26</v>
       </c>
       <c r="N131" s="10" t="s">
-        <v>348</v>
+        <v>349</v>
       </c>
       <c r="O131" s="10" t="s">
-        <v>188</v>
+        <v>189</v>
       </c>
       <c r="P131" s="10" t="s">
-        <v>354</v>
+        <v>355</v>
       </c>
       <c r="Q131" s="10"/>
       <c r="R131" s="10"/>
@@ -9091,7 +9094,7 @@
     </row>
     <row r="132" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A132" s="4" t="s">
-        <v>355</v>
+        <v>356</v>
       </c>
       <c r="B132" s="5">
         <v>46239.653502546294</v>
@@ -9101,7 +9104,7 @@
         <v>46240.595240069444</v>
       </c>
       <c r="E132" s="6" t="s">
-        <v>188</v>
+        <v>189</v>
       </c>
       <c r="F132" s="6" t="s">
         <v>26</v>
@@ -9128,10 +9131,10 @@
         <v>26</v>
       </c>
       <c r="N132" s="6" t="s">
-        <v>348</v>
+        <v>349</v>
       </c>
       <c r="O132" s="6" t="s">
-        <v>194</v>
+        <v>195</v>
       </c>
       <c r="P132" s="6" t="s">
         <v>26</v>
@@ -9144,7 +9147,7 @@
     </row>
     <row r="133" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A133" s="8" t="s">
-        <v>356</v>
+        <v>357</v>
       </c>
       <c r="B133" s="9">
         <v>46239.67035252315</v>
@@ -9154,7 +9157,7 @@
         <v>46240.59523623843</v>
       </c>
       <c r="E133" s="10" t="s">
-        <v>357</v>
+        <v>358</v>
       </c>
       <c r="F133" s="10" t="s">
         <v>26</v>
@@ -9181,13 +9184,13 @@
         <v>26</v>
       </c>
       <c r="N133" s="10" t="s">
-        <v>348</v>
+        <v>349</v>
       </c>
       <c r="O133" s="10" t="s">
         <v>56</v>
       </c>
       <c r="P133" s="10" t="s">
-        <v>358</v>
+        <v>359</v>
       </c>
       <c r="Q133" s="10"/>
       <c r="R133" s="10"/>
@@ -9197,7 +9200,7 @@
     </row>
     <row r="134" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A134" s="4" t="s">
-        <v>359</v>
+        <v>360</v>
       </c>
       <c r="B134" s="5">
         <v>46239.670362372686</v>
@@ -9207,7 +9210,7 @@
         <v>46240.595232673615</v>
       </c>
       <c r="E134" s="6" t="s">
-        <v>360</v>
+        <v>361</v>
       </c>
       <c r="F134" s="6" t="s">
         <v>26</v>
@@ -9234,13 +9237,13 @@
         <v>26</v>
       </c>
       <c r="N134" s="6" t="s">
-        <v>348</v>
+        <v>349</v>
       </c>
       <c r="O134" s="6" t="s">
         <v>56</v>
       </c>
       <c r="P134" s="6" t="s">
-        <v>361</v>
+        <v>362</v>
       </c>
       <c r="Q134" s="6"/>
       <c r="R134" s="6"/>
@@ -9250,7 +9253,7 @@
     </row>
     <row r="135" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A135" s="8" t="s">
-        <v>362</v>
+        <v>363</v>
       </c>
       <c r="B135" s="9">
         <v>46239.67036836805</v>
@@ -9260,7 +9263,7 @@
         <v>46240.59522915509</v>
       </c>
       <c r="E135" s="10" t="s">
-        <v>363</v>
+        <v>364</v>
       </c>
       <c r="F135" s="10" t="s">
         <v>26</v>
@@ -9287,13 +9290,13 @@
         <v>26</v>
       </c>
       <c r="N135" s="10" t="s">
-        <v>348</v>
+        <v>349</v>
       </c>
       <c r="O135" s="10" t="s">
         <v>56</v>
       </c>
       <c r="P135" s="10" t="s">
-        <v>364</v>
+        <v>365</v>
       </c>
       <c r="Q135" s="10"/>
       <c r="R135" s="10"/>
@@ -9303,7 +9306,7 @@
     </row>
     <row r="136" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A136" s="4" t="s">
-        <v>365</v>
+        <v>366</v>
       </c>
       <c r="B136" s="5">
         <v>46239.670374050926</v>
@@ -9313,7 +9316,7 @@
         <v>46240.5952253588</v>
       </c>
       <c r="E136" s="6" t="s">
-        <v>366</v>
+        <v>367</v>
       </c>
       <c r="F136" s="6" t="s">
         <v>26</v>
@@ -9340,13 +9343,13 @@
         <v>26</v>
       </c>
       <c r="N136" s="6" t="s">
-        <v>348</v>
+        <v>349</v>
       </c>
       <c r="O136" s="6" t="s">
         <v>56</v>
       </c>
       <c r="P136" s="6" t="s">
-        <v>367</v>
+        <v>368</v>
       </c>
       <c r="Q136" s="6"/>
       <c r="R136" s="6"/>
@@ -9356,7 +9359,7 @@
     </row>
     <row r="137" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A137" s="8" t="s">
-        <v>368</v>
+        <v>369</v>
       </c>
       <c r="B137" s="9">
         <v>46239.57461079861</v>
@@ -9366,16 +9369,16 @@
         <v>46240.59608133102</v>
       </c>
       <c r="E137" s="10" t="s">
-        <v>369</v>
+        <v>370</v>
       </c>
       <c r="F137" s="10" t="s">
         <v>26</v>
       </c>
       <c r="G137" s="10" t="s">
-        <v>222</v>
+        <v>223</v>
       </c>
       <c r="H137" s="10" t="s">
-        <v>223</v>
+        <v>224</v>
       </c>
       <c r="I137" s="9">
         <v>46412</v>
@@ -9393,13 +9396,13 @@
         <v>26</v>
       </c>
       <c r="N137" s="10" t="s">
-        <v>325</v>
+        <v>326</v>
       </c>
       <c r="O137" s="10" t="s">
-        <v>370</v>
+        <v>371</v>
       </c>
       <c r="P137" s="10" t="s">
-        <v>325</v>
+        <v>326</v>
       </c>
       <c r="Q137" s="9">
         <v>46412</v>
@@ -9419,7 +9422,7 @@
     </row>
     <row r="138" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A138" s="4" t="s">
-        <v>371</v>
+        <v>372</v>
       </c>
       <c r="B138" s="5">
         <v>46239.57461494213</v>
@@ -9429,16 +9432,16 @@
         <v>46240.59571179398</v>
       </c>
       <c r="E138" s="6" t="s">
-        <v>188</v>
+        <v>189</v>
       </c>
       <c r="F138" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G138" s="6" t="s">
-        <v>222</v>
+        <v>223</v>
       </c>
       <c r="H138" s="6" t="s">
-        <v>223</v>
+        <v>224</v>
       </c>
       <c r="I138" s="5">
         <v>46412</v>
@@ -9456,13 +9459,13 @@
         <v>26</v>
       </c>
       <c r="N138" s="6" t="s">
-        <v>369</v>
+        <v>370</v>
       </c>
       <c r="O138" s="6" t="s">
-        <v>188</v>
+        <v>189</v>
       </c>
       <c r="P138" s="6" t="s">
-        <v>372</v>
+        <v>373</v>
       </c>
       <c r="Q138" s="6"/>
       <c r="R138" s="6"/>
@@ -9472,7 +9475,7 @@
     </row>
     <row r="139" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A139" s="8" t="s">
-        <v>373</v>
+        <v>374</v>
       </c>
       <c r="B139" s="9">
         <v>46239.574618680555</v>
@@ -9482,16 +9485,16 @@
         <v>46240.595708611116</v>
       </c>
       <c r="E139" s="10" t="s">
-        <v>188</v>
+        <v>189</v>
       </c>
       <c r="F139" s="10" t="s">
         <v>26</v>
       </c>
       <c r="G139" s="10" t="s">
-        <v>222</v>
+        <v>223</v>
       </c>
       <c r="H139" s="10" t="s">
-        <v>223</v>
+        <v>224</v>
       </c>
       <c r="I139" s="9">
         <v>46412</v>
@@ -9509,13 +9512,13 @@
         <v>26</v>
       </c>
       <c r="N139" s="10" t="s">
-        <v>369</v>
+        <v>370</v>
       </c>
       <c r="O139" s="10" t="s">
-        <v>188</v>
+        <v>189</v>
       </c>
       <c r="P139" s="10" t="s">
-        <v>372</v>
+        <v>373</v>
       </c>
       <c r="Q139" s="10"/>
       <c r="R139" s="10"/>
@@ -9525,7 +9528,7 @@
     </row>
     <row r="140" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A140" s="4" t="s">
-        <v>374</v>
+        <v>375</v>
       </c>
       <c r="B140" s="5">
         <v>46239.57462254629</v>
@@ -9535,16 +9538,16 @@
         <v>46240.59570520833</v>
       </c>
       <c r="E140" s="6" t="s">
-        <v>188</v>
+        <v>189</v>
       </c>
       <c r="F140" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G140" s="6" t="s">
-        <v>222</v>
+        <v>223</v>
       </c>
       <c r="H140" s="6" t="s">
-        <v>223</v>
+        <v>224</v>
       </c>
       <c r="I140" s="5">
         <v>46412</v>
@@ -9562,13 +9565,13 @@
         <v>26</v>
       </c>
       <c r="N140" s="6" t="s">
-        <v>369</v>
+        <v>370</v>
       </c>
       <c r="O140" s="6" t="s">
-        <v>188</v>
+        <v>189</v>
       </c>
       <c r="P140" s="6" t="s">
-        <v>375</v>
+        <v>376</v>
       </c>
       <c r="Q140" s="6"/>
       <c r="R140" s="6"/>
@@ -9578,7 +9581,7 @@
     </row>
     <row r="141" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A141" s="8" t="s">
-        <v>376</v>
+        <v>377</v>
       </c>
       <c r="B141" s="9">
         <v>46239.65356868056</v>
@@ -9588,16 +9591,16 @@
         <v>46240.59570181713</v>
       </c>
       <c r="E141" s="10" t="s">
-        <v>188</v>
+        <v>189</v>
       </c>
       <c r="F141" s="10" t="s">
         <v>26</v>
       </c>
       <c r="G141" s="10" t="s">
-        <v>222</v>
+        <v>223</v>
       </c>
       <c r="H141" s="10" t="s">
-        <v>223</v>
+        <v>224</v>
       </c>
       <c r="I141" s="9">
         <v>46412</v>
@@ -9615,13 +9618,13 @@
         <v>26</v>
       </c>
       <c r="N141" s="10" t="s">
-        <v>369</v>
+        <v>370</v>
       </c>
       <c r="O141" s="10" t="s">
-        <v>194</v>
+        <v>195</v>
       </c>
       <c r="P141" s="10" t="s">
-        <v>369</v>
+        <v>370</v>
       </c>
       <c r="Q141" s="10"/>
       <c r="R141" s="10"/>
@@ -9631,7 +9634,7 @@
     </row>
     <row r="142" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A142" s="4" t="s">
-        <v>377</v>
+        <v>378</v>
       </c>
       <c r="B142" s="5">
         <v>46239.675931875</v>
@@ -9647,10 +9650,10 @@
         <v>26</v>
       </c>
       <c r="G142" s="6" t="s">
-        <v>222</v>
+        <v>223</v>
       </c>
       <c r="H142" s="6" t="s">
-        <v>223</v>
+        <v>224</v>
       </c>
       <c r="I142" s="5">
         <v>46412</v>
@@ -9668,13 +9671,13 @@
         <v>26</v>
       </c>
       <c r="N142" s="6" t="s">
-        <v>369</v>
+        <v>370</v>
       </c>
       <c r="O142" s="6" t="s">
-        <v>357</v>
+        <v>358</v>
       </c>
       <c r="P142" s="6" t="s">
-        <v>369</v>
+        <v>370</v>
       </c>
       <c r="Q142" s="6"/>
       <c r="R142" s="6"/>
@@ -9684,7 +9687,7 @@
     </row>
     <row r="143" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A143" s="8" t="s">
-        <v>378</v>
+        <v>379</v>
       </c>
       <c r="B143" s="9">
         <v>46239.67595826389</v>
@@ -9694,16 +9697,16 @@
         <v>46240.59569465277</v>
       </c>
       <c r="E143" s="10" t="s">
-        <v>379</v>
+        <v>380</v>
       </c>
       <c r="F143" s="10" t="s">
         <v>26</v>
       </c>
       <c r="G143" s="10" t="s">
-        <v>222</v>
+        <v>223</v>
       </c>
       <c r="H143" s="10" t="s">
-        <v>223</v>
+        <v>224</v>
       </c>
       <c r="I143" s="9">
         <v>46412</v>
@@ -9721,13 +9724,13 @@
         <v>26</v>
       </c>
       <c r="N143" s="10" t="s">
-        <v>369</v>
+        <v>370</v>
       </c>
       <c r="O143" s="10" t="s">
-        <v>360</v>
+        <v>361</v>
       </c>
       <c r="P143" s="10" t="s">
-        <v>380</v>
+        <v>381</v>
       </c>
       <c r="Q143" s="10"/>
       <c r="R143" s="10"/>
@@ -9737,7 +9740,7 @@
     </row>
     <row r="144" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A144" s="4" t="s">
-        <v>381</v>
+        <v>382</v>
       </c>
       <c r="B144" s="5">
         <v>46239.67596550926</v>
@@ -9753,10 +9756,10 @@
         <v>26</v>
       </c>
       <c r="G144" s="6" t="s">
-        <v>222</v>
+        <v>223</v>
       </c>
       <c r="H144" s="6" t="s">
-        <v>223</v>
+        <v>224</v>
       </c>
       <c r="I144" s="5">
         <v>46412</v>
@@ -9774,13 +9777,13 @@
         <v>26</v>
       </c>
       <c r="N144" s="6" t="s">
-        <v>369</v>
+        <v>370</v>
       </c>
       <c r="O144" s="6" t="s">
-        <v>363</v>
+        <v>364</v>
       </c>
       <c r="P144" s="6" t="s">
-        <v>380</v>
+        <v>381</v>
       </c>
       <c r="Q144" s="6"/>
       <c r="R144" s="6"/>
@@ -9790,7 +9793,7 @@
     </row>
     <row r="145" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A145" s="8" t="s">
-        <v>382</v>
+        <v>383</v>
       </c>
       <c r="B145" s="9">
         <v>46239.67597105324</v>
@@ -9800,16 +9803,16 @@
         <v>46240.59568726852</v>
       </c>
       <c r="E145" s="10" t="s">
-        <v>379</v>
+        <v>380</v>
       </c>
       <c r="F145" s="10" t="s">
         <v>26</v>
       </c>
       <c r="G145" s="10" t="s">
-        <v>222</v>
+        <v>223</v>
       </c>
       <c r="H145" s="10" t="s">
-        <v>223</v>
+        <v>224</v>
       </c>
       <c r="I145" s="9">
         <v>46412</v>
@@ -9827,13 +9830,13 @@
         <v>26</v>
       </c>
       <c r="N145" s="10" t="s">
-        <v>369</v>
+        <v>370</v>
       </c>
       <c r="O145" s="10" t="s">
-        <v>366</v>
+        <v>367</v>
       </c>
       <c r="P145" s="10" t="s">
-        <v>383</v>
+        <v>384</v>
       </c>
       <c r="Q145" s="10"/>
       <c r="R145" s="10"/>
@@ -9843,7 +9846,7 @@
     </row>
     <row r="146" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A146" s="4" t="s">
-        <v>384</v>
+        <v>385</v>
       </c>
       <c r="B146" s="5">
         <v>46239.574665231485</v>
@@ -9853,16 +9856,16 @@
         <v>46240.59601453703</v>
       </c>
       <c r="E146" s="6" t="s">
-        <v>385</v>
+        <v>386</v>
       </c>
       <c r="F146" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G146" s="6" t="s">
-        <v>222</v>
+        <v>223</v>
       </c>
       <c r="H146" s="6" t="s">
-        <v>223</v>
+        <v>224</v>
       </c>
       <c r="I146" s="5">
         <v>46413</v>
@@ -9880,13 +9883,13 @@
         <v>26</v>
       </c>
       <c r="N146" s="6" t="s">
-        <v>325</v>
+        <v>326</v>
       </c>
       <c r="O146" s="6" t="s">
-        <v>386</v>
+        <v>387</v>
       </c>
       <c r="P146" s="6" t="s">
-        <v>387</v>
+        <v>388</v>
       </c>
       <c r="Q146" s="5">
         <v>46413</v>
@@ -9906,7 +9909,7 @@
     </row>
     <row r="147" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A147" s="8" t="s">
-        <v>388</v>
+        <v>389</v>
       </c>
       <c r="B147" s="9">
         <v>46239.57467313657</v>
@@ -9916,16 +9919,16 @@
         <v>46240.5962641088</v>
       </c>
       <c r="E147" s="10" t="s">
-        <v>188</v>
+        <v>189</v>
       </c>
       <c r="F147" s="10" t="s">
         <v>26</v>
       </c>
       <c r="G147" s="10" t="s">
-        <v>222</v>
+        <v>223</v>
       </c>
       <c r="H147" s="10" t="s">
-        <v>223</v>
+        <v>224</v>
       </c>
       <c r="I147" s="9">
         <v>46413</v>
@@ -9943,13 +9946,13 @@
         <v>26</v>
       </c>
       <c r="N147" s="10" t="s">
-        <v>385</v>
+        <v>386</v>
       </c>
       <c r="O147" s="10" t="s">
-        <v>188</v>
+        <v>189</v>
       </c>
       <c r="P147" s="10" t="s">
-        <v>389</v>
+        <v>390</v>
       </c>
       <c r="Q147" s="10"/>
       <c r="R147" s="10"/>
@@ -9959,7 +9962,7 @@
     </row>
     <row r="148" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A148" s="4" t="s">
-        <v>390</v>
+        <v>391</v>
       </c>
       <c r="B148" s="5">
         <v>46239.57467765047</v>
@@ -9969,16 +9972,16 @@
         <v>46240.5962597801</v>
       </c>
       <c r="E148" s="6" t="s">
-        <v>188</v>
+        <v>189</v>
       </c>
       <c r="F148" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G148" s="6" t="s">
-        <v>222</v>
+        <v>223</v>
       </c>
       <c r="H148" s="6" t="s">
-        <v>223</v>
+        <v>224</v>
       </c>
       <c r="I148" s="5">
         <v>46413</v>
@@ -9996,13 +9999,13 @@
         <v>26</v>
       </c>
       <c r="N148" s="6" t="s">
-        <v>385</v>
+        <v>386</v>
       </c>
       <c r="O148" s="6" t="s">
-        <v>188</v>
+        <v>189</v>
       </c>
       <c r="P148" s="6" t="s">
-        <v>391</v>
+        <v>392</v>
       </c>
       <c r="Q148" s="6"/>
       <c r="R148" s="6"/>
@@ -10012,7 +10015,7 @@
     </row>
     <row r="149" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A149" s="8" t="s">
-        <v>392</v>
+        <v>393</v>
       </c>
       <c r="B149" s="9">
         <v>46239.57468208333</v>
@@ -10022,16 +10025,16 @@
         <v>46240.596255625</v>
       </c>
       <c r="E149" s="10" t="s">
-        <v>188</v>
+        <v>189</v>
       </c>
       <c r="F149" s="10" t="s">
         <v>26</v>
       </c>
       <c r="G149" s="10" t="s">
-        <v>222</v>
+        <v>223</v>
       </c>
       <c r="H149" s="10" t="s">
-        <v>223</v>
+        <v>224</v>
       </c>
       <c r="I149" s="9">
         <v>46413</v>
@@ -10049,13 +10052,13 @@
         <v>26</v>
       </c>
       <c r="N149" s="10" t="s">
-        <v>385</v>
+        <v>386</v>
       </c>
       <c r="O149" s="10" t="s">
-        <v>188</v>
+        <v>189</v>
       </c>
       <c r="P149" s="10" t="s">
-        <v>391</v>
+        <v>392</v>
       </c>
       <c r="Q149" s="10"/>
       <c r="R149" s="10"/>
@@ -10065,7 +10068,7 @@
     </row>
     <row r="150" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A150" s="4" t="s">
-        <v>393</v>
+        <v>394</v>
       </c>
       <c r="B150" s="5">
         <v>46239.653672326385</v>
@@ -10075,16 +10078,16 @@
         <v>46240.59625209491</v>
       </c>
       <c r="E150" s="6" t="s">
-        <v>188</v>
+        <v>189</v>
       </c>
       <c r="F150" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G150" s="6" t="s">
-        <v>222</v>
+        <v>223</v>
       </c>
       <c r="H150" s="6" t="s">
-        <v>223</v>
+        <v>224</v>
       </c>
       <c r="I150" s="5">
         <v>46413</v>
@@ -10102,10 +10105,10 @@
         <v>26</v>
       </c>
       <c r="N150" s="6" t="s">
-        <v>385</v>
+        <v>386</v>
       </c>
       <c r="O150" s="6" t="s">
-        <v>194</v>
+        <v>195</v>
       </c>
       <c r="P150" s="6" t="s">
         <v>26</v>
@@ -10118,7 +10121,7 @@
     </row>
     <row r="151" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A151" s="8" t="s">
-        <v>394</v>
+        <v>395</v>
       </c>
       <c r="B151" s="9">
         <v>46239.67752369213</v>
@@ -10134,10 +10137,10 @@
         <v>26</v>
       </c>
       <c r="G151" s="10" t="s">
-        <v>222</v>
+        <v>223</v>
       </c>
       <c r="H151" s="10" t="s">
-        <v>223</v>
+        <v>224</v>
       </c>
       <c r="I151" s="9">
         <v>46413</v>
@@ -10155,10 +10158,10 @@
         <v>26</v>
       </c>
       <c r="N151" s="10" t="s">
-        <v>385</v>
+        <v>386</v>
       </c>
       <c r="O151" s="10" t="s">
-        <v>357</v>
+        <v>358</v>
       </c>
       <c r="P151" s="10" t="s">
         <v>26</v>
@@ -10171,7 +10174,7 @@
     </row>
     <row r="152" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A152" s="4" t="s">
-        <v>395</v>
+        <v>396</v>
       </c>
       <c r="B152" s="5">
         <v>46239.67753166667</v>
@@ -10187,10 +10190,10 @@
         <v>26</v>
       </c>
       <c r="G152" s="6" t="s">
-        <v>222</v>
+        <v>223</v>
       </c>
       <c r="H152" s="6" t="s">
-        <v>223</v>
+        <v>224</v>
       </c>
       <c r="I152" s="5">
         <v>46413</v>
@@ -10208,10 +10211,10 @@
         <v>26</v>
       </c>
       <c r="N152" s="6" t="s">
-        <v>385</v>
+        <v>386</v>
       </c>
       <c r="O152" s="6" t="s">
-        <v>379</v>
+        <v>380</v>
       </c>
       <c r="P152" s="6" t="s">
         <v>26</v>
@@ -10224,7 +10227,7 @@
     </row>
     <row r="153" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A153" s="8" t="s">
-        <v>396</v>
+        <v>397</v>
       </c>
       <c r="B153" s="9">
         <v>46239.677537361116</v>
@@ -10240,10 +10243,10 @@
         <v>26</v>
       </c>
       <c r="G153" s="10" t="s">
-        <v>222</v>
+        <v>223</v>
       </c>
       <c r="H153" s="10" t="s">
-        <v>223</v>
+        <v>224</v>
       </c>
       <c r="I153" s="9">
         <v>46413</v>
@@ -10261,7 +10264,7 @@
         <v>26</v>
       </c>
       <c r="N153" s="10" t="s">
-        <v>385</v>
+        <v>386</v>
       </c>
       <c r="O153" s="10" t="s">
         <v>56</v>
@@ -10277,7 +10280,7 @@
     </row>
     <row r="154" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A154" s="4" t="s">
-        <v>397</v>
+        <v>398</v>
       </c>
       <c r="B154" s="5">
         <v>46239.67754380787</v>
@@ -10293,10 +10296,10 @@
         <v>26</v>
       </c>
       <c r="G154" s="6" t="s">
-        <v>222</v>
+        <v>223</v>
       </c>
       <c r="H154" s="6" t="s">
-        <v>223</v>
+        <v>224</v>
       </c>
       <c r="I154" s="5">
         <v>46413</v>
@@ -10314,10 +10317,10 @@
         <v>26</v>
       </c>
       <c r="N154" s="6" t="s">
-        <v>385</v>
+        <v>386</v>
       </c>
       <c r="O154" s="6" t="s">
-        <v>379</v>
+        <v>380</v>
       </c>
       <c r="P154" s="6" t="s">
         <v>26</v>
@@ -10330,7 +10333,7 @@
     </row>
     <row r="155" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A155" s="8" t="s">
-        <v>398</v>
+        <v>399</v>
       </c>
       <c r="B155" s="9">
         <v>46239.57468613426</v>
@@ -10340,7 +10343,7 @@
         <v>46240.58500695602</v>
       </c>
       <c r="E155" s="10" t="s">
-        <v>399</v>
+        <v>400</v>
       </c>
       <c r="F155" s="10" t="s">
         <v>25</v>
@@ -10364,7 +10367,7 @@
         <v>26</v>
       </c>
       <c r="O155" s="10" t="s">
-        <v>400</v>
+        <v>401</v>
       </c>
       <c r="P155" s="10" t="s">
         <v>26</v>
@@ -10377,7 +10380,7 @@
     </row>
     <row r="156" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A156" s="4" t="s">
-        <v>401</v>
+        <v>402</v>
       </c>
       <c r="B156" s="5">
         <v>46239.57468942129</v>
@@ -10387,16 +10390,16 @@
         <v>46240.596291608796</v>
       </c>
       <c r="E156" s="6" t="s">
-        <v>402</v>
+        <v>403</v>
       </c>
       <c r="F156" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G156" s="6" t="s">
-        <v>403</v>
+        <v>404</v>
       </c>
       <c r="H156" s="6" t="s">
-        <v>404</v>
+        <v>405</v>
       </c>
       <c r="I156" s="5">
         <v>46414</v>
@@ -10414,13 +10417,13 @@
         <v>26</v>
       </c>
       <c r="N156" s="6" t="s">
-        <v>399</v>
+        <v>400</v>
       </c>
       <c r="O156" s="6" t="s">
-        <v>405</v>
+        <v>406</v>
       </c>
       <c r="P156" s="6" t="s">
-        <v>399</v>
+        <v>400</v>
       </c>
       <c r="Q156" s="5">
         <v>46422</v>
@@ -10440,7 +10443,7 @@
     </row>
     <row r="157" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A157" s="8" t="s">
-        <v>406</v>
+        <v>407</v>
       </c>
       <c r="B157" s="9">
         <v>46239.57469508101</v>
@@ -10450,16 +10453,16 @@
         <v>46240.596288217595</v>
       </c>
       <c r="E157" s="10" t="s">
-        <v>407</v>
+        <v>408</v>
       </c>
       <c r="F157" s="10" t="s">
         <v>26</v>
       </c>
       <c r="G157" s="10" t="s">
-        <v>403</v>
+        <v>404</v>
       </c>
       <c r="H157" s="10" t="s">
-        <v>404</v>
+        <v>405</v>
       </c>
       <c r="I157" s="9">
         <v>46414</v>
@@ -10477,13 +10480,13 @@
         <v>26</v>
       </c>
       <c r="N157" s="10" t="s">
-        <v>399</v>
+        <v>400</v>
       </c>
       <c r="O157" s="10" t="s">
-        <v>408</v>
+        <v>409</v>
       </c>
       <c r="P157" s="10" t="s">
-        <v>399</v>
+        <v>400</v>
       </c>
       <c r="Q157" s="9">
         <v>46422</v>

--- a/data/50001592 - VITA EXPRESS INC (Venezuela).xlsx
+++ b/data/50001592 - VITA EXPRESS INC (Venezuela).xlsx
@@ -5799,7 +5799,7 @@
       </c>
       <c r="C72" s="6"/>
       <c r="D72" s="5">
-        <v>46240.59335420139</v>
+        <v>46261.77653263889</v>
       </c>
       <c r="E72" s="6" t="s">
         <v>238</v>

--- a/data/50001592 - VITA EXPRESS INC (Venezuela).xlsx
+++ b/data/50001592 - VITA EXPRESS INC (Venezuela).xlsx
@@ -4525,7 +4525,7 @@
       </c>
       <c r="C50" s="6"/>
       <c r="D50" s="5">
-        <v>46255.20385244213</v>
+        <v>46262.17148158565</v>
       </c>
       <c r="E50" s="6" t="s">
         <v>170</v>

--- a/data/50001592 - VITA EXPRESS INC (Venezuela).xlsx
+++ b/data/50001592 - VITA EXPRESS INC (Venezuela).xlsx
@@ -4478,7 +4478,7 @@
       </c>
       <c r="C49" s="10"/>
       <c r="D49" s="9">
-        <v>46240.58279298611</v>
+        <v>46262.606391203706</v>
       </c>
       <c r="E49" s="10" t="s">
         <v>167</v>
@@ -4523,9 +4523,11 @@
       <c r="B50" s="5">
         <v>46239.574202800926</v>
       </c>
-      <c r="C50" s="6"/>
+      <c r="C50" s="5">
+        <v>46262.60637799768</v>
+      </c>
       <c r="D50" s="5">
-        <v>46262.17148158565</v>
+        <v>46262.606404039354</v>
       </c>
       <c r="E50" s="6" t="s">
         <v>170</v>
@@ -4573,10 +4575,10 @@
         <v>174</v>
       </c>
       <c r="T50" s="6">
-        <v>0</v>
-      </c>
-      <c r="U50" s="12" t="s">
-        <v>49</v>
+        <v>1</v>
+      </c>
+      <c r="U50" s="7" t="s">
+        <v>27</v>
       </c>
     </row>
     <row r="51" spans="1:21" x14ac:dyDescent="0.25">
@@ -4588,7 +4590,7 @@
       </c>
       <c r="C51" s="10"/>
       <c r="D51" s="9">
-        <v>46251.97138391204</v>
+        <v>46262.60639164352</v>
       </c>
       <c r="E51" s="10" t="s">
         <v>176</v>

--- a/data/50001592 - VITA EXPRESS INC (Venezuela).xlsx
+++ b/data/50001592 - VITA EXPRESS INC (Venezuela).xlsx
@@ -11,7 +11,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1814" uniqueCount="410">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1814" uniqueCount="409">
   <si>
     <t>50001592 - VITA EXPRESS INC (Venezuela)</t>
   </si>
@@ -553,9 +553,6 @@
   </si>
   <si>
     <t xml:space="preserve">Ingenieria y diseñoo:,Plano Definitivos ot 4395  </t>
-  </si>
-  <si>
-    <t>Media</t>
   </si>
   <si>
     <t>1217190619377469</t>
@@ -4527,7 +4524,7 @@
         <v>46262.60637799768</v>
       </c>
       <c r="D50" s="5">
-        <v>46262.606404039354</v>
+        <v>46263.19028643519</v>
       </c>
       <c r="E50" s="6" t="s">
         <v>170</v>
@@ -4571,8 +4568,8 @@
       <c r="R50" s="5">
         <v>46245</v>
       </c>
-      <c r="S50" s="12" t="s">
-        <v>174</v>
+      <c r="S50" s="11" t="s">
+        <v>33</v>
       </c>
       <c r="T50" s="6">
         <v>1</v>
@@ -4583,7 +4580,7 @@
     </row>
     <row r="51" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A51" s="8" t="s">
-        <v>175</v>
+        <v>174</v>
       </c>
       <c r="B51" s="9">
         <v>46239.574207060185</v>
@@ -4593,7 +4590,7 @@
         <v>46262.60639164352</v>
       </c>
       <c r="E51" s="10" t="s">
-        <v>176</v>
+        <v>175</v>
       </c>
       <c r="F51" s="10" t="s">
         <v>26</v>
@@ -4623,10 +4620,10 @@
         <v>167</v>
       </c>
       <c r="O51" s="10" t="s">
+        <v>176</v>
+      </c>
+      <c r="P51" s="10" t="s">
         <v>177</v>
-      </c>
-      <c r="P51" s="10" t="s">
-        <v>178</v>
       </c>
       <c r="Q51" s="9">
         <v>46315</v>
@@ -4646,7 +4643,7 @@
     </row>
     <row r="52" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A52" s="4" t="s">
-        <v>179</v>
+        <v>178</v>
       </c>
       <c r="B52" s="5">
         <v>46239.57421190973</v>
@@ -4662,10 +4659,10 @@
         <v>26</v>
       </c>
       <c r="G52" s="6" t="s">
+        <v>179</v>
+      </c>
+      <c r="H52" s="6" t="s">
         <v>180</v>
-      </c>
-      <c r="H52" s="6" t="s">
-        <v>181</v>
       </c>
       <c r="I52" s="5">
         <v>46316</v>
@@ -4686,10 +4683,10 @@
         <v>167</v>
       </c>
       <c r="O52" s="6" t="s">
-        <v>176</v>
+        <v>175</v>
       </c>
       <c r="P52" s="6" t="s">
-        <v>182</v>
+        <v>181</v>
       </c>
       <c r="Q52" s="5">
         <v>46316</v>
@@ -4709,7 +4706,7 @@
     </row>
     <row r="53" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A53" s="8" t="s">
-        <v>183</v>
+        <v>182</v>
       </c>
       <c r="B53" s="9">
         <v>46239.57422061343</v>
@@ -4719,16 +4716,16 @@
         <v>46240.59657887732</v>
       </c>
       <c r="E53" s="10" t="s">
+        <v>183</v>
+      </c>
+      <c r="F53" s="10" t="s">
+        <v>26</v>
+      </c>
+      <c r="G53" s="10" t="s">
         <v>184</v>
       </c>
-      <c r="F53" s="10" t="s">
-        <v>26</v>
-      </c>
-      <c r="G53" s="10" t="s">
+      <c r="H53" s="10" t="s">
         <v>185</v>
-      </c>
-      <c r="H53" s="10" t="s">
-        <v>186</v>
       </c>
       <c r="I53" s="9">
         <v>46405</v>
@@ -4749,7 +4746,7 @@
         <v>167</v>
       </c>
       <c r="O53" s="10" t="s">
-        <v>187</v>
+        <v>186</v>
       </c>
       <c r="P53" s="10" t="s">
         <v>167</v>
@@ -4772,7 +4769,7 @@
     </row>
     <row r="54" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A54" s="4" t="s">
-        <v>188</v>
+        <v>187</v>
       </c>
       <c r="B54" s="5">
         <v>46239.57422527778</v>
@@ -4782,16 +4779,16 @@
         <v>46240.58711</v>
       </c>
       <c r="E54" s="6" t="s">
-        <v>189</v>
+        <v>188</v>
       </c>
       <c r="F54" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G54" s="6" t="s">
+        <v>184</v>
+      </c>
+      <c r="H54" s="6" t="s">
         <v>185</v>
-      </c>
-      <c r="H54" s="6" t="s">
-        <v>186</v>
       </c>
       <c r="I54" s="5">
         <v>46405</v>
@@ -4809,13 +4806,13 @@
         <v>26</v>
       </c>
       <c r="N54" s="6" t="s">
-        <v>184</v>
+        <v>183</v>
       </c>
       <c r="O54" s="6" t="s">
+        <v>188</v>
+      </c>
+      <c r="P54" s="6" t="s">
         <v>189</v>
-      </c>
-      <c r="P54" s="6" t="s">
-        <v>190</v>
       </c>
       <c r="Q54" s="6"/>
       <c r="R54" s="6"/>
@@ -4825,7 +4822,7 @@
     </row>
     <row r="55" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A55" s="8" t="s">
-        <v>191</v>
+        <v>190</v>
       </c>
       <c r="B55" s="9">
         <v>46239.5742288426</v>
@@ -4835,16 +4832,16 @@
         <v>46240.58710615741</v>
       </c>
       <c r="E55" s="10" t="s">
-        <v>189</v>
+        <v>188</v>
       </c>
       <c r="F55" s="10" t="s">
         <v>26</v>
       </c>
       <c r="G55" s="10" t="s">
+        <v>184</v>
+      </c>
+      <c r="H55" s="10" t="s">
         <v>185</v>
-      </c>
-      <c r="H55" s="10" t="s">
-        <v>186</v>
       </c>
       <c r="I55" s="9">
         <v>46405</v>
@@ -4862,13 +4859,13 @@
         <v>26</v>
       </c>
       <c r="N55" s="10" t="s">
-        <v>184</v>
+        <v>183</v>
       </c>
       <c r="O55" s="10" t="s">
-        <v>189</v>
+        <v>188</v>
       </c>
       <c r="P55" s="10" t="s">
-        <v>192</v>
+        <v>191</v>
       </c>
       <c r="Q55" s="10"/>
       <c r="R55" s="10"/>
@@ -4878,7 +4875,7 @@
     </row>
     <row r="56" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A56" s="4" t="s">
-        <v>193</v>
+        <v>192</v>
       </c>
       <c r="B56" s="5">
         <v>46239.57430761574</v>
@@ -4888,16 +4885,16 @@
         <v>46240.58710263889</v>
       </c>
       <c r="E56" s="6" t="s">
-        <v>189</v>
+        <v>188</v>
       </c>
       <c r="F56" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G56" s="6" t="s">
+        <v>184</v>
+      </c>
+      <c r="H56" s="6" t="s">
         <v>185</v>
-      </c>
-      <c r="H56" s="6" t="s">
-        <v>186</v>
       </c>
       <c r="I56" s="5">
         <v>46405</v>
@@ -4915,13 +4912,13 @@
         <v>26</v>
       </c>
       <c r="N56" s="6" t="s">
-        <v>184</v>
+        <v>183</v>
       </c>
       <c r="O56" s="6" t="s">
+        <v>188</v>
+      </c>
+      <c r="P56" s="6" t="s">
         <v>189</v>
-      </c>
-      <c r="P56" s="6" t="s">
-        <v>190</v>
       </c>
       <c r="Q56" s="6"/>
       <c r="R56" s="6"/>
@@ -4931,7 +4928,7 @@
     </row>
     <row r="57" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A57" s="8" t="s">
-        <v>194</v>
+        <v>193</v>
       </c>
       <c r="B57" s="9">
         <v>46239.66388140046</v>
@@ -4941,16 +4938,16 @@
         <v>46240.587098715274</v>
       </c>
       <c r="E57" s="10" t="s">
-        <v>189</v>
+        <v>188</v>
       </c>
       <c r="F57" s="10" t="s">
         <v>26</v>
       </c>
       <c r="G57" s="10" t="s">
+        <v>184</v>
+      </c>
+      <c r="H57" s="10" t="s">
         <v>185</v>
-      </c>
-      <c r="H57" s="10" t="s">
-        <v>186</v>
       </c>
       <c r="I57" s="9">
         <v>46405</v>
@@ -4968,10 +4965,10 @@
         <v>26</v>
       </c>
       <c r="N57" s="10" t="s">
-        <v>184</v>
+        <v>183</v>
       </c>
       <c r="O57" s="10" t="s">
-        <v>195</v>
+        <v>194</v>
       </c>
       <c r="P57" s="10" t="s">
         <v>26</v>
@@ -4984,7 +4981,7 @@
     </row>
     <row r="58" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A58" s="4" t="s">
-        <v>196</v>
+        <v>195</v>
       </c>
       <c r="B58" s="5">
         <v>46239.57431149305</v>
@@ -4994,7 +4991,7 @@
         <v>46239.7159622801</v>
       </c>
       <c r="E58" s="6" t="s">
-        <v>197</v>
+        <v>196</v>
       </c>
       <c r="F58" s="6" t="s">
         <v>25</v>
@@ -5018,7 +5015,7 @@
         <v>26</v>
       </c>
       <c r="O58" s="6" t="s">
-        <v>198</v>
+        <v>197</v>
       </c>
       <c r="P58" s="6" t="s">
         <v>26</v>
@@ -5031,7 +5028,7 @@
     </row>
     <row r="59" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A59" s="8" t="s">
-        <v>199</v>
+        <v>198</v>
       </c>
       <c r="B59" s="9">
         <v>46239.57431462963</v>
@@ -5041,16 +5038,16 @@
         <v>46240.587207523145</v>
       </c>
       <c r="E59" s="10" t="s">
+        <v>199</v>
+      </c>
+      <c r="F59" s="10" t="s">
+        <v>26</v>
+      </c>
+      <c r="G59" s="10" t="s">
         <v>200</v>
       </c>
-      <c r="F59" s="10" t="s">
-        <v>26</v>
-      </c>
-      <c r="G59" s="10" t="s">
+      <c r="H59" s="10" t="s">
         <v>201</v>
-      </c>
-      <c r="H59" s="10" t="s">
-        <v>202</v>
       </c>
       <c r="I59" s="9">
         <v>46332</v>
@@ -5068,13 +5065,13 @@
         <v>26</v>
       </c>
       <c r="N59" s="10" t="s">
-        <v>197</v>
+        <v>196</v>
       </c>
       <c r="O59" s="10" t="s">
         <v>112</v>
       </c>
       <c r="P59" s="10" t="s">
-        <v>203</v>
+        <v>202</v>
       </c>
       <c r="Q59" s="9">
         <v>46335</v>
@@ -5094,7 +5091,7 @@
     </row>
     <row r="60" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A60" s="4" t="s">
-        <v>204</v>
+        <v>203</v>
       </c>
       <c r="B60" s="5">
         <v>46239.57431895833</v>
@@ -5104,16 +5101,16 @@
         <v>46240.587203958334</v>
       </c>
       <c r="E60" s="6" t="s">
-        <v>205</v>
+        <v>204</v>
       </c>
       <c r="F60" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G60" s="6" t="s">
+        <v>200</v>
+      </c>
+      <c r="H60" s="6" t="s">
         <v>201</v>
-      </c>
-      <c r="H60" s="6" t="s">
-        <v>202</v>
       </c>
       <c r="I60" s="5">
         <v>46332</v>
@@ -5131,13 +5128,13 @@
         <v>26</v>
       </c>
       <c r="N60" s="6" t="s">
-        <v>197</v>
+        <v>196</v>
       </c>
       <c r="O60" s="6" t="s">
         <v>120</v>
       </c>
       <c r="P60" s="6" t="s">
-        <v>206</v>
+        <v>205</v>
       </c>
       <c r="Q60" s="5">
         <v>46335</v>
@@ -5157,7 +5154,7 @@
     </row>
     <row r="61" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A61" s="8" t="s">
-        <v>207</v>
+        <v>206</v>
       </c>
       <c r="B61" s="9">
         <v>46239.57432314815</v>
@@ -5167,16 +5164,16 @@
         <v>46240.587200486116</v>
       </c>
       <c r="E61" s="10" t="s">
-        <v>208</v>
+        <v>207</v>
       </c>
       <c r="F61" s="10" t="s">
         <v>26</v>
       </c>
       <c r="G61" s="10" t="s">
+        <v>200</v>
+      </c>
+      <c r="H61" s="10" t="s">
         <v>201</v>
-      </c>
-      <c r="H61" s="10" t="s">
-        <v>202</v>
       </c>
       <c r="I61" s="9">
         <v>46332</v>
@@ -5194,13 +5191,13 @@
         <v>26</v>
       </c>
       <c r="N61" s="10" t="s">
-        <v>197</v>
+        <v>196</v>
       </c>
       <c r="O61" s="10" t="s">
         <v>128</v>
       </c>
       <c r="P61" s="10" t="s">
-        <v>209</v>
+        <v>208</v>
       </c>
       <c r="Q61" s="9">
         <v>46335</v>
@@ -5220,7 +5217,7 @@
     </row>
     <row r="62" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A62" s="4" t="s">
-        <v>210</v>
+        <v>209</v>
       </c>
       <c r="B62" s="5">
         <v>46239.57432760416</v>
@@ -5230,7 +5227,7 @@
         <v>46240.58727070602</v>
       </c>
       <c r="E62" s="6" t="s">
-        <v>211</v>
+        <v>210</v>
       </c>
       <c r="F62" s="6" t="s">
         <v>26</v>
@@ -5257,13 +5254,13 @@
         <v>26</v>
       </c>
       <c r="N62" s="6" t="s">
-        <v>197</v>
+        <v>196</v>
       </c>
       <c r="O62" s="6" t="s">
-        <v>200</v>
+        <v>199</v>
       </c>
       <c r="P62" s="6" t="s">
-        <v>212</v>
+        <v>211</v>
       </c>
       <c r="Q62" s="5">
         <v>46337</v>
@@ -5283,7 +5280,7 @@
     </row>
     <row r="63" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A63" s="8" t="s">
-        <v>213</v>
+        <v>212</v>
       </c>
       <c r="B63" s="9">
         <v>46239.574331689815</v>
@@ -5293,7 +5290,7 @@
         <v>46240.58726702546</v>
       </c>
       <c r="E63" s="10" t="s">
-        <v>214</v>
+        <v>213</v>
       </c>
       <c r="F63" s="10" t="s">
         <v>26</v>
@@ -5320,13 +5317,13 @@
         <v>26</v>
       </c>
       <c r="N63" s="10" t="s">
-        <v>197</v>
+        <v>196</v>
       </c>
       <c r="O63" s="10" t="s">
-        <v>205</v>
+        <v>204</v>
       </c>
       <c r="P63" s="10" t="s">
-        <v>212</v>
+        <v>211</v>
       </c>
       <c r="Q63" s="9">
         <v>46337</v>
@@ -5346,7 +5343,7 @@
     </row>
     <row r="64" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A64" s="4" t="s">
-        <v>215</v>
+        <v>214</v>
       </c>
       <c r="B64" s="5">
         <v>46239.57433570602</v>
@@ -5356,7 +5353,7 @@
         <v>46240.58726326389</v>
       </c>
       <c r="E64" s="6" t="s">
-        <v>216</v>
+        <v>215</v>
       </c>
       <c r="F64" s="6" t="s">
         <v>26</v>
@@ -5383,13 +5380,13 @@
         <v>26</v>
       </c>
       <c r="N64" s="6" t="s">
-        <v>197</v>
+        <v>196</v>
       </c>
       <c r="O64" s="6" t="s">
-        <v>208</v>
+        <v>207</v>
       </c>
       <c r="P64" s="6" t="s">
-        <v>217</v>
+        <v>216</v>
       </c>
       <c r="Q64" s="5">
         <v>46337</v>
@@ -5409,7 +5406,7 @@
     </row>
     <row r="65" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A65" s="8" t="s">
-        <v>218</v>
+        <v>217</v>
       </c>
       <c r="B65" s="9">
         <v>46239.574339363426</v>
@@ -5419,7 +5416,7 @@
         <v>46240.57123085648</v>
       </c>
       <c r="E65" s="10" t="s">
-        <v>219</v>
+        <v>218</v>
       </c>
       <c r="F65" s="10" t="s">
         <v>25</v>
@@ -5443,7 +5440,7 @@
         <v>26</v>
       </c>
       <c r="O65" s="10" t="s">
-        <v>220</v>
+        <v>219</v>
       </c>
       <c r="P65" s="10" t="s">
         <v>26</v>
@@ -5456,7 +5453,7 @@
     </row>
     <row r="66" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A66" s="4" t="s">
-        <v>221</v>
+        <v>220</v>
       </c>
       <c r="B66" s="5">
         <v>46239.57434170139</v>
@@ -5466,16 +5463,16 @@
         <v>46240.59315164352</v>
       </c>
       <c r="E66" s="6" t="s">
+        <v>221</v>
+      </c>
+      <c r="F66" s="6" t="s">
+        <v>26</v>
+      </c>
+      <c r="G66" s="6" t="s">
         <v>222</v>
       </c>
-      <c r="F66" s="6" t="s">
-        <v>26</v>
-      </c>
-      <c r="G66" s="6" t="s">
+      <c r="H66" s="6" t="s">
         <v>223</v>
-      </c>
-      <c r="H66" s="6" t="s">
-        <v>224</v>
       </c>
       <c r="I66" s="5">
         <v>46338</v>
@@ -5493,13 +5490,13 @@
         <v>26</v>
       </c>
       <c r="N66" s="6" t="s">
-        <v>219</v>
+        <v>218</v>
       </c>
       <c r="O66" s="6" t="s">
         <v>91</v>
       </c>
       <c r="P66" s="6" t="s">
-        <v>225</v>
+        <v>224</v>
       </c>
       <c r="Q66" s="5">
         <v>46346</v>
@@ -5519,7 +5516,7 @@
     </row>
     <row r="67" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A67" s="8" t="s">
-        <v>226</v>
+        <v>225</v>
       </c>
       <c r="B67" s="9">
         <v>46239.574346504625</v>
@@ -5529,16 +5526,16 @@
         <v>46240.593254861116</v>
       </c>
       <c r="E67" s="10" t="s">
-        <v>227</v>
+        <v>226</v>
       </c>
       <c r="F67" s="10" t="s">
         <v>26</v>
       </c>
       <c r="G67" s="10" t="s">
+        <v>222</v>
+      </c>
+      <c r="H67" s="10" t="s">
         <v>223</v>
-      </c>
-      <c r="H67" s="10" t="s">
-        <v>224</v>
       </c>
       <c r="I67" s="9">
         <v>46349</v>
@@ -5556,13 +5553,13 @@
         <v>26</v>
       </c>
       <c r="N67" s="10" t="s">
-        <v>219</v>
+        <v>218</v>
       </c>
       <c r="O67" s="10" t="s">
-        <v>187</v>
+        <v>186</v>
       </c>
       <c r="P67" s="10" t="s">
-        <v>219</v>
+        <v>218</v>
       </c>
       <c r="Q67" s="9">
         <v>46367</v>
@@ -5582,7 +5579,7 @@
     </row>
     <row r="68" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A68" s="4" t="s">
-        <v>228</v>
+        <v>227</v>
       </c>
       <c r="B68" s="5">
         <v>46239.57435601852</v>
@@ -5592,16 +5589,16 @@
         <v>46240.58742517361</v>
       </c>
       <c r="E68" s="6" t="s">
-        <v>189</v>
+        <v>188</v>
       </c>
       <c r="F68" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G68" s="6" t="s">
+        <v>222</v>
+      </c>
+      <c r="H68" s="6" t="s">
         <v>223</v>
-      </c>
-      <c r="H68" s="6" t="s">
-        <v>224</v>
       </c>
       <c r="I68" s="5">
         <v>46349</v>
@@ -5619,13 +5616,13 @@
         <v>26</v>
       </c>
       <c r="N68" s="6" t="s">
-        <v>227</v>
+        <v>226</v>
       </c>
       <c r="O68" s="6" t="s">
+        <v>228</v>
+      </c>
+      <c r="P68" s="6" t="s">
         <v>229</v>
-      </c>
-      <c r="P68" s="6" t="s">
-        <v>230</v>
       </c>
       <c r="Q68" s="6"/>
       <c r="R68" s="6"/>
@@ -5635,7 +5632,7 @@
     </row>
     <row r="69" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A69" s="8" t="s">
-        <v>231</v>
+        <v>230</v>
       </c>
       <c r="B69" s="9">
         <v>46239.574361817125</v>
@@ -5645,16 +5642,16 @@
         <v>46240.58742163195</v>
       </c>
       <c r="E69" s="10" t="s">
-        <v>189</v>
+        <v>188</v>
       </c>
       <c r="F69" s="10" t="s">
         <v>26</v>
       </c>
       <c r="G69" s="10" t="s">
+        <v>222</v>
+      </c>
+      <c r="H69" s="10" t="s">
         <v>223</v>
-      </c>
-      <c r="H69" s="10" t="s">
-        <v>224</v>
       </c>
       <c r="I69" s="9">
         <v>46349</v>
@@ -5672,13 +5669,13 @@
         <v>26</v>
       </c>
       <c r="N69" s="10" t="s">
-        <v>227</v>
+        <v>226</v>
       </c>
       <c r="O69" s="10" t="s">
-        <v>232</v>
+        <v>231</v>
       </c>
       <c r="P69" s="10" t="s">
-        <v>230</v>
+        <v>229</v>
       </c>
       <c r="Q69" s="10"/>
       <c r="R69" s="10"/>
@@ -5688,7 +5685,7 @@
     </row>
     <row r="70" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A70" s="4" t="s">
-        <v>233</v>
+        <v>232</v>
       </c>
       <c r="B70" s="5">
         <v>46239.574366967594</v>
@@ -5698,16 +5695,16 @@
         <v>46240.58741825231</v>
       </c>
       <c r="E70" s="6" t="s">
-        <v>189</v>
+        <v>188</v>
       </c>
       <c r="F70" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G70" s="6" t="s">
+        <v>222</v>
+      </c>
+      <c r="H70" s="6" t="s">
         <v>223</v>
-      </c>
-      <c r="H70" s="6" t="s">
-        <v>224</v>
       </c>
       <c r="I70" s="5">
         <v>46349</v>
@@ -5725,13 +5722,13 @@
         <v>26</v>
       </c>
       <c r="N70" s="6" t="s">
-        <v>227</v>
+        <v>226</v>
       </c>
       <c r="O70" s="6" t="s">
+        <v>233</v>
+      </c>
+      <c r="P70" s="6" t="s">
         <v>234</v>
-      </c>
-      <c r="P70" s="6" t="s">
-        <v>235</v>
       </c>
       <c r="Q70" s="6"/>
       <c r="R70" s="6"/>
@@ -5741,7 +5738,7 @@
     </row>
     <row r="71" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A71" s="8" t="s">
-        <v>236</v>
+        <v>235</v>
       </c>
       <c r="B71" s="9">
         <v>46239.65279153935</v>
@@ -5751,16 +5748,16 @@
         <v>46240.58741491898</v>
       </c>
       <c r="E71" s="10" t="s">
-        <v>189</v>
+        <v>188</v>
       </c>
       <c r="F71" s="10" t="s">
         <v>26</v>
       </c>
       <c r="G71" s="10" t="s">
+        <v>222</v>
+      </c>
+      <c r="H71" s="10" t="s">
         <v>223</v>
-      </c>
-      <c r="H71" s="10" t="s">
-        <v>224</v>
       </c>
       <c r="I71" s="9">
         <v>46349</v>
@@ -5778,13 +5775,13 @@
         <v>26</v>
       </c>
       <c r="N71" s="10" t="s">
-        <v>227</v>
+        <v>226</v>
       </c>
       <c r="O71" s="10" t="s">
-        <v>222</v>
+        <v>221</v>
       </c>
       <c r="P71" s="10" t="s">
-        <v>189</v>
+        <v>188</v>
       </c>
       <c r="Q71" s="10"/>
       <c r="R71" s="10"/>
@@ -5794,7 +5791,7 @@
     </row>
     <row r="72" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A72" s="4" t="s">
-        <v>237</v>
+        <v>236</v>
       </c>
       <c r="B72" s="5">
         <v>46239.57437221065</v>
@@ -5804,7 +5801,7 @@
         <v>46261.77653263889</v>
       </c>
       <c r="E72" s="6" t="s">
-        <v>238</v>
+        <v>237</v>
       </c>
       <c r="F72" s="6" t="s">
         <v>26</v>
@@ -5831,13 +5828,13 @@
         <v>26</v>
       </c>
       <c r="N72" s="6" t="s">
-        <v>219</v>
+        <v>218</v>
       </c>
       <c r="O72" s="6" t="s">
-        <v>187</v>
+        <v>186</v>
       </c>
       <c r="P72" s="6" t="s">
-        <v>219</v>
+        <v>218</v>
       </c>
       <c r="Q72" s="5">
         <v>46370</v>
@@ -5857,7 +5854,7 @@
     </row>
     <row r="73" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A73" s="8" t="s">
-        <v>239</v>
+        <v>238</v>
       </c>
       <c r="B73" s="9">
         <v>46239.574375833334</v>
@@ -5867,7 +5864,7 @@
         <v>46240.587564953705</v>
       </c>
       <c r="E73" s="10" t="s">
-        <v>189</v>
+        <v>188</v>
       </c>
       <c r="F73" s="10" t="s">
         <v>26</v>
@@ -5894,13 +5891,13 @@
         <v>26</v>
       </c>
       <c r="N73" s="10" t="s">
-        <v>238</v>
+        <v>237</v>
       </c>
       <c r="O73" s="10" t="s">
+        <v>239</v>
+      </c>
+      <c r="P73" s="10" t="s">
         <v>240</v>
-      </c>
-      <c r="P73" s="10" t="s">
-        <v>241</v>
       </c>
       <c r="Q73" s="10"/>
       <c r="R73" s="10"/>
@@ -5910,7 +5907,7 @@
     </row>
     <row r="74" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A74" s="4" t="s">
-        <v>242</v>
+        <v>241</v>
       </c>
       <c r="B74" s="5">
         <v>46239.57437981482</v>
@@ -5920,7 +5917,7 @@
         <v>46240.587560659726</v>
       </c>
       <c r="E74" s="6" t="s">
-        <v>189</v>
+        <v>188</v>
       </c>
       <c r="F74" s="6" t="s">
         <v>26</v>
@@ -5947,13 +5944,13 @@
         <v>26</v>
       </c>
       <c r="N74" s="6" t="s">
-        <v>238</v>
+        <v>237</v>
       </c>
       <c r="O74" s="6" t="s">
-        <v>240</v>
+        <v>239</v>
       </c>
       <c r="P74" s="6" t="s">
-        <v>243</v>
+        <v>242</v>
       </c>
       <c r="Q74" s="6"/>
       <c r="R74" s="6"/>
@@ -5963,7 +5960,7 @@
     </row>
     <row r="75" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A75" s="8" t="s">
-        <v>244</v>
+        <v>243</v>
       </c>
       <c r="B75" s="9">
         <v>46239.574383750005</v>
@@ -5973,7 +5970,7 @@
         <v>46240.587557210645</v>
       </c>
       <c r="E75" s="10" t="s">
-        <v>189</v>
+        <v>188</v>
       </c>
       <c r="F75" s="10" t="s">
         <v>26</v>
@@ -6000,13 +5997,13 @@
         <v>26</v>
       </c>
       <c r="N75" s="10" t="s">
-        <v>238</v>
+        <v>237</v>
       </c>
       <c r="O75" s="10" t="s">
-        <v>245</v>
+        <v>244</v>
       </c>
       <c r="P75" s="10" t="s">
-        <v>243</v>
+        <v>242</v>
       </c>
       <c r="Q75" s="10"/>
       <c r="R75" s="10"/>
@@ -6016,7 +6013,7 @@
     </row>
     <row r="76" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A76" s="4" t="s">
-        <v>246</v>
+        <v>245</v>
       </c>
       <c r="B76" s="5">
         <v>46239.65287751157</v>
@@ -6026,7 +6023,7 @@
         <v>46240.5875534838</v>
       </c>
       <c r="E76" s="6" t="s">
-        <v>189</v>
+        <v>188</v>
       </c>
       <c r="F76" s="6" t="s">
         <v>26</v>
@@ -6053,13 +6050,13 @@
         <v>26</v>
       </c>
       <c r="N76" s="6" t="s">
-        <v>238</v>
+        <v>237</v>
       </c>
       <c r="O76" s="6" t="s">
-        <v>189</v>
+        <v>188</v>
       </c>
       <c r="P76" s="6" t="s">
-        <v>189</v>
+        <v>188</v>
       </c>
       <c r="Q76" s="6"/>
       <c r="R76" s="6"/>
@@ -6069,7 +6066,7 @@
     </row>
     <row r="77" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A77" s="8" t="s">
-        <v>247</v>
+        <v>246</v>
       </c>
       <c r="B77" s="9">
         <v>46239.574387534725</v>
@@ -6079,7 +6076,7 @@
         <v>46240.57208707176</v>
       </c>
       <c r="E77" s="10" t="s">
-        <v>248</v>
+        <v>247</v>
       </c>
       <c r="F77" s="10" t="s">
         <v>25</v>
@@ -6103,7 +6100,7 @@
         <v>26</v>
       </c>
       <c r="O77" s="10" t="s">
-        <v>249</v>
+        <v>248</v>
       </c>
       <c r="P77" s="10" t="s">
         <v>26</v>
@@ -6116,7 +6113,7 @@
     </row>
     <row r="78" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A78" s="4" t="s">
-        <v>250</v>
+        <v>249</v>
       </c>
       <c r="B78" s="5">
         <v>46239.57438989583</v>
@@ -6126,16 +6123,16 @@
         <v>46247.20311761574</v>
       </c>
       <c r="E78" s="6" t="s">
-        <v>251</v>
+        <v>250</v>
       </c>
       <c r="F78" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G78" s="6" t="s">
+        <v>200</v>
+      </c>
+      <c r="H78" s="6" t="s">
         <v>201</v>
-      </c>
-      <c r="H78" s="6" t="s">
-        <v>202</v>
       </c>
       <c r="I78" s="5">
         <v>46245</v>
@@ -6153,13 +6150,13 @@
         <v>26</v>
       </c>
       <c r="N78" s="6" t="s">
-        <v>248</v>
+        <v>247</v>
       </c>
       <c r="O78" s="6" t="s">
         <v>74</v>
       </c>
       <c r="P78" s="6" t="s">
-        <v>252</v>
+        <v>251</v>
       </c>
       <c r="Q78" s="5">
         <v>46246</v>
@@ -6179,7 +6176,7 @@
     </row>
     <row r="79" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A79" s="8" t="s">
-        <v>253</v>
+        <v>252</v>
       </c>
       <c r="B79" s="9">
         <v>46239.57439460648</v>
@@ -6189,16 +6186,16 @@
         <v>46247.2031178125</v>
       </c>
       <c r="E79" s="10" t="s">
-        <v>254</v>
+        <v>253</v>
       </c>
       <c r="F79" s="10" t="s">
         <v>26</v>
       </c>
       <c r="G79" s="10" t="s">
+        <v>200</v>
+      </c>
+      <c r="H79" s="10" t="s">
         <v>201</v>
-      </c>
-      <c r="H79" s="10" t="s">
-        <v>202</v>
       </c>
       <c r="I79" s="9">
         <v>46245</v>
@@ -6216,13 +6213,13 @@
         <v>26</v>
       </c>
       <c r="N79" s="10" t="s">
-        <v>248</v>
+        <v>247</v>
       </c>
       <c r="O79" s="10" t="s">
         <v>79</v>
       </c>
       <c r="P79" s="10" t="s">
-        <v>252</v>
+        <v>251</v>
       </c>
       <c r="Q79" s="9">
         <v>46246</v>
@@ -6242,7 +6239,7 @@
     </row>
     <row r="80" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A80" s="4" t="s">
-        <v>255</v>
+        <v>254</v>
       </c>
       <c r="B80" s="5">
         <v>46239.5743990162</v>
@@ -6252,16 +6249,16 @@
         <v>46240.58768672454</v>
       </c>
       <c r="E80" s="6" t="s">
-        <v>256</v>
+        <v>255</v>
       </c>
       <c r="F80" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G80" s="6" t="s">
+        <v>200</v>
+      </c>
+      <c r="H80" s="6" t="s">
         <v>201</v>
-      </c>
-      <c r="H80" s="6" t="s">
-        <v>202</v>
       </c>
       <c r="I80" s="5">
         <v>46372</v>
@@ -6279,13 +6276,13 @@
         <v>26</v>
       </c>
       <c r="N80" s="6" t="s">
-        <v>248</v>
+        <v>247</v>
       </c>
       <c r="O80" s="6" t="s">
         <v>153</v>
       </c>
       <c r="P80" s="6" t="s">
-        <v>257</v>
+        <v>256</v>
       </c>
       <c r="Q80" s="5">
         <v>46372</v>
@@ -6305,7 +6302,7 @@
     </row>
     <row r="81" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A81" s="8" t="s">
-        <v>258</v>
+        <v>257</v>
       </c>
       <c r="B81" s="9">
         <v>46239.59988357639</v>
@@ -6321,10 +6318,10 @@
         <v>26</v>
       </c>
       <c r="G81" s="10" t="s">
+        <v>200</v>
+      </c>
+      <c r="H81" s="10" t="s">
         <v>201</v>
-      </c>
-      <c r="H81" s="10" t="s">
-        <v>202</v>
       </c>
       <c r="I81" s="9">
         <v>46302</v>
@@ -6342,7 +6339,7 @@
         <v>26</v>
       </c>
       <c r="N81" s="10" t="s">
-        <v>248</v>
+        <v>247</v>
       </c>
       <c r="O81" s="10" t="s">
         <v>164</v>
@@ -6368,7 +6365,7 @@
     </row>
     <row r="82" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A82" s="4" t="s">
-        <v>259</v>
+        <v>258</v>
       </c>
       <c r="B82" s="5">
         <v>46239.574403680555</v>
@@ -6378,7 +6375,7 @@
         <v>46240.58015300926</v>
       </c>
       <c r="E82" s="6" t="s">
-        <v>260</v>
+        <v>259</v>
       </c>
       <c r="F82" s="6" t="s">
         <v>25</v>
@@ -6402,7 +6399,7 @@
         <v>26</v>
       </c>
       <c r="O82" s="6" t="s">
-        <v>261</v>
+        <v>260</v>
       </c>
       <c r="P82" s="6" t="s">
         <v>26</v>
@@ -6415,7 +6412,7 @@
     </row>
     <row r="83" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A83" s="8" t="s">
-        <v>262</v>
+        <v>261</v>
       </c>
       <c r="B83" s="9">
         <v>46239.57440625</v>
@@ -6425,7 +6422,7 @@
         <v>46240.593524502314</v>
       </c>
       <c r="E83" s="10" t="s">
-        <v>263</v>
+        <v>262</v>
       </c>
       <c r="F83" s="10" t="s">
         <v>26</v>
@@ -6452,13 +6449,13 @@
         <v>26</v>
       </c>
       <c r="N83" s="10" t="s">
-        <v>260</v>
+        <v>259</v>
       </c>
       <c r="O83" s="10" t="s">
-        <v>187</v>
+        <v>186</v>
       </c>
       <c r="P83" s="10" t="s">
-        <v>260</v>
+        <v>259</v>
       </c>
       <c r="Q83" s="9">
         <v>46392</v>
@@ -6478,7 +6475,7 @@
     </row>
     <row r="84" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A84" s="4" t="s">
-        <v>264</v>
+        <v>263</v>
       </c>
       <c r="B84" s="5">
         <v>46239.57441001157</v>
@@ -6488,7 +6485,7 @@
         <v>46240.58779871528</v>
       </c>
       <c r="E84" s="6" t="s">
-        <v>189</v>
+        <v>188</v>
       </c>
       <c r="F84" s="6" t="s">
         <v>26</v>
@@ -6515,13 +6512,13 @@
         <v>26</v>
       </c>
       <c r="N84" s="6" t="s">
-        <v>263</v>
+        <v>262</v>
       </c>
       <c r="O84" s="6" t="s">
-        <v>189</v>
+        <v>188</v>
       </c>
       <c r="P84" s="6" t="s">
-        <v>265</v>
+        <v>264</v>
       </c>
       <c r="Q84" s="6"/>
       <c r="R84" s="6"/>
@@ -6531,7 +6528,7 @@
     </row>
     <row r="85" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A85" s="8" t="s">
-        <v>266</v>
+        <v>265</v>
       </c>
       <c r="B85" s="9">
         <v>46239.57441357639</v>
@@ -6541,7 +6538,7 @@
         <v>46240.58779524306</v>
       </c>
       <c r="E85" s="10" t="s">
-        <v>189</v>
+        <v>188</v>
       </c>
       <c r="F85" s="10" t="s">
         <v>26</v>
@@ -6568,13 +6565,13 @@
         <v>26</v>
       </c>
       <c r="N85" s="10" t="s">
-        <v>263</v>
+        <v>262</v>
       </c>
       <c r="O85" s="10" t="s">
-        <v>189</v>
+        <v>188</v>
       </c>
       <c r="P85" s="10" t="s">
-        <v>265</v>
+        <v>264</v>
       </c>
       <c r="Q85" s="10"/>
       <c r="R85" s="10"/>
@@ -6584,7 +6581,7 @@
     </row>
     <row r="86" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A86" s="4" t="s">
-        <v>267</v>
+        <v>266</v>
       </c>
       <c r="B86" s="5">
         <v>46239.57441700231</v>
@@ -6594,7 +6591,7 @@
         <v>46240.58779197917</v>
       </c>
       <c r="E86" s="6" t="s">
-        <v>189</v>
+        <v>188</v>
       </c>
       <c r="F86" s="6" t="s">
         <v>26</v>
@@ -6621,13 +6618,13 @@
         <v>26</v>
       </c>
       <c r="N86" s="6" t="s">
-        <v>263</v>
+        <v>262</v>
       </c>
       <c r="O86" s="6" t="s">
-        <v>189</v>
+        <v>188</v>
       </c>
       <c r="P86" s="6" t="s">
-        <v>268</v>
+        <v>267</v>
       </c>
       <c r="Q86" s="6"/>
       <c r="R86" s="6"/>
@@ -6637,7 +6634,7 @@
     </row>
     <row r="87" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A87" s="8" t="s">
-        <v>269</v>
+        <v>268</v>
       </c>
       <c r="B87" s="9">
         <v>46239.65295363426</v>
@@ -6647,7 +6644,7 @@
         <v>46240.58778819445</v>
       </c>
       <c r="E87" s="10" t="s">
-        <v>189</v>
+        <v>188</v>
       </c>
       <c r="F87" s="10" t="s">
         <v>26</v>
@@ -6674,13 +6671,13 @@
         <v>26</v>
       </c>
       <c r="N87" s="10" t="s">
-        <v>263</v>
+        <v>262</v>
       </c>
       <c r="O87" s="10" t="s">
-        <v>189</v>
+        <v>188</v>
       </c>
       <c r="P87" s="10" t="s">
-        <v>189</v>
+        <v>188</v>
       </c>
       <c r="Q87" s="10"/>
       <c r="R87" s="10"/>
@@ -6690,7 +6687,7 @@
     </row>
     <row r="88" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A88" s="4" t="s">
-        <v>270</v>
+        <v>269</v>
       </c>
       <c r="B88" s="5">
         <v>46239.5744203125</v>
@@ -6700,7 +6697,7 @@
         <v>46240.59358774306</v>
       </c>
       <c r="E88" s="6" t="s">
-        <v>271</v>
+        <v>270</v>
       </c>
       <c r="F88" s="6" t="s">
         <v>26</v>
@@ -6727,10 +6724,10 @@
         <v>26</v>
       </c>
       <c r="N88" s="6" t="s">
-        <v>260</v>
+        <v>259</v>
       </c>
       <c r="O88" s="6" t="s">
-        <v>187</v>
+        <v>186</v>
       </c>
       <c r="P88" s="6" t="s">
         <v>26</v>
@@ -6753,7 +6750,7 @@
     </row>
     <row r="89" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A89" s="8" t="s">
-        <v>272</v>
+        <v>271</v>
       </c>
       <c r="B89" s="9">
         <v>46239.57442366898</v>
@@ -6763,7 +6760,7 @@
         <v>46240.5880146875</v>
       </c>
       <c r="E89" s="10" t="s">
-        <v>189</v>
+        <v>188</v>
       </c>
       <c r="F89" s="10" t="s">
         <v>26</v>
@@ -6790,13 +6787,13 @@
         <v>26</v>
       </c>
       <c r="N89" s="10" t="s">
-        <v>271</v>
+        <v>270</v>
       </c>
       <c r="O89" s="10" t="s">
+        <v>272</v>
+      </c>
+      <c r="P89" s="10" t="s">
         <v>273</v>
-      </c>
-      <c r="P89" s="10" t="s">
-        <v>274</v>
       </c>
       <c r="Q89" s="10"/>
       <c r="R89" s="10"/>
@@ -6806,7 +6803,7 @@
     </row>
     <row r="90" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A90" s="4" t="s">
-        <v>275</v>
+        <v>274</v>
       </c>
       <c r="B90" s="5">
         <v>46239.57442798611</v>
@@ -6816,7 +6813,7 @@
         <v>46240.58801127315</v>
       </c>
       <c r="E90" s="6" t="s">
-        <v>189</v>
+        <v>188</v>
       </c>
       <c r="F90" s="6" t="s">
         <v>26</v>
@@ -6843,13 +6840,13 @@
         <v>26</v>
       </c>
       <c r="N90" s="6" t="s">
-        <v>271</v>
+        <v>270</v>
       </c>
       <c r="O90" s="6" t="s">
-        <v>276</v>
+        <v>275</v>
       </c>
       <c r="P90" s="6" t="s">
-        <v>274</v>
+        <v>273</v>
       </c>
       <c r="Q90" s="6"/>
       <c r="R90" s="6"/>
@@ -6859,7 +6856,7 @@
     </row>
     <row r="91" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A91" s="8" t="s">
-        <v>277</v>
+        <v>276</v>
       </c>
       <c r="B91" s="9">
         <v>46239.57443190972</v>
@@ -6869,7 +6866,7 @@
         <v>46240.58800769676</v>
       </c>
       <c r="E91" s="10" t="s">
-        <v>189</v>
+        <v>188</v>
       </c>
       <c r="F91" s="10" t="s">
         <v>26</v>
@@ -6896,13 +6893,13 @@
         <v>26</v>
       </c>
       <c r="N91" s="10" t="s">
-        <v>271</v>
+        <v>270</v>
       </c>
       <c r="O91" s="10" t="s">
-        <v>276</v>
+        <v>275</v>
       </c>
       <c r="P91" s="10" t="s">
-        <v>274</v>
+        <v>273</v>
       </c>
       <c r="Q91" s="10"/>
       <c r="R91" s="10"/>
@@ -6912,7 +6909,7 @@
     </row>
     <row r="92" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A92" s="4" t="s">
-        <v>278</v>
+        <v>277</v>
       </c>
       <c r="B92" s="5">
         <v>46239.653021875</v>
@@ -6922,7 +6919,7 @@
         <v>46240.588004212965</v>
       </c>
       <c r="E92" s="6" t="s">
-        <v>195</v>
+        <v>194</v>
       </c>
       <c r="F92" s="6" t="s">
         <v>26</v>
@@ -6949,13 +6946,13 @@
         <v>26</v>
       </c>
       <c r="N92" s="6" t="s">
-        <v>271</v>
+        <v>270</v>
       </c>
       <c r="O92" s="6" t="s">
-        <v>276</v>
+        <v>275</v>
       </c>
       <c r="P92" s="6" t="s">
-        <v>279</v>
+        <v>278</v>
       </c>
       <c r="Q92" s="6"/>
       <c r="R92" s="6"/>
@@ -6965,7 +6962,7 @@
     </row>
     <row r="93" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A93" s="8" t="s">
-        <v>280</v>
+        <v>279</v>
       </c>
       <c r="B93" s="9">
         <v>46239.57443621528</v>
@@ -6975,7 +6972,7 @@
         <v>46246.17023978009</v>
       </c>
       <c r="E93" s="10" t="s">
-        <v>281</v>
+        <v>280</v>
       </c>
       <c r="F93" s="10" t="s">
         <v>26</v>
@@ -7002,13 +6999,13 @@
         <v>26</v>
       </c>
       <c r="N93" s="10" t="s">
-        <v>260</v>
+        <v>259</v>
       </c>
       <c r="O93" s="10" t="s">
+        <v>281</v>
+      </c>
+      <c r="P93" s="10" t="s">
         <v>282</v>
-      </c>
-      <c r="P93" s="10" t="s">
-        <v>283</v>
       </c>
       <c r="Q93" s="9">
         <v>46245</v>
@@ -7028,7 +7025,7 @@
     </row>
     <row r="94" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A94" s="4" t="s">
-        <v>284</v>
+        <v>283</v>
       </c>
       <c r="B94" s="5">
         <v>46239.57444033565</v>
@@ -7038,7 +7035,7 @@
         <v>46240.58943795139</v>
       </c>
       <c r="E94" s="6" t="s">
-        <v>189</v>
+        <v>188</v>
       </c>
       <c r="F94" s="6" t="s">
         <v>26</v>
@@ -7065,13 +7062,13 @@
         <v>26</v>
       </c>
       <c r="N94" s="6" t="s">
-        <v>281</v>
+        <v>280</v>
       </c>
       <c r="O94" s="6" t="s">
-        <v>285</v>
+        <v>284</v>
       </c>
       <c r="P94" s="6" t="s">
-        <v>281</v>
+        <v>280</v>
       </c>
       <c r="Q94" s="6"/>
       <c r="R94" s="6"/>
@@ -7081,7 +7078,7 @@
     </row>
     <row r="95" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A95" s="8" t="s">
-        <v>286</v>
+        <v>285</v>
       </c>
       <c r="B95" s="9">
         <v>46239.57444496528</v>
@@ -7091,7 +7088,7 @@
         <v>46240.589434444446</v>
       </c>
       <c r="E95" s="10" t="s">
-        <v>189</v>
+        <v>188</v>
       </c>
       <c r="F95" s="10" t="s">
         <v>26</v>
@@ -7118,13 +7115,13 @@
         <v>26</v>
       </c>
       <c r="N95" s="10" t="s">
-        <v>281</v>
+        <v>280</v>
       </c>
       <c r="O95" s="10" t="s">
-        <v>285</v>
+        <v>284</v>
       </c>
       <c r="P95" s="10" t="s">
-        <v>287</v>
+        <v>286</v>
       </c>
       <c r="Q95" s="10"/>
       <c r="R95" s="10"/>
@@ -7134,7 +7131,7 @@
     </row>
     <row r="96" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A96" s="4" t="s">
-        <v>288</v>
+        <v>287</v>
       </c>
       <c r="B96" s="5">
         <v>46239.57445002315</v>
@@ -7144,7 +7141,7 @@
         <v>46240.58943064815</v>
       </c>
       <c r="E96" s="6" t="s">
-        <v>189</v>
+        <v>188</v>
       </c>
       <c r="F96" s="6" t="s">
         <v>26</v>
@@ -7171,13 +7168,13 @@
         <v>26</v>
       </c>
       <c r="N96" s="6" t="s">
-        <v>281</v>
+        <v>280</v>
       </c>
       <c r="O96" s="6" t="s">
-        <v>289</v>
+        <v>288</v>
       </c>
       <c r="P96" s="6" t="s">
-        <v>287</v>
+        <v>286</v>
       </c>
       <c r="Q96" s="6"/>
       <c r="R96" s="6"/>
@@ -7187,7 +7184,7 @@
     </row>
     <row r="97" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A97" s="8" t="s">
-        <v>290</v>
+        <v>289</v>
       </c>
       <c r="B97" s="9">
         <v>46239.65309570602</v>
@@ -7197,7 +7194,7 @@
         <v>46240.58942697917</v>
       </c>
       <c r="E97" s="10" t="s">
-        <v>189</v>
+        <v>188</v>
       </c>
       <c r="F97" s="10" t="s">
         <v>26</v>
@@ -7224,10 +7221,10 @@
         <v>26</v>
       </c>
       <c r="N97" s="10" t="s">
-        <v>281</v>
+        <v>280</v>
       </c>
       <c r="O97" s="10" t="s">
-        <v>189</v>
+        <v>188</v>
       </c>
       <c r="P97" s="10" t="s">
         <v>26</v>
@@ -7240,7 +7237,7 @@
     </row>
     <row r="98" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A98" s="4" t="s">
-        <v>291</v>
+        <v>290</v>
       </c>
       <c r="B98" s="5">
         <v>46239.57450405092</v>
@@ -7250,7 +7247,7 @@
         <v>46240.59374053241</v>
       </c>
       <c r="E98" s="6" t="s">
-        <v>292</v>
+        <v>291</v>
       </c>
       <c r="F98" s="6" t="s">
         <v>26</v>
@@ -7277,13 +7274,13 @@
         <v>26</v>
       </c>
       <c r="N98" s="6" t="s">
-        <v>260</v>
+        <v>259</v>
       </c>
       <c r="O98" s="6" t="s">
-        <v>187</v>
+        <v>186</v>
       </c>
       <c r="P98" s="6" t="s">
-        <v>293</v>
+        <v>292</v>
       </c>
       <c r="Q98" s="5">
         <v>46400</v>
@@ -7303,7 +7300,7 @@
     </row>
     <row r="99" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A99" s="8" t="s">
-        <v>294</v>
+        <v>293</v>
       </c>
       <c r="B99" s="9">
         <v>46239.57451060185</v>
@@ -7313,7 +7310,7 @@
         <v>46240.58955791667</v>
       </c>
       <c r="E99" s="10" t="s">
-        <v>189</v>
+        <v>188</v>
       </c>
       <c r="F99" s="10" t="s">
         <v>26</v>
@@ -7340,13 +7337,13 @@
         <v>26</v>
       </c>
       <c r="N99" s="10" t="s">
-        <v>292</v>
+        <v>291</v>
       </c>
       <c r="O99" s="10" t="s">
-        <v>189</v>
+        <v>188</v>
       </c>
       <c r="P99" s="10" t="s">
-        <v>295</v>
+        <v>294</v>
       </c>
       <c r="Q99" s="10"/>
       <c r="R99" s="10"/>
@@ -7356,7 +7353,7 @@
     </row>
     <row r="100" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A100" s="4" t="s">
-        <v>296</v>
+        <v>295</v>
       </c>
       <c r="B100" s="5">
         <v>46239.57451451389</v>
@@ -7366,7 +7363,7 @@
         <v>46240.58955409723</v>
       </c>
       <c r="E100" s="6" t="s">
-        <v>189</v>
+        <v>188</v>
       </c>
       <c r="F100" s="6" t="s">
         <v>26</v>
@@ -7393,13 +7390,13 @@
         <v>26</v>
       </c>
       <c r="N100" s="6" t="s">
-        <v>292</v>
+        <v>291</v>
       </c>
       <c r="O100" s="6" t="s">
-        <v>189</v>
+        <v>188</v>
       </c>
       <c r="P100" s="6" t="s">
-        <v>297</v>
+        <v>296</v>
       </c>
       <c r="Q100" s="6"/>
       <c r="R100" s="6"/>
@@ -7409,7 +7406,7 @@
     </row>
     <row r="101" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A101" s="8" t="s">
-        <v>298</v>
+        <v>297</v>
       </c>
       <c r="B101" s="9">
         <v>46239.57451872685</v>
@@ -7419,7 +7416,7 @@
         <v>46240.589550289355</v>
       </c>
       <c r="E101" s="10" t="s">
-        <v>189</v>
+        <v>188</v>
       </c>
       <c r="F101" s="10" t="s">
         <v>26</v>
@@ -7446,13 +7443,13 @@
         <v>26</v>
       </c>
       <c r="N101" s="10" t="s">
-        <v>292</v>
+        <v>291</v>
       </c>
       <c r="O101" s="10" t="s">
-        <v>189</v>
+        <v>188</v>
       </c>
       <c r="P101" s="10" t="s">
-        <v>297</v>
+        <v>296</v>
       </c>
       <c r="Q101" s="10"/>
       <c r="R101" s="10"/>
@@ -7462,7 +7459,7 @@
     </row>
     <row r="102" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A102" s="4" t="s">
-        <v>299</v>
+        <v>298</v>
       </c>
       <c r="B102" s="5">
         <v>46239.65315884259</v>
@@ -7472,7 +7469,7 @@
         <v>46240.58954619213</v>
       </c>
       <c r="E102" s="6" t="s">
-        <v>189</v>
+        <v>188</v>
       </c>
       <c r="F102" s="6" t="s">
         <v>26</v>
@@ -7499,10 +7496,10 @@
         <v>26</v>
       </c>
       <c r="N102" s="6" t="s">
-        <v>292</v>
+        <v>291</v>
       </c>
       <c r="O102" s="6" t="s">
-        <v>195</v>
+        <v>194</v>
       </c>
       <c r="P102" s="6" t="s">
         <v>26</v>
@@ -7515,7 +7512,7 @@
     </row>
     <row r="103" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A103" s="8" t="s">
-        <v>300</v>
+        <v>299</v>
       </c>
       <c r="B103" s="9">
         <v>46239.57452252315</v>
@@ -7525,7 +7522,7 @@
         <v>46240.594121284725</v>
       </c>
       <c r="E103" s="10" t="s">
-        <v>301</v>
+        <v>300</v>
       </c>
       <c r="F103" s="10" t="s">
         <v>26</v>
@@ -7552,13 +7549,13 @@
         <v>26</v>
       </c>
       <c r="N103" s="10" t="s">
-        <v>260</v>
+        <v>259</v>
       </c>
       <c r="O103" s="10" t="s">
+        <v>301</v>
+      </c>
+      <c r="P103" s="10" t="s">
         <v>302</v>
-      </c>
-      <c r="P103" s="10" t="s">
-        <v>303</v>
       </c>
       <c r="Q103" s="9">
         <v>46401</v>
@@ -7578,7 +7575,7 @@
     </row>
     <row r="104" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A104" s="4" t="s">
-        <v>304</v>
+        <v>303</v>
       </c>
       <c r="B104" s="5">
         <v>46239.57452674769</v>
@@ -7588,7 +7585,7 @@
         <v>46240.58973622685</v>
       </c>
       <c r="E104" s="6" t="s">
-        <v>189</v>
+        <v>188</v>
       </c>
       <c r="F104" s="6" t="s">
         <v>26</v>
@@ -7615,13 +7612,13 @@
         <v>26</v>
       </c>
       <c r="N104" s="6" t="s">
-        <v>301</v>
+        <v>300</v>
       </c>
       <c r="O104" s="6" t="s">
-        <v>189</v>
+        <v>188</v>
       </c>
       <c r="P104" s="6" t="s">
-        <v>305</v>
+        <v>304</v>
       </c>
       <c r="Q104" s="6"/>
       <c r="R104" s="6"/>
@@ -7631,7 +7628,7 @@
     </row>
     <row r="105" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A105" s="8" t="s">
-        <v>306</v>
+        <v>305</v>
       </c>
       <c r="B105" s="9">
         <v>46239.574530763886</v>
@@ -7641,7 +7638,7 @@
         <v>46240.58973244213</v>
       </c>
       <c r="E105" s="10" t="s">
-        <v>189</v>
+        <v>188</v>
       </c>
       <c r="F105" s="10" t="s">
         <v>26</v>
@@ -7668,13 +7665,13 @@
         <v>26</v>
       </c>
       <c r="N105" s="10" t="s">
-        <v>301</v>
+        <v>300</v>
       </c>
       <c r="O105" s="10" t="s">
-        <v>189</v>
+        <v>188</v>
       </c>
       <c r="P105" s="10" t="s">
-        <v>301</v>
+        <v>300</v>
       </c>
       <c r="Q105" s="10"/>
       <c r="R105" s="10"/>
@@ -7684,7 +7681,7 @@
     </row>
     <row r="106" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A106" s="4" t="s">
-        <v>307</v>
+        <v>306</v>
       </c>
       <c r="B106" s="5">
         <v>46239.5745340162</v>
@@ -7694,7 +7691,7 @@
         <v>46240.589728692124</v>
       </c>
       <c r="E106" s="6" t="s">
-        <v>189</v>
+        <v>188</v>
       </c>
       <c r="F106" s="6" t="s">
         <v>26</v>
@@ -7721,13 +7718,13 @@
         <v>26</v>
       </c>
       <c r="N106" s="6" t="s">
-        <v>301</v>
+        <v>300</v>
       </c>
       <c r="O106" s="6" t="s">
-        <v>189</v>
+        <v>188</v>
       </c>
       <c r="P106" s="6" t="s">
-        <v>308</v>
+        <v>307</v>
       </c>
       <c r="Q106" s="6"/>
       <c r="R106" s="6"/>
@@ -7737,7 +7734,7 @@
     </row>
     <row r="107" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A107" s="8" t="s">
-        <v>309</v>
+        <v>308</v>
       </c>
       <c r="B107" s="9">
         <v>46239.65323541667</v>
@@ -7747,7 +7744,7 @@
         <v>46240.58972483796</v>
       </c>
       <c r="E107" s="10" t="s">
-        <v>189</v>
+        <v>188</v>
       </c>
       <c r="F107" s="10" t="s">
         <v>26</v>
@@ -7774,13 +7771,13 @@
         <v>26</v>
       </c>
       <c r="N107" s="10" t="s">
-        <v>301</v>
+        <v>300</v>
       </c>
       <c r="O107" s="10" t="s">
-        <v>195</v>
+        <v>194</v>
       </c>
       <c r="P107" s="10" t="s">
-        <v>189</v>
+        <v>188</v>
       </c>
       <c r="Q107" s="10"/>
       <c r="R107" s="10"/>
@@ -7790,7 +7787,7 @@
     </row>
     <row r="108" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A108" s="4" t="s">
-        <v>310</v>
+        <v>309</v>
       </c>
       <c r="B108" s="5">
         <v>46239.57453762731</v>
@@ -7800,7 +7797,7 @@
         <v>46240.59673913194</v>
       </c>
       <c r="E108" s="6" t="s">
-        <v>303</v>
+        <v>302</v>
       </c>
       <c r="F108" s="6" t="s">
         <v>26</v>
@@ -7827,13 +7824,13 @@
         <v>26</v>
       </c>
       <c r="N108" s="6" t="s">
-        <v>260</v>
+        <v>259</v>
       </c>
       <c r="O108" s="6" t="s">
+        <v>310</v>
+      </c>
+      <c r="P108" s="6" t="s">
         <v>311</v>
-      </c>
-      <c r="P108" s="6" t="s">
-        <v>312</v>
       </c>
       <c r="Q108" s="5">
         <v>46402</v>
@@ -7853,7 +7850,7 @@
     </row>
     <row r="109" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A109" s="8" t="s">
-        <v>313</v>
+        <v>312</v>
       </c>
       <c r="B109" s="9">
         <v>46239.57454184028</v>
@@ -7863,7 +7860,7 @@
         <v>46240.59276476852</v>
       </c>
       <c r="E109" s="10" t="s">
-        <v>189</v>
+        <v>188</v>
       </c>
       <c r="F109" s="10" t="s">
         <v>26</v>
@@ -7890,13 +7887,13 @@
         <v>26</v>
       </c>
       <c r="N109" s="10" t="s">
-        <v>303</v>
+        <v>302</v>
       </c>
       <c r="O109" s="10" t="s">
-        <v>189</v>
+        <v>188</v>
       </c>
       <c r="P109" s="10" t="s">
-        <v>314</v>
+        <v>313</v>
       </c>
       <c r="Q109" s="10"/>
       <c r="R109" s="10"/>
@@ -7906,7 +7903,7 @@
     </row>
     <row r="110" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A110" s="4" t="s">
-        <v>315</v>
+        <v>314</v>
       </c>
       <c r="B110" s="5">
         <v>46239.57454601851</v>
@@ -7916,7 +7913,7 @@
         <v>46240.59276085648</v>
       </c>
       <c r="E110" s="6" t="s">
-        <v>189</v>
+        <v>188</v>
       </c>
       <c r="F110" s="6" t="s">
         <v>26</v>
@@ -7943,13 +7940,13 @@
         <v>26</v>
       </c>
       <c r="N110" s="6" t="s">
-        <v>303</v>
+        <v>302</v>
       </c>
       <c r="O110" s="6" t="s">
-        <v>187</v>
+        <v>186</v>
       </c>
       <c r="P110" s="6" t="s">
-        <v>314</v>
+        <v>313</v>
       </c>
       <c r="Q110" s="6"/>
       <c r="R110" s="6"/>
@@ -7959,7 +7956,7 @@
     </row>
     <row r="111" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A111" s="8" t="s">
-        <v>316</v>
+        <v>315</v>
       </c>
       <c r="B111" s="9">
         <v>46239.57455318287</v>
@@ -7969,7 +7966,7 @@
         <v>46240.59275711805</v>
       </c>
       <c r="E111" s="10" t="s">
-        <v>189</v>
+        <v>188</v>
       </c>
       <c r="F111" s="10" t="s">
         <v>26</v>
@@ -7996,13 +7993,13 @@
         <v>26</v>
       </c>
       <c r="N111" s="10" t="s">
-        <v>303</v>
+        <v>302</v>
       </c>
       <c r="O111" s="10" t="s">
-        <v>187</v>
+        <v>186</v>
       </c>
       <c r="P111" s="10" t="s">
-        <v>314</v>
+        <v>313</v>
       </c>
       <c r="Q111" s="10"/>
       <c r="R111" s="10"/>
@@ -8012,7 +8009,7 @@
     </row>
     <row r="112" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A112" s="4" t="s">
-        <v>317</v>
+        <v>316</v>
       </c>
       <c r="B112" s="5">
         <v>46239.65330143519</v>
@@ -8022,7 +8019,7 @@
         <v>46240.59275344908</v>
       </c>
       <c r="E112" s="6" t="s">
-        <v>189</v>
+        <v>188</v>
       </c>
       <c r="F112" s="6" t="s">
         <v>26</v>
@@ -8049,10 +8046,10 @@
         <v>26</v>
       </c>
       <c r="N112" s="6" t="s">
-        <v>303</v>
+        <v>302</v>
       </c>
       <c r="O112" s="6" t="s">
-        <v>189</v>
+        <v>188</v>
       </c>
       <c r="P112" s="6" t="s">
         <v>26</v>
@@ -8065,7 +8062,7 @@
     </row>
     <row r="113" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A113" s="8" t="s">
-        <v>318</v>
+        <v>317</v>
       </c>
       <c r="B113" s="9">
         <v>46239.57455898148</v>
@@ -8075,7 +8072,7 @@
         <v>46240.59432991898</v>
       </c>
       <c r="E113" s="10" t="s">
-        <v>312</v>
+        <v>311</v>
       </c>
       <c r="F113" s="10" t="s">
         <v>26</v>
@@ -8102,10 +8099,10 @@
         <v>26</v>
       </c>
       <c r="N113" s="10" t="s">
-        <v>260</v>
+        <v>259</v>
       </c>
       <c r="O113" s="10" t="s">
-        <v>319</v>
+        <v>318</v>
       </c>
       <c r="P113" s="10" t="s">
         <v>26</v>
@@ -8128,7 +8125,7 @@
     </row>
     <row r="114" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A114" s="4" t="s">
-        <v>320</v>
+        <v>319</v>
       </c>
       <c r="B114" s="5">
         <v>46239.57456341435</v>
@@ -8138,7 +8135,7 @@
         <v>46240.59289621528</v>
       </c>
       <c r="E114" s="6" t="s">
-        <v>189</v>
+        <v>188</v>
       </c>
       <c r="F114" s="6" t="s">
         <v>26</v>
@@ -8165,13 +8162,13 @@
         <v>26</v>
       </c>
       <c r="N114" s="6" t="s">
-        <v>312</v>
+        <v>311</v>
       </c>
       <c r="O114" s="6" t="s">
-        <v>189</v>
+        <v>188</v>
       </c>
       <c r="P114" s="6" t="s">
-        <v>321</v>
+        <v>320</v>
       </c>
       <c r="Q114" s="6"/>
       <c r="R114" s="6"/>
@@ -8181,7 +8178,7 @@
     </row>
     <row r="115" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A115" s="8" t="s">
-        <v>322</v>
+        <v>321</v>
       </c>
       <c r="B115" s="9">
         <v>46239.57456761574</v>
@@ -8191,7 +8188,7 @@
         <v>46240.59289185185</v>
       </c>
       <c r="E115" s="10" t="s">
-        <v>189</v>
+        <v>188</v>
       </c>
       <c r="F115" s="10" t="s">
         <v>26</v>
@@ -8218,13 +8215,13 @@
         <v>26</v>
       </c>
       <c r="N115" s="10" t="s">
-        <v>312</v>
+        <v>311</v>
       </c>
       <c r="O115" s="10" t="s">
-        <v>189</v>
+        <v>188</v>
       </c>
       <c r="P115" s="10" t="s">
-        <v>321</v>
+        <v>320</v>
       </c>
       <c r="Q115" s="10"/>
       <c r="R115" s="10"/>
@@ -8234,7 +8231,7 @@
     </row>
     <row r="116" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A116" s="4" t="s">
-        <v>323</v>
+        <v>322</v>
       </c>
       <c r="B116" s="5">
         <v>46239.574571840276</v>
@@ -8244,7 +8241,7 @@
         <v>46240.59288778935</v>
       </c>
       <c r="E116" s="6" t="s">
-        <v>189</v>
+        <v>188</v>
       </c>
       <c r="F116" s="6" t="s">
         <v>26</v>
@@ -8271,13 +8268,13 @@
         <v>26</v>
       </c>
       <c r="N116" s="6" t="s">
-        <v>312</v>
+        <v>311</v>
       </c>
       <c r="O116" s="6" t="s">
-        <v>189</v>
+        <v>188</v>
       </c>
       <c r="P116" s="6" t="s">
-        <v>321</v>
+        <v>320</v>
       </c>
       <c r="Q116" s="6"/>
       <c r="R116" s="6"/>
@@ -8287,7 +8284,7 @@
     </row>
     <row r="117" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A117" s="8" t="s">
-        <v>324</v>
+        <v>323</v>
       </c>
       <c r="B117" s="9">
         <v>46239.65337195602</v>
@@ -8297,7 +8294,7 @@
         <v>46240.59288347222</v>
       </c>
       <c r="E117" s="10" t="s">
-        <v>189</v>
+        <v>188</v>
       </c>
       <c r="F117" s="10" t="s">
         <v>26</v>
@@ -8324,13 +8321,13 @@
         <v>26</v>
       </c>
       <c r="N117" s="10" t="s">
-        <v>312</v>
+        <v>311</v>
       </c>
       <c r="O117" s="10" t="s">
-        <v>195</v>
+        <v>194</v>
       </c>
       <c r="P117" s="10" t="s">
-        <v>189</v>
+        <v>188</v>
       </c>
       <c r="Q117" s="10"/>
       <c r="R117" s="10"/>
@@ -8340,7 +8337,7 @@
     </row>
     <row r="118" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A118" s="4" t="s">
-        <v>325</v>
+        <v>324</v>
       </c>
       <c r="B118" s="5">
         <v>46239.57457591435</v>
@@ -8350,7 +8347,7 @@
         <v>46240.58467253472</v>
       </c>
       <c r="E118" s="6" t="s">
-        <v>326</v>
+        <v>325</v>
       </c>
       <c r="F118" s="6" t="s">
         <v>25</v>
@@ -8374,7 +8371,7 @@
         <v>26</v>
       </c>
       <c r="O118" s="6" t="s">
-        <v>327</v>
+        <v>326</v>
       </c>
       <c r="P118" s="6" t="s">
         <v>26</v>
@@ -8387,7 +8384,7 @@
     </row>
     <row r="119" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A119" s="8" t="s">
-        <v>328</v>
+        <v>327</v>
       </c>
       <c r="B119" s="9">
         <v>46239.57457920139</v>
@@ -8397,16 +8394,16 @@
         <v>46240.595475775466</v>
       </c>
       <c r="E119" s="10" t="s">
+        <v>328</v>
+      </c>
+      <c r="F119" s="10" t="s">
+        <v>26</v>
+      </c>
+      <c r="G119" s="10" t="s">
         <v>329</v>
       </c>
-      <c r="F119" s="10" t="s">
-        <v>26</v>
-      </c>
-      <c r="G119" s="10" t="s">
+      <c r="H119" s="10" t="s">
         <v>330</v>
-      </c>
-      <c r="H119" s="10" t="s">
-        <v>331</v>
       </c>
       <c r="I119" s="9">
         <v>46407</v>
@@ -8424,13 +8421,13 @@
         <v>26</v>
       </c>
       <c r="N119" s="10" t="s">
-        <v>326</v>
+        <v>325</v>
       </c>
       <c r="O119" s="10" t="s">
+        <v>331</v>
+      </c>
+      <c r="P119" s="10" t="s">
         <v>332</v>
-      </c>
-      <c r="P119" s="10" t="s">
-        <v>333</v>
       </c>
       <c r="Q119" s="9">
         <v>46407</v>
@@ -8450,7 +8447,7 @@
     </row>
     <row r="120" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A120" s="4" t="s">
-        <v>334</v>
+        <v>333</v>
       </c>
       <c r="B120" s="5">
         <v>46239.57458372685</v>
@@ -8460,16 +8457,16 @@
         <v>46240.595126388886</v>
       </c>
       <c r="E120" s="6" t="s">
-        <v>189</v>
+        <v>188</v>
       </c>
       <c r="F120" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G120" s="6" t="s">
+        <v>329</v>
+      </c>
+      <c r="H120" s="6" t="s">
         <v>330</v>
-      </c>
-      <c r="H120" s="6" t="s">
-        <v>331</v>
       </c>
       <c r="I120" s="5">
         <v>46407</v>
@@ -8487,13 +8484,13 @@
         <v>26</v>
       </c>
       <c r="N120" s="6" t="s">
-        <v>329</v>
+        <v>328</v>
       </c>
       <c r="O120" s="6" t="s">
-        <v>189</v>
+        <v>188</v>
       </c>
       <c r="P120" s="6" t="s">
-        <v>335</v>
+        <v>334</v>
       </c>
       <c r="Q120" s="6"/>
       <c r="R120" s="6"/>
@@ -8503,7 +8500,7 @@
     </row>
     <row r="121" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A121" s="8" t="s">
-        <v>336</v>
+        <v>335</v>
       </c>
       <c r="B121" s="9">
         <v>46239.574587662035</v>
@@ -8513,16 +8510,16 @@
         <v>46240.59512229166</v>
       </c>
       <c r="E121" s="10" t="s">
-        <v>189</v>
+        <v>188</v>
       </c>
       <c r="F121" s="10" t="s">
         <v>26</v>
       </c>
       <c r="G121" s="10" t="s">
+        <v>329</v>
+      </c>
+      <c r="H121" s="10" t="s">
         <v>330</v>
-      </c>
-      <c r="H121" s="10" t="s">
-        <v>331</v>
       </c>
       <c r="I121" s="9">
         <v>46407</v>
@@ -8540,13 +8537,13 @@
         <v>26</v>
       </c>
       <c r="N121" s="10" t="s">
-        <v>329</v>
+        <v>328</v>
       </c>
       <c r="O121" s="10" t="s">
-        <v>189</v>
+        <v>188</v>
       </c>
       <c r="P121" s="10" t="s">
-        <v>337</v>
+        <v>336</v>
       </c>
       <c r="Q121" s="10"/>
       <c r="R121" s="10"/>
@@ -8556,7 +8553,7 @@
     </row>
     <row r="122" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A122" s="4" t="s">
-        <v>338</v>
+        <v>337</v>
       </c>
       <c r="B122" s="5">
         <v>46239.57459146991</v>
@@ -8566,16 +8563,16 @@
         <v>46240.59511797453</v>
       </c>
       <c r="E122" s="6" t="s">
-        <v>189</v>
+        <v>188</v>
       </c>
       <c r="F122" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G122" s="6" t="s">
+        <v>329</v>
+      </c>
+      <c r="H122" s="6" t="s">
         <v>330</v>
-      </c>
-      <c r="H122" s="6" t="s">
-        <v>331</v>
       </c>
       <c r="I122" s="5">
         <v>46407</v>
@@ -8593,13 +8590,13 @@
         <v>26</v>
       </c>
       <c r="N122" s="6" t="s">
-        <v>329</v>
+        <v>328</v>
       </c>
       <c r="O122" s="6" t="s">
-        <v>189</v>
+        <v>188</v>
       </c>
       <c r="P122" s="6" t="s">
-        <v>335</v>
+        <v>334</v>
       </c>
       <c r="Q122" s="6"/>
       <c r="R122" s="6"/>
@@ -8609,7 +8606,7 @@
     </row>
     <row r="123" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A123" s="8" t="s">
-        <v>339</v>
+        <v>338</v>
       </c>
       <c r="B123" s="9">
         <v>46239.65343762732</v>
@@ -8619,16 +8616,16 @@
         <v>46240.5951130787</v>
       </c>
       <c r="E123" s="10" t="s">
-        <v>189</v>
+        <v>188</v>
       </c>
       <c r="F123" s="10" t="s">
         <v>26</v>
       </c>
       <c r="G123" s="10" t="s">
+        <v>329</v>
+      </c>
+      <c r="H123" s="10" t="s">
         <v>330</v>
-      </c>
-      <c r="H123" s="10" t="s">
-        <v>331</v>
       </c>
       <c r="I123" s="9">
         <v>46407</v>
@@ -8646,10 +8643,10 @@
         <v>26</v>
       </c>
       <c r="N123" s="10" t="s">
-        <v>329</v>
+        <v>328</v>
       </c>
       <c r="O123" s="10" t="s">
-        <v>189</v>
+        <v>188</v>
       </c>
       <c r="P123" s="10" t="s">
         <v>26</v>
@@ -8662,7 +8659,7 @@
     </row>
     <row r="124" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A124" s="4" t="s">
-        <v>340</v>
+        <v>339</v>
       </c>
       <c r="B124" s="5">
         <v>46239.665801446754</v>
@@ -8678,10 +8675,10 @@
         <v>26</v>
       </c>
       <c r="G124" s="6" t="s">
+        <v>329</v>
+      </c>
+      <c r="H124" s="6" t="s">
         <v>330</v>
-      </c>
-      <c r="H124" s="6" t="s">
-        <v>331</v>
       </c>
       <c r="I124" s="5">
         <v>46407</v>
@@ -8699,13 +8696,13 @@
         <v>26</v>
       </c>
       <c r="N124" s="6" t="s">
-        <v>329</v>
+        <v>328</v>
       </c>
       <c r="O124" s="6" t="s">
         <v>56</v>
       </c>
       <c r="P124" s="6" t="s">
-        <v>341</v>
+        <v>340</v>
       </c>
       <c r="Q124" s="6"/>
       <c r="R124" s="6"/>
@@ -8715,7 +8712,7 @@
     </row>
     <row r="125" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A125" s="8" t="s">
-        <v>342</v>
+        <v>341</v>
       </c>
       <c r="B125" s="9">
         <v>46239.665817581015</v>
@@ -8731,10 +8728,10 @@
         <v>26</v>
       </c>
       <c r="G125" s="10" t="s">
+        <v>329</v>
+      </c>
+      <c r="H125" s="10" t="s">
         <v>330</v>
-      </c>
-      <c r="H125" s="10" t="s">
-        <v>331</v>
       </c>
       <c r="I125" s="9">
         <v>46407</v>
@@ -8752,13 +8749,13 @@
         <v>26</v>
       </c>
       <c r="N125" s="10" t="s">
-        <v>329</v>
+        <v>328</v>
       </c>
       <c r="O125" s="10" t="s">
         <v>56</v>
       </c>
       <c r="P125" s="10" t="s">
-        <v>343</v>
+        <v>342</v>
       </c>
       <c r="Q125" s="10"/>
       <c r="R125" s="10"/>
@@ -8768,7 +8765,7 @@
     </row>
     <row r="126" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A126" s="4" t="s">
-        <v>344</v>
+        <v>343</v>
       </c>
       <c r="B126" s="5">
         <v>46239.66583704861</v>
@@ -8784,10 +8781,10 @@
         <v>26</v>
       </c>
       <c r="G126" s="6" t="s">
+        <v>329</v>
+      </c>
+      <c r="H126" s="6" t="s">
         <v>330</v>
-      </c>
-      <c r="H126" s="6" t="s">
-        <v>331</v>
       </c>
       <c r="I126" s="5">
         <v>46407</v>
@@ -8805,13 +8802,13 @@
         <v>26</v>
       </c>
       <c r="N126" s="6" t="s">
-        <v>329</v>
+        <v>328</v>
       </c>
       <c r="O126" s="6" t="s">
         <v>56</v>
       </c>
       <c r="P126" s="6" t="s">
-        <v>345</v>
+        <v>344</v>
       </c>
       <c r="Q126" s="6"/>
       <c r="R126" s="6"/>
@@ -8821,7 +8818,7 @@
     </row>
     <row r="127" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A127" s="8" t="s">
-        <v>346</v>
+        <v>345</v>
       </c>
       <c r="B127" s="9">
         <v>46239.66587196759</v>
@@ -8837,10 +8834,10 @@
         <v>26</v>
       </c>
       <c r="G127" s="10" t="s">
+        <v>329</v>
+      </c>
+      <c r="H127" s="10" t="s">
         <v>330</v>
-      </c>
-      <c r="H127" s="10" t="s">
-        <v>331</v>
       </c>
       <c r="I127" s="9">
         <v>46407</v>
@@ -8858,13 +8855,13 @@
         <v>26</v>
       </c>
       <c r="N127" s="10" t="s">
-        <v>329</v>
+        <v>328</v>
       </c>
       <c r="O127" s="10" t="s">
         <v>56</v>
       </c>
       <c r="P127" s="10" t="s">
-        <v>347</v>
+        <v>346</v>
       </c>
       <c r="Q127" s="10"/>
       <c r="R127" s="10"/>
@@ -8874,7 +8871,7 @@
     </row>
     <row r="128" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A128" s="4" t="s">
-        <v>348</v>
+        <v>347</v>
       </c>
       <c r="B128" s="5">
         <v>46239.57459537037</v>
@@ -8884,7 +8881,7 @@
         <v>46240.595416041666</v>
       </c>
       <c r="E128" s="6" t="s">
-        <v>349</v>
+        <v>348</v>
       </c>
       <c r="F128" s="6" t="s">
         <v>26</v>
@@ -8911,10 +8908,10 @@
         <v>26</v>
       </c>
       <c r="N128" s="6" t="s">
-        <v>326</v>
+        <v>325</v>
       </c>
       <c r="O128" s="6" t="s">
-        <v>350</v>
+        <v>349</v>
       </c>
       <c r="P128" s="6" t="s">
         <v>26</v>
@@ -8937,7 +8934,7 @@
     </row>
     <row r="129" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A129" s="8" t="s">
-        <v>351</v>
+        <v>350</v>
       </c>
       <c r="B129" s="9">
         <v>46239.57459956019</v>
@@ -8947,7 +8944,7 @@
         <v>46240.59525278935</v>
       </c>
       <c r="E129" s="10" t="s">
-        <v>189</v>
+        <v>188</v>
       </c>
       <c r="F129" s="10" t="s">
         <v>26</v>
@@ -8974,13 +8971,13 @@
         <v>26</v>
       </c>
       <c r="N129" s="10" t="s">
-        <v>349</v>
+        <v>348</v>
       </c>
       <c r="O129" s="10" t="s">
-        <v>189</v>
+        <v>188</v>
       </c>
       <c r="P129" s="10" t="s">
-        <v>352</v>
+        <v>351</v>
       </c>
       <c r="Q129" s="10"/>
       <c r="R129" s="10"/>
@@ -8990,7 +8987,7 @@
     </row>
     <row r="130" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A130" s="4" t="s">
-        <v>353</v>
+        <v>352</v>
       </c>
       <c r="B130" s="5">
         <v>46239.57460317129</v>
@@ -9000,7 +8997,7 @@
         <v>46240.595248032405</v>
       </c>
       <c r="E130" s="6" t="s">
-        <v>189</v>
+        <v>188</v>
       </c>
       <c r="F130" s="6" t="s">
         <v>26</v>
@@ -9027,13 +9024,13 @@
         <v>26</v>
       </c>
       <c r="N130" s="6" t="s">
-        <v>349</v>
+        <v>348</v>
       </c>
       <c r="O130" s="6" t="s">
-        <v>189</v>
+        <v>188</v>
       </c>
       <c r="P130" s="6" t="s">
-        <v>352</v>
+        <v>351</v>
       </c>
       <c r="Q130" s="6"/>
       <c r="R130" s="6"/>
@@ -9043,7 +9040,7 @@
     </row>
     <row r="131" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A131" s="8" t="s">
-        <v>354</v>
+        <v>353</v>
       </c>
       <c r="B131" s="9">
         <v>46239.57460717593</v>
@@ -9053,7 +9050,7 @@
         <v>46240.595243749995</v>
       </c>
       <c r="E131" s="10" t="s">
-        <v>189</v>
+        <v>188</v>
       </c>
       <c r="F131" s="10" t="s">
         <v>26</v>
@@ -9080,13 +9077,13 @@
         <v>26</v>
       </c>
       <c r="N131" s="10" t="s">
-        <v>349</v>
+        <v>348</v>
       </c>
       <c r="O131" s="10" t="s">
-        <v>189</v>
+        <v>188</v>
       </c>
       <c r="P131" s="10" t="s">
-        <v>355</v>
+        <v>354</v>
       </c>
       <c r="Q131" s="10"/>
       <c r="R131" s="10"/>
@@ -9096,7 +9093,7 @@
     </row>
     <row r="132" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A132" s="4" t="s">
-        <v>356</v>
+        <v>355</v>
       </c>
       <c r="B132" s="5">
         <v>46239.653502546294</v>
@@ -9106,7 +9103,7 @@
         <v>46240.595240069444</v>
       </c>
       <c r="E132" s="6" t="s">
-        <v>189</v>
+        <v>188</v>
       </c>
       <c r="F132" s="6" t="s">
         <v>26</v>
@@ -9133,10 +9130,10 @@
         <v>26</v>
       </c>
       <c r="N132" s="6" t="s">
-        <v>349</v>
+        <v>348</v>
       </c>
       <c r="O132" s="6" t="s">
-        <v>195</v>
+        <v>194</v>
       </c>
       <c r="P132" s="6" t="s">
         <v>26</v>
@@ -9149,7 +9146,7 @@
     </row>
     <row r="133" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A133" s="8" t="s">
-        <v>357</v>
+        <v>356</v>
       </c>
       <c r="B133" s="9">
         <v>46239.67035252315</v>
@@ -9159,7 +9156,7 @@
         <v>46240.59523623843</v>
       </c>
       <c r="E133" s="10" t="s">
-        <v>358</v>
+        <v>357</v>
       </c>
       <c r="F133" s="10" t="s">
         <v>26</v>
@@ -9186,13 +9183,13 @@
         <v>26</v>
       </c>
       <c r="N133" s="10" t="s">
-        <v>349</v>
+        <v>348</v>
       </c>
       <c r="O133" s="10" t="s">
         <v>56</v>
       </c>
       <c r="P133" s="10" t="s">
-        <v>359</v>
+        <v>358</v>
       </c>
       <c r="Q133" s="10"/>
       <c r="R133" s="10"/>
@@ -9202,7 +9199,7 @@
     </row>
     <row r="134" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A134" s="4" t="s">
-        <v>360</v>
+        <v>359</v>
       </c>
       <c r="B134" s="5">
         <v>46239.670362372686</v>
@@ -9212,7 +9209,7 @@
         <v>46240.595232673615</v>
       </c>
       <c r="E134" s="6" t="s">
-        <v>361</v>
+        <v>360</v>
       </c>
       <c r="F134" s="6" t="s">
         <v>26</v>
@@ -9239,13 +9236,13 @@
         <v>26</v>
       </c>
       <c r="N134" s="6" t="s">
-        <v>349</v>
+        <v>348</v>
       </c>
       <c r="O134" s="6" t="s">
         <v>56</v>
       </c>
       <c r="P134" s="6" t="s">
-        <v>362</v>
+        <v>361</v>
       </c>
       <c r="Q134" s="6"/>
       <c r="R134" s="6"/>
@@ -9255,7 +9252,7 @@
     </row>
     <row r="135" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A135" s="8" t="s">
-        <v>363</v>
+        <v>362</v>
       </c>
       <c r="B135" s="9">
         <v>46239.67036836805</v>
@@ -9265,7 +9262,7 @@
         <v>46240.59522915509</v>
       </c>
       <c r="E135" s="10" t="s">
-        <v>364</v>
+        <v>363</v>
       </c>
       <c r="F135" s="10" t="s">
         <v>26</v>
@@ -9292,13 +9289,13 @@
         <v>26</v>
       </c>
       <c r="N135" s="10" t="s">
-        <v>349</v>
+        <v>348</v>
       </c>
       <c r="O135" s="10" t="s">
         <v>56</v>
       </c>
       <c r="P135" s="10" t="s">
-        <v>365</v>
+        <v>364</v>
       </c>
       <c r="Q135" s="10"/>
       <c r="R135" s="10"/>
@@ -9308,7 +9305,7 @@
     </row>
     <row r="136" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A136" s="4" t="s">
-        <v>366</v>
+        <v>365</v>
       </c>
       <c r="B136" s="5">
         <v>46239.670374050926</v>
@@ -9318,7 +9315,7 @@
         <v>46240.5952253588</v>
       </c>
       <c r="E136" s="6" t="s">
-        <v>367</v>
+        <v>366</v>
       </c>
       <c r="F136" s="6" t="s">
         <v>26</v>
@@ -9345,13 +9342,13 @@
         <v>26</v>
       </c>
       <c r="N136" s="6" t="s">
-        <v>349</v>
+        <v>348</v>
       </c>
       <c r="O136" s="6" t="s">
         <v>56</v>
       </c>
       <c r="P136" s="6" t="s">
-        <v>368</v>
+        <v>367</v>
       </c>
       <c r="Q136" s="6"/>
       <c r="R136" s="6"/>
@@ -9361,7 +9358,7 @@
     </row>
     <row r="137" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A137" s="8" t="s">
-        <v>369</v>
+        <v>368</v>
       </c>
       <c r="B137" s="9">
         <v>46239.57461079861</v>
@@ -9371,16 +9368,16 @@
         <v>46240.59608133102</v>
       </c>
       <c r="E137" s="10" t="s">
-        <v>370</v>
+        <v>369</v>
       </c>
       <c r="F137" s="10" t="s">
         <v>26</v>
       </c>
       <c r="G137" s="10" t="s">
+        <v>222</v>
+      </c>
+      <c r="H137" s="10" t="s">
         <v>223</v>
-      </c>
-      <c r="H137" s="10" t="s">
-        <v>224</v>
       </c>
       <c r="I137" s="9">
         <v>46412</v>
@@ -9398,13 +9395,13 @@
         <v>26</v>
       </c>
       <c r="N137" s="10" t="s">
-        <v>326</v>
+        <v>325</v>
       </c>
       <c r="O137" s="10" t="s">
-        <v>371</v>
+        <v>370</v>
       </c>
       <c r="P137" s="10" t="s">
-        <v>326</v>
+        <v>325</v>
       </c>
       <c r="Q137" s="9">
         <v>46412</v>
@@ -9424,7 +9421,7 @@
     </row>
     <row r="138" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A138" s="4" t="s">
-        <v>372</v>
+        <v>371</v>
       </c>
       <c r="B138" s="5">
         <v>46239.57461494213</v>
@@ -9434,16 +9431,16 @@
         <v>46240.59571179398</v>
       </c>
       <c r="E138" s="6" t="s">
-        <v>189</v>
+        <v>188</v>
       </c>
       <c r="F138" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G138" s="6" t="s">
+        <v>222</v>
+      </c>
+      <c r="H138" s="6" t="s">
         <v>223</v>
-      </c>
-      <c r="H138" s="6" t="s">
-        <v>224</v>
       </c>
       <c r="I138" s="5">
         <v>46412</v>
@@ -9461,13 +9458,13 @@
         <v>26</v>
       </c>
       <c r="N138" s="6" t="s">
-        <v>370</v>
+        <v>369</v>
       </c>
       <c r="O138" s="6" t="s">
-        <v>189</v>
+        <v>188</v>
       </c>
       <c r="P138" s="6" t="s">
-        <v>373</v>
+        <v>372</v>
       </c>
       <c r="Q138" s="6"/>
       <c r="R138" s="6"/>
@@ -9477,7 +9474,7 @@
     </row>
     <row r="139" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A139" s="8" t="s">
-        <v>374</v>
+        <v>373</v>
       </c>
       <c r="B139" s="9">
         <v>46239.574618680555</v>
@@ -9487,16 +9484,16 @@
         <v>46240.595708611116</v>
       </c>
       <c r="E139" s="10" t="s">
-        <v>189</v>
+        <v>188</v>
       </c>
       <c r="F139" s="10" t="s">
         <v>26</v>
       </c>
       <c r="G139" s="10" t="s">
+        <v>222</v>
+      </c>
+      <c r="H139" s="10" t="s">
         <v>223</v>
-      </c>
-      <c r="H139" s="10" t="s">
-        <v>224</v>
       </c>
       <c r="I139" s="9">
         <v>46412</v>
@@ -9514,13 +9511,13 @@
         <v>26</v>
       </c>
       <c r="N139" s="10" t="s">
-        <v>370</v>
+        <v>369</v>
       </c>
       <c r="O139" s="10" t="s">
-        <v>189</v>
+        <v>188</v>
       </c>
       <c r="P139" s="10" t="s">
-        <v>373</v>
+        <v>372</v>
       </c>
       <c r="Q139" s="10"/>
       <c r="R139" s="10"/>
@@ -9530,7 +9527,7 @@
     </row>
     <row r="140" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A140" s="4" t="s">
-        <v>375</v>
+        <v>374</v>
       </c>
       <c r="B140" s="5">
         <v>46239.57462254629</v>
@@ -9540,16 +9537,16 @@
         <v>46240.59570520833</v>
       </c>
       <c r="E140" s="6" t="s">
-        <v>189</v>
+        <v>188</v>
       </c>
       <c r="F140" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G140" s="6" t="s">
+        <v>222</v>
+      </c>
+      <c r="H140" s="6" t="s">
         <v>223</v>
-      </c>
-      <c r="H140" s="6" t="s">
-        <v>224</v>
       </c>
       <c r="I140" s="5">
         <v>46412</v>
@@ -9567,13 +9564,13 @@
         <v>26</v>
       </c>
       <c r="N140" s="6" t="s">
-        <v>370</v>
+        <v>369</v>
       </c>
       <c r="O140" s="6" t="s">
-        <v>189</v>
+        <v>188</v>
       </c>
       <c r="P140" s="6" t="s">
-        <v>376</v>
+        <v>375</v>
       </c>
       <c r="Q140" s="6"/>
       <c r="R140" s="6"/>
@@ -9583,7 +9580,7 @@
     </row>
     <row r="141" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A141" s="8" t="s">
-        <v>377</v>
+        <v>376</v>
       </c>
       <c r="B141" s="9">
         <v>46239.65356868056</v>
@@ -9593,16 +9590,16 @@
         <v>46240.59570181713</v>
       </c>
       <c r="E141" s="10" t="s">
-        <v>189</v>
+        <v>188</v>
       </c>
       <c r="F141" s="10" t="s">
         <v>26</v>
       </c>
       <c r="G141" s="10" t="s">
+        <v>222</v>
+      </c>
+      <c r="H141" s="10" t="s">
         <v>223</v>
-      </c>
-      <c r="H141" s="10" t="s">
-        <v>224</v>
       </c>
       <c r="I141" s="9">
         <v>46412</v>
@@ -9620,13 +9617,13 @@
         <v>26</v>
       </c>
       <c r="N141" s="10" t="s">
-        <v>370</v>
+        <v>369</v>
       </c>
       <c r="O141" s="10" t="s">
-        <v>195</v>
+        <v>194</v>
       </c>
       <c r="P141" s="10" t="s">
-        <v>370</v>
+        <v>369</v>
       </c>
       <c r="Q141" s="10"/>
       <c r="R141" s="10"/>
@@ -9636,7 +9633,7 @@
     </row>
     <row r="142" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A142" s="4" t="s">
-        <v>378</v>
+        <v>377</v>
       </c>
       <c r="B142" s="5">
         <v>46239.675931875</v>
@@ -9652,10 +9649,10 @@
         <v>26</v>
       </c>
       <c r="G142" s="6" t="s">
+        <v>222</v>
+      </c>
+      <c r="H142" s="6" t="s">
         <v>223</v>
-      </c>
-      <c r="H142" s="6" t="s">
-        <v>224</v>
       </c>
       <c r="I142" s="5">
         <v>46412</v>
@@ -9673,13 +9670,13 @@
         <v>26</v>
       </c>
       <c r="N142" s="6" t="s">
-        <v>370</v>
+        <v>369</v>
       </c>
       <c r="O142" s="6" t="s">
-        <v>358</v>
+        <v>357</v>
       </c>
       <c r="P142" s="6" t="s">
-        <v>370</v>
+        <v>369</v>
       </c>
       <c r="Q142" s="6"/>
       <c r="R142" s="6"/>
@@ -9689,7 +9686,7 @@
     </row>
     <row r="143" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A143" s="8" t="s">
-        <v>379</v>
+        <v>378</v>
       </c>
       <c r="B143" s="9">
         <v>46239.67595826389</v>
@@ -9699,16 +9696,16 @@
         <v>46240.59569465277</v>
       </c>
       <c r="E143" s="10" t="s">
-        <v>380</v>
+        <v>379</v>
       </c>
       <c r="F143" s="10" t="s">
         <v>26</v>
       </c>
       <c r="G143" s="10" t="s">
+        <v>222</v>
+      </c>
+      <c r="H143" s="10" t="s">
         <v>223</v>
-      </c>
-      <c r="H143" s="10" t="s">
-        <v>224</v>
       </c>
       <c r="I143" s="9">
         <v>46412</v>
@@ -9726,13 +9723,13 @@
         <v>26</v>
       </c>
       <c r="N143" s="10" t="s">
-        <v>370</v>
+        <v>369</v>
       </c>
       <c r="O143" s="10" t="s">
-        <v>361</v>
+        <v>360</v>
       </c>
       <c r="P143" s="10" t="s">
-        <v>381</v>
+        <v>380</v>
       </c>
       <c r="Q143" s="10"/>
       <c r="R143" s="10"/>
@@ -9742,7 +9739,7 @@
     </row>
     <row r="144" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A144" s="4" t="s">
-        <v>382</v>
+        <v>381</v>
       </c>
       <c r="B144" s="5">
         <v>46239.67596550926</v>
@@ -9758,10 +9755,10 @@
         <v>26</v>
       </c>
       <c r="G144" s="6" t="s">
+        <v>222</v>
+      </c>
+      <c r="H144" s="6" t="s">
         <v>223</v>
-      </c>
-      <c r="H144" s="6" t="s">
-        <v>224</v>
       </c>
       <c r="I144" s="5">
         <v>46412</v>
@@ -9779,13 +9776,13 @@
         <v>26</v>
       </c>
       <c r="N144" s="6" t="s">
-        <v>370</v>
+        <v>369</v>
       </c>
       <c r="O144" s="6" t="s">
-        <v>364</v>
+        <v>363</v>
       </c>
       <c r="P144" s="6" t="s">
-        <v>381</v>
+        <v>380</v>
       </c>
       <c r="Q144" s="6"/>
       <c r="R144" s="6"/>
@@ -9795,7 +9792,7 @@
     </row>
     <row r="145" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A145" s="8" t="s">
-        <v>383</v>
+        <v>382</v>
       </c>
       <c r="B145" s="9">
         <v>46239.67597105324</v>
@@ -9805,16 +9802,16 @@
         <v>46240.59568726852</v>
       </c>
       <c r="E145" s="10" t="s">
-        <v>380</v>
+        <v>379</v>
       </c>
       <c r="F145" s="10" t="s">
         <v>26</v>
       </c>
       <c r="G145" s="10" t="s">
+        <v>222</v>
+      </c>
+      <c r="H145" s="10" t="s">
         <v>223</v>
-      </c>
-      <c r="H145" s="10" t="s">
-        <v>224</v>
       </c>
       <c r="I145" s="9">
         <v>46412</v>
@@ -9832,13 +9829,13 @@
         <v>26</v>
       </c>
       <c r="N145" s="10" t="s">
-        <v>370</v>
+        <v>369</v>
       </c>
       <c r="O145" s="10" t="s">
-        <v>367</v>
+        <v>366</v>
       </c>
       <c r="P145" s="10" t="s">
-        <v>384</v>
+        <v>383</v>
       </c>
       <c r="Q145" s="10"/>
       <c r="R145" s="10"/>
@@ -9848,7 +9845,7 @@
     </row>
     <row r="146" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A146" s="4" t="s">
-        <v>385</v>
+        <v>384</v>
       </c>
       <c r="B146" s="5">
         <v>46239.574665231485</v>
@@ -9858,16 +9855,16 @@
         <v>46240.59601453703</v>
       </c>
       <c r="E146" s="6" t="s">
-        <v>386</v>
+        <v>385</v>
       </c>
       <c r="F146" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G146" s="6" t="s">
+        <v>222</v>
+      </c>
+      <c r="H146" s="6" t="s">
         <v>223</v>
-      </c>
-      <c r="H146" s="6" t="s">
-        <v>224</v>
       </c>
       <c r="I146" s="5">
         <v>46413</v>
@@ -9885,13 +9882,13 @@
         <v>26</v>
       </c>
       <c r="N146" s="6" t="s">
-        <v>326</v>
+        <v>325</v>
       </c>
       <c r="O146" s="6" t="s">
+        <v>386</v>
+      </c>
+      <c r="P146" s="6" t="s">
         <v>387</v>
-      </c>
-      <c r="P146" s="6" t="s">
-        <v>388</v>
       </c>
       <c r="Q146" s="5">
         <v>46413</v>
@@ -9911,7 +9908,7 @@
     </row>
     <row r="147" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A147" s="8" t="s">
-        <v>389</v>
+        <v>388</v>
       </c>
       <c r="B147" s="9">
         <v>46239.57467313657</v>
@@ -9921,16 +9918,16 @@
         <v>46240.5962641088</v>
       </c>
       <c r="E147" s="10" t="s">
-        <v>189</v>
+        <v>188</v>
       </c>
       <c r="F147" s="10" t="s">
         <v>26</v>
       </c>
       <c r="G147" s="10" t="s">
+        <v>222</v>
+      </c>
+      <c r="H147" s="10" t="s">
         <v>223</v>
-      </c>
-      <c r="H147" s="10" t="s">
-        <v>224</v>
       </c>
       <c r="I147" s="9">
         <v>46413</v>
@@ -9948,13 +9945,13 @@
         <v>26</v>
       </c>
       <c r="N147" s="10" t="s">
-        <v>386</v>
+        <v>385</v>
       </c>
       <c r="O147" s="10" t="s">
-        <v>189</v>
+        <v>188</v>
       </c>
       <c r="P147" s="10" t="s">
-        <v>390</v>
+        <v>389</v>
       </c>
       <c r="Q147" s="10"/>
       <c r="R147" s="10"/>
@@ -9964,7 +9961,7 @@
     </row>
     <row r="148" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A148" s="4" t="s">
-        <v>391</v>
+        <v>390</v>
       </c>
       <c r="B148" s="5">
         <v>46239.57467765047</v>
@@ -9974,16 +9971,16 @@
         <v>46240.5962597801</v>
       </c>
       <c r="E148" s="6" t="s">
-        <v>189</v>
+        <v>188</v>
       </c>
       <c r="F148" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G148" s="6" t="s">
+        <v>222</v>
+      </c>
+      <c r="H148" s="6" t="s">
         <v>223</v>
-      </c>
-      <c r="H148" s="6" t="s">
-        <v>224</v>
       </c>
       <c r="I148" s="5">
         <v>46413</v>
@@ -10001,13 +9998,13 @@
         <v>26</v>
       </c>
       <c r="N148" s="6" t="s">
-        <v>386</v>
+        <v>385</v>
       </c>
       <c r="O148" s="6" t="s">
-        <v>189</v>
+        <v>188</v>
       </c>
       <c r="P148" s="6" t="s">
-        <v>392</v>
+        <v>391</v>
       </c>
       <c r="Q148" s="6"/>
       <c r="R148" s="6"/>
@@ -10017,7 +10014,7 @@
     </row>
     <row r="149" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A149" s="8" t="s">
-        <v>393</v>
+        <v>392</v>
       </c>
       <c r="B149" s="9">
         <v>46239.57468208333</v>
@@ -10027,16 +10024,16 @@
         <v>46240.596255625</v>
       </c>
       <c r="E149" s="10" t="s">
-        <v>189</v>
+        <v>188</v>
       </c>
       <c r="F149" s="10" t="s">
         <v>26</v>
       </c>
       <c r="G149" s="10" t="s">
+        <v>222</v>
+      </c>
+      <c r="H149" s="10" t="s">
         <v>223</v>
-      </c>
-      <c r="H149" s="10" t="s">
-        <v>224</v>
       </c>
       <c r="I149" s="9">
         <v>46413</v>
@@ -10054,13 +10051,13 @@
         <v>26</v>
       </c>
       <c r="N149" s="10" t="s">
-        <v>386</v>
+        <v>385</v>
       </c>
       <c r="O149" s="10" t="s">
-        <v>189</v>
+        <v>188</v>
       </c>
       <c r="P149" s="10" t="s">
-        <v>392</v>
+        <v>391</v>
       </c>
       <c r="Q149" s="10"/>
       <c r="R149" s="10"/>
@@ -10070,7 +10067,7 @@
     </row>
     <row r="150" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A150" s="4" t="s">
-        <v>394</v>
+        <v>393</v>
       </c>
       <c r="B150" s="5">
         <v>46239.653672326385</v>
@@ -10080,16 +10077,16 @@
         <v>46240.59625209491</v>
       </c>
       <c r="E150" s="6" t="s">
-        <v>189</v>
+        <v>188</v>
       </c>
       <c r="F150" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G150" s="6" t="s">
+        <v>222</v>
+      </c>
+      <c r="H150" s="6" t="s">
         <v>223</v>
-      </c>
-      <c r="H150" s="6" t="s">
-        <v>224</v>
       </c>
       <c r="I150" s="5">
         <v>46413</v>
@@ -10107,10 +10104,10 @@
         <v>26</v>
       </c>
       <c r="N150" s="6" t="s">
-        <v>386</v>
+        <v>385</v>
       </c>
       <c r="O150" s="6" t="s">
-        <v>195</v>
+        <v>194</v>
       </c>
       <c r="P150" s="6" t="s">
         <v>26</v>
@@ -10123,7 +10120,7 @@
     </row>
     <row r="151" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A151" s="8" t="s">
-        <v>395</v>
+        <v>394</v>
       </c>
       <c r="B151" s="9">
         <v>46239.67752369213</v>
@@ -10139,10 +10136,10 @@
         <v>26</v>
       </c>
       <c r="G151" s="10" t="s">
+        <v>222</v>
+      </c>
+      <c r="H151" s="10" t="s">
         <v>223</v>
-      </c>
-      <c r="H151" s="10" t="s">
-        <v>224</v>
       </c>
       <c r="I151" s="9">
         <v>46413</v>
@@ -10160,10 +10157,10 @@
         <v>26</v>
       </c>
       <c r="N151" s="10" t="s">
-        <v>386</v>
+        <v>385</v>
       </c>
       <c r="O151" s="10" t="s">
-        <v>358</v>
+        <v>357</v>
       </c>
       <c r="P151" s="10" t="s">
         <v>26</v>
@@ -10176,7 +10173,7 @@
     </row>
     <row r="152" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A152" s="4" t="s">
-        <v>396</v>
+        <v>395</v>
       </c>
       <c r="B152" s="5">
         <v>46239.67753166667</v>
@@ -10192,10 +10189,10 @@
         <v>26</v>
       </c>
       <c r="G152" s="6" t="s">
+        <v>222</v>
+      </c>
+      <c r="H152" s="6" t="s">
         <v>223</v>
-      </c>
-      <c r="H152" s="6" t="s">
-        <v>224</v>
       </c>
       <c r="I152" s="5">
         <v>46413</v>
@@ -10213,10 +10210,10 @@
         <v>26</v>
       </c>
       <c r="N152" s="6" t="s">
-        <v>386</v>
+        <v>385</v>
       </c>
       <c r="O152" s="6" t="s">
-        <v>380</v>
+        <v>379</v>
       </c>
       <c r="P152" s="6" t="s">
         <v>26</v>
@@ -10229,7 +10226,7 @@
     </row>
     <row r="153" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A153" s="8" t="s">
-        <v>397</v>
+        <v>396</v>
       </c>
       <c r="B153" s="9">
         <v>46239.677537361116</v>
@@ -10245,10 +10242,10 @@
         <v>26</v>
       </c>
       <c r="G153" s="10" t="s">
+        <v>222</v>
+      </c>
+      <c r="H153" s="10" t="s">
         <v>223</v>
-      </c>
-      <c r="H153" s="10" t="s">
-        <v>224</v>
       </c>
       <c r="I153" s="9">
         <v>46413</v>
@@ -10266,7 +10263,7 @@
         <v>26</v>
       </c>
       <c r="N153" s="10" t="s">
-        <v>386</v>
+        <v>385</v>
       </c>
       <c r="O153" s="10" t="s">
         <v>56</v>
@@ -10282,7 +10279,7 @@
     </row>
     <row r="154" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A154" s="4" t="s">
-        <v>398</v>
+        <v>397</v>
       </c>
       <c r="B154" s="5">
         <v>46239.67754380787</v>
@@ -10298,10 +10295,10 @@
         <v>26</v>
       </c>
       <c r="G154" s="6" t="s">
+        <v>222</v>
+      </c>
+      <c r="H154" s="6" t="s">
         <v>223</v>
-      </c>
-      <c r="H154" s="6" t="s">
-        <v>224</v>
       </c>
       <c r="I154" s="5">
         <v>46413</v>
@@ -10319,10 +10316,10 @@
         <v>26</v>
       </c>
       <c r="N154" s="6" t="s">
-        <v>386</v>
+        <v>385</v>
       </c>
       <c r="O154" s="6" t="s">
-        <v>380</v>
+        <v>379</v>
       </c>
       <c r="P154" s="6" t="s">
         <v>26</v>
@@ -10335,7 +10332,7 @@
     </row>
     <row r="155" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A155" s="8" t="s">
-        <v>399</v>
+        <v>398</v>
       </c>
       <c r="B155" s="9">
         <v>46239.57468613426</v>
@@ -10345,7 +10342,7 @@
         <v>46240.58500695602</v>
       </c>
       <c r="E155" s="10" t="s">
-        <v>400</v>
+        <v>399</v>
       </c>
       <c r="F155" s="10" t="s">
         <v>25</v>
@@ -10369,7 +10366,7 @@
         <v>26</v>
       </c>
       <c r="O155" s="10" t="s">
-        <v>401</v>
+        <v>400</v>
       </c>
       <c r="P155" s="10" t="s">
         <v>26</v>
@@ -10382,7 +10379,7 @@
     </row>
     <row r="156" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A156" s="4" t="s">
-        <v>402</v>
+        <v>401</v>
       </c>
       <c r="B156" s="5">
         <v>46239.57468942129</v>
@@ -10392,16 +10389,16 @@
         <v>46240.596291608796</v>
       </c>
       <c r="E156" s="6" t="s">
+        <v>402</v>
+      </c>
+      <c r="F156" s="6" t="s">
+        <v>26</v>
+      </c>
+      <c r="G156" s="6" t="s">
         <v>403</v>
       </c>
-      <c r="F156" s="6" t="s">
-        <v>26</v>
-      </c>
-      <c r="G156" s="6" t="s">
+      <c r="H156" s="6" t="s">
         <v>404</v>
-      </c>
-      <c r="H156" s="6" t="s">
-        <v>405</v>
       </c>
       <c r="I156" s="5">
         <v>46414</v>
@@ -10419,13 +10416,13 @@
         <v>26</v>
       </c>
       <c r="N156" s="6" t="s">
-        <v>400</v>
+        <v>399</v>
       </c>
       <c r="O156" s="6" t="s">
-        <v>406</v>
+        <v>405</v>
       </c>
       <c r="P156" s="6" t="s">
-        <v>400</v>
+        <v>399</v>
       </c>
       <c r="Q156" s="5">
         <v>46422</v>
@@ -10445,7 +10442,7 @@
     </row>
     <row r="157" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A157" s="8" t="s">
-        <v>407</v>
+        <v>406</v>
       </c>
       <c r="B157" s="9">
         <v>46239.57469508101</v>
@@ -10455,16 +10452,16 @@
         <v>46240.596288217595</v>
       </c>
       <c r="E157" s="10" t="s">
-        <v>408</v>
+        <v>407</v>
       </c>
       <c r="F157" s="10" t="s">
         <v>26</v>
       </c>
       <c r="G157" s="10" t="s">
+        <v>403</v>
+      </c>
+      <c r="H157" s="10" t="s">
         <v>404</v>
-      </c>
-      <c r="H157" s="10" t="s">
-        <v>405</v>
       </c>
       <c r="I157" s="9">
         <v>46414</v>
@@ -10482,13 +10479,13 @@
         <v>26</v>
       </c>
       <c r="N157" s="10" t="s">
-        <v>400</v>
+        <v>399</v>
       </c>
       <c r="O157" s="10" t="s">
-        <v>409</v>
+        <v>408</v>
       </c>
       <c r="P157" s="10" t="s">
-        <v>400</v>
+        <v>399</v>
       </c>
       <c r="Q157" s="9">
         <v>46422</v>

--- a/data/50001592 - VITA EXPRESS INC (Venezuela).xlsx
+++ b/data/50001592 - VITA EXPRESS INC (Venezuela).xlsx
@@ -4147,7 +4147,7 @@
       </c>
       <c r="C43" s="10"/>
       <c r="D43" s="9">
-        <v>46240.58674861111</v>
+        <v>46265.17152752315</v>
       </c>
       <c r="E43" s="10" t="s">
         <v>97</v>
